--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0016.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0016.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Chiến Thuật Chủ Động ({0}): Display tối đa 3 lá bài có Biến Đổi từ bộ bài. Rút &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; lá vào tay. Trộn những lá không chọn {Cus:Sap,S=cards P=card SapTag=1} lại vào bộ bài.</t>
+          <t>Chiến Thuật Chủ Động ({0}): Hiển thị tối đa 3 lá bài có Transform từ bộ bài. Rút &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; lá vào tay. Trộn những lá không chọn {Cus:Sap,S=cards P=card SapTag=1} lại vào bộ bài.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Khi ngươi Điều Chỉnh Tacet Discord này, lật lên tối đa 3 lá bài có Biến Đổi từ bộ bài và thêm 1 lá vào tay. Trộn các lá không chọn lại vào bộ bài và nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Năng Lượng.</t>
+          <t>Khi ngươi Điều Chỉnh Tacet Discord này, lật lên tối đa 3 lá bài có Transform từ bộ bài và thêm 1 lá vào tay. Trộn các lá không chọn lại vào bộ bài và nhận &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
         <is>
           <t>Biểu đồ dạng sóng của Cartethyia cho thấy dao động hình elip với miền thời gian ổn định. Giá trị đỉnh giữa giới hạn trên và dưới có xu hướng tăng gián đoạn, nhưng chưa vượt ngưỡng nguy hiểm. Không phát hiện dao động bất thường.
 Lực bên trong và bên ngoài Cartethyia gần như đã đạt đến trạng thái hợp nhất.
-Mức Độ Cộng Hưởng Nguy Hiểm: High. Độ ổn định cao, rủi ro &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp. Tuy nhiên, cần lưu ý rằng cơ thể Cartethyia xuất hiện dao động năng lượng không ổn định khi rời xa &lt;te href=850096&gt;Rinascita&lt;/te&gt;.
+Mức Độ Cộng Hưởng Nguy Hiểm: Cao. Độ ổn định cao, rủi ro &lt;te href=850073&gt;Quá Tải&lt;/te&gt; rất thấp. Tuy nhiên, cần lưu ý rằng cơ thể Cartethyia xuất hiện dao động năng lượng không ổn định khi rời xa &lt;te href=850096&gt;Rinascita&lt;/te&gt;.
 Cartethyia là một cá thể hiếm hoi đã trải qua Thức Tỉnh Lần Hai, cho phép cô tự do chuyển đổi giữa hai hình thái. Cần nhấn mạnh rằng đây không phải là Quá Tải, mà là sự vận dụng sức mạnh một cách chính xác.
 &lt;i&gt;Ghi chú từ một Người Gìn Giữ Hoa: Khi cô Cartethyia... không, xin lỗi, Fleurdelys, thể hiện sức mạnh của mình, cơn bão gần như xé toang cả mô phỏng! Trời ơi, lần thử nghiệm tới chúng ta phải cẩn thận hơn mới được!&lt;/i&gt;</t>
         </is>
@@ -2214,7 +2214,7 @@
           <t>Một nhà viết kịch đã nghỉ hưu thích kể một câu chuyện nhất định: Ngày xửa ngày xưa, ở vùng quê của Thị trấn Egla, có một hiệp sĩ lang thang. Tay cầm thanh kiếm, chàng đi khắp nơi tìm kiếm một người khổng lồ huyền thoại. Một gã khổng lồ cao như cối xay gió, cánh tay dài và mảnh như những lưỡi dao của nó. Hết lần này đến lần khác, hiệp sĩ lang thang chiến đấu hết mình với gã khổng lồ, nhưng hắn không hề nói một lời, chỉ vung vẩy đôi tay, khiến mọi đòn tấn công của hiệp sĩ đều vô hiệu.
 Có người cười nhạo sự ngốc nghếch của hiệp sĩ, có người thương hại cho ảo tưởng của chàng. Suy cho cùng, cái gọi là khổng lồ ấy chẳng qua chỉ là một chiếc cối xay gió, và những trận chiến của chàng chỉ là ảo mộng. Nhưng cô bé tinh nghịch nhất vùng quê lại nhìn nhận khác.
 Cô tìm cho mình một chiếc mũ giáp của hiệp sĩ và nài nỉ nhà viết kịch tặng một thanh kiếm gỗ nhỏ. "Để chiến đấu vì một gã khổng lồ như thế," cô nói, "chàng ấy hẳn phải có trái tim thuần khiết và cao quý." Và thế là cô cũng muốn trở thành hiệp sĩ, đi tìm gã khổng lồ đã phá hủy nhà cửa và xua đuổi gia súc, để những con Dơi Vàng Cắp Trộm ẩn nấp ven đường không còn cướp đi bất kỳ kho báu nào của lữ khách.
-Cưỡi một con Tumbleyak sặc sỡ, cô phi qua những cánh đồng lúa mì. Thế giới chưa bao giờ rộng lớn đến thế. Đây là nơi huyền thoại của Thánh Nữ bắt đầu. Qua những cánh đồng, qua những lễ hội, và tiến vào Tower Ngược.
+Cưỡi một con Tumbleyak sặc sỡ, cô phi qua những cánh đồng lúa mì. Thế giới chưa bao giờ rộng lớn đến thế. Đây là nơi huyền thoại của Thánh Nữ bắt đầu. Qua những cánh đồng, qua những lễ hội, và tiến vào Tháp Ngược.
 Đó sẽ là một cuộc phiêu lưu hào hùng.</t>
         </is>
       </c>
@@ -2371,7 +2371,7 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>Là Fleurdelys, nàng buộc phải cầm gươm ra trận.
-Vì điều này, nàng đã học hỏi tất cả những gì có thể. Nàng nghiên cứu kinh điển của Giáo Hội và rèn giũa kỹ năng chiến đấu. Nàng lắng nghe tiếng lòng của nhân dân, tận tâm thực hiện những nguyện vọng của họ. Khi ai đó cầu nguyện cho sức khỏe, nàng sắp xếp gửi đến những loại thuốc quý giá. Khi ai đó tìm kiếm bình yên, nàng sẽ lắng nghe những lời sám hối, ôm trọn những nỗi đau quá khứ của họ. Khi một &lt;te href=850081&gt;Discord&lt;/te&gt; bùng phát, nàng rút gươm dập tắt nó từ trong trứng nước. Những việc làm ấy chẳng khác gì những gì nàng từng làm ở quê nhà.
+Vì điều này, nàng đã học hỏi tất cả những gì có thể. Nàng nghiên cứu kinh điển của Giáo Hội và rèn giũa kỹ năng chiến đấu. Nàng lắng nghe tiếng lòng của nhân dân, tận tâm thực hiện những nguyện vọng của họ. Khi ai đó cầu nguyện cho sức khỏe, nàng sắp xếp gửi đến những loại thuốc quý giá. Khi ai đó tìm kiếm bình yên, nàng sẽ lắng nghe những lời sám hối, ôm trọn những nỗi đau quá khứ của họ. Khi một &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; bùng phát, nàng rút gươm dập tắt nó từ trong trứng nước. Những việc làm ấy chẳng khác gì những gì nàng từng làm ở quê nhà.
 Điểm khác biệt duy nhất là nàng không còn đối mặt với một ngôi làng nhỏ hay những gương mặt thân quen. Phần lớn những người tìm đến sự giúp đỡ của nàng đều là người lạ, và nàng hiểu rằng mỗi người trong số họ như một ngọn đèn nhỏ. Càng giúp đỡ nhiều, họ sẽ càng tỏa sáng trên bầu trời đêm của &lt;te href=850096&gt;Rinascita&lt;/te&gt;.
 Thế nhưng, thế giới quá rộng lớn, và Giáo Hội cũng chẳng hoàn hảo như những gì sách vở từng ca tụng. Giới quý tộc chỉ biết lo cho lợi ích của riêng mình, còn những tín đồ tự xưng mộ đạo chỉ biết diễn trò sùng kính, nhắm mắt làm ngơ trước tiếng kêu cứu của dân chúng. Nàng đã thấy những kẻ quý tộc khoe khoang lòng nhân từ nhưng lại nhét đầy túi tiền, ngoảnh mặt làm ngơ trước lời cầu xin của những người khốn khổ.
 Trong những lúc như thế, tất cả những gì nàng có thể làm là siết chặt tay cầm gươm.
@@ -4042,7 +4042,7 @@
         <is>
           <t>[
 Xác Nhận Điều Kiện Trước Trận Đấu]
-Name Đấu Sĩ: Lupa
+Tên Đấu Sĩ: Lupa
 Phân tích dạng sóng quang phổ cho thấy dao động elip với miền thời gian ổn định. Không phát hiện mẫu dị thường.
 Chẩn đoán: Ngưỡng &lt;te href=850073&gt;Overclocking&lt;/te&gt; cao. Độ ổn định của đối tượng vẫn vững chắc. Không có dấu hiệu hoặc tiền sử Overclocking.
 &lt;i&gt;"Đấu sĩ Lupa luôn tuân thủ lịch kiểm tra sức khỏe đều đặn. Trong số các Võ Sĩ hàng đầu, hiếm ai duy trì kỷ luật như cô ấy."&lt;/i&gt;</t>
@@ -4324,7 +4324,7 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>Từ ngày cha mẹ Lupa đoạn tuyệt với cô, khuôn mặt họ dần mờ nhạt trong ký ức.
-Những gì còn đọng lại là cách họ thường hồi tưởng về những ngày tháng trên Capitoline Hill, nơi xa xôi so với ngôi làng nhỏ bé mà cô gọi là nhà. Họ từng mang họ Silva, cho đến khi bị trục xuất, chịu nhục nhã vì thất bại trên đấu trường. Từ đó, cuộc đời họ chỉ còn lại hối tiếc, khổ đau và những ngón tay chì chiết.
+Những gì còn đọng lại là cách họ thường hồi tưởng về những ngày tháng trên Đồi Capitoline, nơi xa xôi so với ngôi làng nhỏ bé mà cô gọi là nhà. Họ từng mang họ Silva, cho đến khi bị trục xuất, chịu nhục nhã vì thất bại trên đấu trường. Từ đó, cuộc đời họ chỉ còn lại hối tiếc, khổ đau và những ngón tay chì chiết.
 Thế nhưng, khi nghe tin Lupa thắng trận đầu tiên, họ vẫn đến thợ rèn và đặt làm chiếc huy chương này, một món quà kỷ niệm chiến thắng của cô.</t>
         </is>
       </c>
@@ -4536,9 +4536,9 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>Nóng rực. Đó là ký ức đầu tiên của Lupa về ngôi làng nhỏ nơi cô sinh ra.
-Mùa hè kéo dài vô tận, cái nóng như thiêu đốt đến nỗi mặt hồ cũng như sôi lên. Nhưng lũ trẻ ở Septimont chẳng màng gì. Xa xa, trên đỉnh Capitoline Hill, Đại Hội Agon sắp bắt đầu. Làng hiếm khi có Võ Sĩ nào đủ tài để tham gia, nhưng không khí hào hứng vẫn lan tỏa khắp nơi. Ngay cả lũ trẻ cũng không thể cưỡng lại việc cầm vũ khí lên và tái hiện những trận chiến giả để ăn mừng.
+Mùa hè kéo dài vô tận, cái nóng như thiêu đốt đến nỗi mặt hồ cũng như sôi lên. Nhưng lũ trẻ ở Septimont chẳng màng gì. Xa xa, trên đỉnh Đồi Capitoline, Đại Hội Agon sắp bắt đầu. Làng hiếm khi có Võ Sĩ nào đủ tài để tham gia, nhưng không khí hào hứng vẫn lan tỏa khắp nơi. Ngay cả lũ trẻ cũng không thể cưỡng lại việc cầm vũ khí lên và tái hiện những trận chiến giả để ăn mừng.
 Giữa một trong những trận Agon trẻ con ấy, Lupa bị gọi về nhà.
-Bước qua cánh cửa, cô lại nghe thấy cuộc trò chuyện quen thuộc. Cha mẹ hỏi liệu cô có sẵn sàng chuyển lên Capitoline Hill không. Cô nói có. Họ hỏi liệu cô có muốn trở thành Võ Sĩ vì đã bộc lộ dấu hiệu của một Resonator không. Và một lần nữa, cô lại nói có. Những câu hỏi này đã được lặp đi lặp lại nhiều lần, và câu trả lời của cô vẫn không đổi. Thế nhưng mỗi lần, cha mẹ cô đều như thở phào nhẹ nhõm, như thể sợ một ngày nào đó cô sẽ từ chối, dù điều đó chưa bao giờ xảy ra.
+Bước qua cánh cửa, cô lại nghe thấy cuộc trò chuyện quen thuộc. Cha mẹ hỏi liệu cô có sẵn sàng chuyển lên Đồi Capitoline không. Cô nói có. Họ hỏi liệu cô có muốn trở thành Võ Sĩ vì đã bộc lộ dấu hiệu của một Resonator không. Và một lần nữa, cô lại nói có. Những câu hỏi này đã được lặp đi lặp lại nhiều lần, và câu trả lời của cô vẫn không đổi. Thế nhưng mỗi lần, cha mẹ cô đều như thở phào nhẹ nhõm, như thể sợ một ngày nào đó cô sẽ từ chối, dù điều đó chưa bao giờ xảy ra.
 Rồi những cuộc tranh cãi quen thuộc lại bắt đầu. Họ nên cố gắng hàn gắn mối quan hệ với Nhà Silva – những kẻ đã quay lưng với họ trong lúc khó khăn nhất? Hay nên bắt đầu lại ở một nơi mới? Mỗi khi nhắc đến thành phố lấp lánh trên đồi và Gia tộc mà họ từng phụng sự, giọng nói của họ lại mang một âm điệu – vừa khát khao được chấp nhận, vừa sợ hãi bị từ chối, giống như khi họ nói với Lupa về tương lai của cô.
 Lupa ngồi nghe một lúc. Khi nhận ra cha mẹ mình đã chìm vào cuộc cãi vã, quên mất sự hiện diện của cô, cô lặng lẽ đứng dậy, bước ra ngoài và quay trở lại đấu trường của mình. Cái nóng ngột ngạt bên trong cơ thể như bám chặt lấy cô, nặng nề và ẩm ướt, ngày càng lớn dần, đè nặng lên người. Nó thiêu đốt trong huyết quản, một cơn giận dữ ẩm ướt và bất an, ngày càng nóng bỏng hơn. Nó thúc đẩy cô tiến lên, khiến cô chạy nhanh hơn, đánh mạnh hơn, và lao vào đối thủ với tất cả sức lực.
 Và rồi cô nghe thấy tiếng thét kinh ngạc từ đám đông.
@@ -4615,7 +4615,7 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>Sau đó, Lupa theo cha mẹ đến Thành phố Septimont.
-Những bức tường đá trắng, tiếng chuông gió trong veo, và những bức tượng anh hùng ở khắp mọi ngả—thành phố như một cảnh tượng chói lòa. Nhưng điều khiến Lupa say mê nhất lại là cảnh tượng phổ biến nhất ở đây: những Võ Sĩ Giác Đấu. Vũ khí của họ, &lt;te href=850082&gt;Echoes&lt;/te&gt; của họ, ánh mắt rực sáng khi họ nói về các đội và điểm số... Tất cả đều khơi lên một tia lửa trong huyết quản cô. Ngọn lửa nhỏ bé trong tim cô bùng lên dữ dội, thôi thúc cô lao thẳng đến Colosseum Olymdos và đắm mình trong cơn say của trận chiến.
+Những bức tường đá trắng, tiếng chuông gió trong veo, và những bức tượng anh hùng ở khắp mọi ngả—thành phố như một cảnh tượng chói lòa. Nhưng điều khiến Lupa say mê nhất lại là cảnh tượng phổ biến nhất ở đây: những Võ Sĩ Giác Đấu. Vũ khí của họ, &lt;te href=850082&gt;Echoes&lt;/te&gt; của họ, ánh mắt rực sáng khi họ nói về các đội và điểm số... Tất cả đều khơi lên một tia lửa trong huyết quản cô. Ngọn lửa nhỏ bé trong tim cô bùng lên dữ dội, thôi thúc cô lao thẳng đến Đấu Trường Olymdos và đắm mình trong cơn say của trận chiến.
 Nhưng điều đó đã không xảy ra. Thay vào đó, cha mẹ cô dẫn cô đến dinh thự Silva, nơi nhiều thiếu niên đầy khát vọng như cô đang đứng chờ.
 Trận đấu này đến trận đấu khác, Lupa chiến đấu không ngừng. Cho đến khi, nghiến răng và nắm chặt ngọn giáo, cô bước qua những đối thủ gục ngã để tiến vào đại sảnh của Silva.
 Đó là lúc Domina Julia chọn cô giữa đám đông.
@@ -4695,16 +4695,16 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>The Nameless loạng choạng tiến về phía trước, đi ngang qua một Người Khổng Lồ Glory im lặng.
+          <t>Kẻ Vô Danh loạng choạng tiến về phía trước, đi ngang qua một Người Khổng Lồ Vinh Quang im lặng.
 Đôi chân cô nặng trĩu, ký ức dần tan rã. Ngay cả việc ghép nối một ý nghĩ hoàn chỉnh cũng trở nên khó khăn. Đôi khi, khi Cartethyia nói chuyện với cô, cô phải dừng lại rất lâu mới có thể đáp lời.
 Hành trình ngắn ngủi này có lẽ sắp kết thúc.
-Septimont, thành phố của cô, thành phố huy hoàng, giờ đây chìm trong Biển Tối… The Nameless không còn biết liệu nó có thể được cứu vớt hay không. Có lẽ cuộc điều tra mà họ đang bám víu đã sớm thất bại. Cartethyia không nghĩ vậy, nhưng The Nameless không còn đủ sức níu giữ. Cảm giác buồn nôn từ làn nước lạnh bên trong đang lan dần qua xương thịt, từ từ biến cô thành thứ gì đó khác.
+Septimont, thành phố của cô, thành phố huy hoàng, giờ đây chìm trong Biển Tối… Kẻ Vô Danh không còn biết liệu nó có thể được cứu vớt hay không. Có lẽ cuộc điều tra mà họ đang bám víu đã sớm thất bại. Cartethyia không nghĩ vậy, nhưng Kẻ Vô Danh không còn đủ sức níu giữ. Cảm giác buồn nôn từ làn nước lạnh bên trong đang lan dần qua xương thịt, từ từ biến cô thành thứ gì đó khác.
 Tin tốt là cô cảm thấy sự tồn tại của mình đang yếu dần. Có lẽ cô có thể tan biến trước khi hoàn toàn bị Biển Tối chiếm hữu. Ít nhất, như vậy cô sẽ không phải để Cartethyia gánh chịu gánh nặng cuối cùng.
-Khi làm việc cùng người khác, The Nameless hiếm khi là người được chăm sóc. Giờ đây, sự bất lực này lần đầu gặm nhấm cô. Cartethyia phải chậm lại vì cô. Nỗi xấu hổ thiêu đốt trong lòng The Nameless, nhưng cô chẳng thể làm gì ngoài việc hy vọng—vâng, hy vọng rằng Người Công Chính mà Cartethyia tin tưởng sẽ sớm xuất hiện.
+Khi làm việc cùng người khác, Kẻ Vô Danh hiếm khi là người được chăm sóc. Giờ đây, sự bất lực này lần đầu gặm nhấm cô. Cartethyia phải chậm lại vì cô. Nỗi xấu hổ thiêu đốt trong lòng Kẻ Vô Danh, nhưng cô chẳng thể làm gì ngoài việc hy vọng—vâng, hy vọng rằng Người Công Chính mà Cartethyia tin tưởng sẽ sớm xuất hiện.
 "Ước gì ta vẫn còn hữu dụng với người bạn mới này..."
 Nghiến răng, cô chống cây vũ khí xuống và ép mình bước thêm một bước.
 "Ước gì ta vẫn còn làm được nhiều hơn..."
-The Nameless ngẩng đầu lên. Phía trên, một anh hùng từng ghi danh vào lịch sử Septimont vẫn đứng sừng sững, tay cầm giáo, nhìn xuống. Khuôn mặt đá tạc dường như mang một niềm thương cảm thầm lặng, che chở cô khỏi cơn mưa đen từ bầu trời, dang rộng vòng tay vô ngôn cho những kẻ đến sau.</t>
+Kẻ Vô Danh ngẩng đầu lên. Phía trên, một anh hùng từng ghi danh vào lịch sử Septimont vẫn đứng sừng sững, tay cầm giáo, nhìn xuống. Khuôn mặt đá tạc dường như mang một niềm thương cảm thầm lặng, che chở cô khỏi cơn mưa đen từ bầu trời, dang rộng vòng tay vô ngôn cho những kẻ đến sau.</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
 Chỉ có ba người họ biết sự thật, nhưng đó thực sự là một hành trình đầy gập ghềnh và kịch tính, xứng đáng được kể lại trong một thiên sử thi.
 Nhưng khi mọi chuyện đã ổn thỏa và căng thẳng dần tan biến, một nỗi lo âu mơ hồ lại bắt đầu len lỏi trong lòng Lupa, lo cho {PlayerName}, người đồng đội tuyệt vời nhất của cô.
 Cô đã tận mắt chứng kiến sức mạnh của {PlayerName}. Nếu không có sự giúp đỡ của {PlayerName}, việc cứu Septimont đã là điều không thể. Nhưng chính vì {PlayerName} lại chiến thắng một cách quá đỗi tự nhiên, Lupa mới cảm thấy bất an. Cô không xa lạ gì với chiến thắng, và cô hiểu hơn ai hết bản chất hai mặt của những thành công liên tiếp. Sau chuỗi thắng lợi, một thất bại thực sự—không phải một vấp ngã nhỏ, mà là một cú ngã đau đớn—đôi khi có thể hủy hoại một người.
-Đúng là {PlayerName} rất mạnh mẽ. Lupa không thể tưởng tượng nổi điều gì có thể đánh bại {Male=anh;Female=cô} ấy. Nhưng nếu ngày đó đến...
+Đúng là {PlayerName} rất mạnh mẽ. Lupa không thể tưởng tượng nổi điều gì có thể đánh bại {Male=him;Female=her} ấy. Nhưng nếu ngày đó đến...
 Dù vậy, cô không biết phải nói gì. Tất cả những gì cô có thể làm là tự nhủ mình sẽ luôn ở đó, sẵn sàng giúp đỡ. Bằng cách nào đó, Lupa cảm nhận được rằng {PlayerName} đang hướng đến một vận mệnh vĩ đại hơn, một điều gì đó quá lớn lao mà cô không thể chạm tới hay thay đổi. Đúng vậy, có những điều lớn lao, và cũng có những điều nhỏ bé. Cứu một thành phố là điều vĩ đại. Chiến thắng một trận đấu, chỉ là chuyện nhỏ...
 ...Hay không hẳn.
 Cô chưa bao giờ nói với {PlayerName}, nhưng trong khi việc cứu thành phố là một thành tựu vĩ đại, thì hành trình ngắn ngủi họ đã đi cùng nhau lại mang đến cho cô nhiều điều không kém. Dù với {PlayerName}, đó có lẽ chỉ là một chiến thắng dễ dàng khác, nhưng với Lupa, nó có ý nghĩa rất lớn. Khi họ thắng trận bán kết và dựa vào nhau trong phòng chờ thoáng chốc, cô tràn ngập một niềm hạnh phúc chưa từng biết đến. Chính vì {PlayerName} coi đó như một việc thường ngày, không đáng để bận tâm, Lupa mới có thể tận hưởng trọn vẹn niềm vui thuần khiết của cuộc thi một lần nữa.
@@ -6160,7 +6160,7 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>Mya thu mình trong một con hẻm vắng, run rẩy vì cơn hoảng loạn dâng trào.
-Cô đã thắng trận bán kết, vậy mà những tiếng nói trong đầu vẫn không ngừng nghỉ. Cố gắng kìm Dodgen bản thân, cô bỏ chạy khỏi đấu trường.
+Cô đã thắng trận bán kết, vậy mà những tiếng nói trong đầu vẫn không ngừng nghỉ. Cố gắng kìm nén bản thân, cô bỏ chạy khỏi đấu trường.
 Một cái chạm nhẹ vào cánh tay khiến cô ngẩng lên. Một đứa trẻ Septimont nhỏ bé đứng đó, đưa cho cô một bó hoa. Đỏ mặt, đứa bé lắp bắp: "Chị chiến đấu giỏi lắm!" rồi chạy vụt đi.
 Những giọt sương vỡ trên đóa Viburnum lá đỏ. Mya ôm chặt bó hoa lạnh lẽo, ẩm ướt, khi một dòng nước mắt lăn dài trên má.</t>
         </is>
@@ -6515,7 +6515,7 @@
         <is>
           <t>Câu chuyện sắp đi đến hồi kết.
 Cartethyia cảm nhận được thế giới xung quanh đang thay đổi. Những tòa nhà, bức tượng, thậm chí cả mặt đất đều nứt vỡ như giấy ướt. Nhưng điều đó không còn quan trọng nữa. Cô đã tìm ra manh mối chỉ đến kẻ chủ mưu và đang tiến về phía Nhà Soạn Kịch. Với đám Fractsidus còn lẩn khuất ở đây, cô đã sẵn sàng cho trận chiến sắp tới.
-Còn những chuyện khác, Cartethyia không hề nghi ngờ gì về {PlayerName}. Người chính là thanh kiếm của cô, và cô hoàn toàn tin tưởng vào {Male=anh;Female=chị}.</t>
+Còn những chuyện khác, Cartethyia không hề nghi ngờ gì về {PlayerName}. Người chính là thanh kiếm của cô, và cô hoàn toàn tin tưởng vào {Male=him;Female=her}.</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Mắt Lupa chớp mở, hơi thở đứt quãng. Cơn lốc ký ức bất ngờ ùa về trong đầu suýt khiến cô nghẹn thở. Cartethyia, người đồng hành ngắn ngủi, đồng đội cùng giành danh hiệu với {PlayerName}, sự hỗn loạn ở Central Hub... và vô số vòng lặp trước đó khi Septimont bị Bóng Tối nuốt chửng. 
+          <t>Mắt Lupa chớp mở, hơi thở đứt quãng. Cơn lốc ký ức bất ngờ ùa về trong đầu suýt khiến cô nghẹn thở. Cartethyia, người đồng hành ngắn ngủi, đồng đội cùng giành danh hiệu với {PlayerName}, sự hỗn loạn ở Trung Tâm Điều Hành... và vô số vòng lặp trước đó khi Septimont bị Bóng Tối nuốt chửng. 
 Bầu trời phía trên vẫn trong xanh như chưa từng có chuyện gì. Tất cả những gì vừa xảy ra dường như chỉ là một cơn ác mộng. 
 Lupa mở bàn tay, tấm huy chương mà cô và Chiến Binh giành được cùng nhau nằm trên lòng bàn tay ướt đẫm mồ hôi. 
 Cô hít một hơi sâu, rồi lại một hơi nữa, trước khi nắm chặt nó trong tay. Cạnh sắc của huy chương cắm vào da thịt, nỗi đau kéo cô trở về thực tại. Nó thúc giục cô phải tiến về phía trước.</t>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Dữ liệu của Resonator đã chọn không tương thích với Trial Tai Họa này, có thể gây quá tải tính toán nghiêm trọng, dẫn đến độ khó tăng đột biến. Hãy cân nhắc sử dụng Resonator khác.</t>
+          <t>Dữ liệu của Resonator đã chọn không tương thích với Thử Thách Tai Họa này, có thể gây quá tải tính toán nghiêm trọng, dẫn đến độ khó tăng đột biến. Hãy cân nhắc sử dụng Resonator khác.</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
         <is>
           <t>Tờ giới thiệu hữu ích về Septimont, kèm theo vé trận đấu của các Chiến Binh.
 Thân gửi những người bạn từ phương xa, xin chào đón bằng những tràng pháo tay!
-Cảm ơn các bạn đã ủng hộ các Chiến Binh của chúng tôi. Chúng tôi chân thành mời các bạn tham dự Đại Hội Agon tại Colosseum Olymdos, đấu trường vĩ đại nhất của Septimont.
+Cảm ơn các bạn đã ủng hộ các Chiến Binh của chúng tôi. Chúng tôi chân thành mời các bạn tham dự Đại Hội Agon tại Đấu Trường Olymdos, đấu trường vĩ đại nhất của Septimont.
 Đại Hội Agon, sự kiện lớn nhất và danh giá nhất trong các kỳ Agon của Septimont, được tổ chức bốn năm một lần, trải qua nhiều vòng đấu để tìm ra chiến binh mạnh nhất thời đại.
 Các Chiến Binh đứng đầu sẽ nhận được phần thưởng hậu hĩnh, và đội vô địch sẽ được chính Ngài Ephor uy nghi của Septimont trao tặng danh hiệu cao quý.
 Nếu tiếng gọi của đấu trường thôi thúc bạn, sao không trực tiếp tham gia trận chiến? Cánh cổng Đại Hội Agon luôn rộng mở chào đón những kẻ dũng cảm sẵn sàng khắc tên mình vào lịch sử.</t>
@@ -7215,7 +7215,7 @@
       <c r="M100" t="inlineStr">
         <is>
           <t>Nếu đây là lần đầu các vị đặt chân đến Septimont, chúng tôi khuyến nghị bắt đầu hành trình tại Thermes Baths – viên ngọc văn hóa độc đáo của thành phố huy hoàng này.
-Tại đây, tắm không chỉ để thư giãn, mà còn là một phần thiết yếu của cuộc sống. Các vị sẽ được nghe những truyền thuyết về anh hùng, những tin đồn từ phố thị, và nếu may mắn, thậm chí còn gặp gỡ các Gladiator mà các vị hâm mộ, lắng nghe những câu chuyện trận mạc từ chính miệng họ!
+Tại đây, tắm không chỉ để thư giãn, mà còn là một phần thiết yếu của cuộc sống. Các vị sẽ được nghe những truyền thuyết về anh hùng, những tin đồn từ phố thị, và nếu may mắn, thậm chí còn gặp gỡ các Chiến Binh Gladiator mà các vị hâm mộ, lắng nghe những câu chuyện trận mạc từ chính miệng họ!
 Sau khi tắm táp thoải mái, còn gì tuyệt hơn một ly rượu để thư giãn? Hãy đến Caracalla Market, nơi hai địa điểm nổi tiếng chờ đón: Solis Tavern và Passa Inn &amp; Restaurant. Một số vé còn cho phép các vị hưởng ưu đãi độc quyền tại đây, đừng bỏ lỡ nhé!
 Chúc các vị săn tìm vui vẻ! Mong thời gian ở Septimont sẽ tràn đầy những khoảnh khắc khó quên.</t>
         </is>
@@ -7285,8 +7285,8 @@
       <c r="M101" t="inlineStr">
         <is>
           <t>Mục Tiêu Giai Đoạn khó đạt hơn.
-&lt;te href=851000&gt;&lt;color=#c79f49&gt;Giấc Mơ Gradation&lt;/color&gt;&lt;/te&gt; Echoes xuất hiện nhiều hơn.
-Bắt đầu với đạo cụ &lt;te href=851030&gt;&lt;color=#c79f49&gt;Fortune Bell&lt;/color&gt;&lt;/te&gt;.</t>
+&lt;te href=851000&gt;&lt;color=#c79f49&gt;Giấc Mơ Phân Cấp&lt;/color&gt;&lt;/te&gt; Echo xuất hiện nhiều hơn.
+Bắt đầu với đạo cụ &lt;te href=851030&gt;&lt;color=#c79f49&gt;Chuông May Mắn&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -7354,7 +7354,7 @@
       <c r="M102" t="inlineStr">
         <is>
           <t>Mục Tiêu Giai Đoạn khó đạt hơn.
-&lt;te href=851001&gt;&lt;color=#c79f49&gt;Giấc Mơ Nuốt Chửng&lt;/color&gt;&lt;/te&gt; Echoes xuất hiện nhiều hơn.
+&lt;te href=851001&gt;&lt;color=#c79f49&gt;Giấc Mơ Nuốt Chửng&lt;/color&gt;&lt;/te&gt; Echo xuất hiện nhiều hơn.
 Bắt đầu với đạo cụ &lt;te href=851029&gt;&lt;color=#c79f49&gt;Tượng: Nhạc Trưởng&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
@@ -7424,7 +7424,7 @@
         <is>
           <t>Mục tiêu Giai đoạn khó đạt hơn rồi.
 Chế độ Vô Tận sẽ mở khóa sau khi hoàn thành Mục tiêu Giai đoạn.
-Hãy bắt đầu với đạo cụ &lt;te href=851031&gt;&lt;color=#c79f49&gt;Mô Hình: Gulpuff&lt;/color&gt;&lt;/te&gt; và &lt;te href=851032&gt;&lt;color=#c79f49&gt;Round Quay Mộng Mị&lt;/color&gt;&lt;/te&gt;.</t>
+Hãy bắt đầu với đạo cụ &lt;te href=851031&gt;&lt;color=#c79f49&gt;Mô Hình: Gulpuff&lt;/color&gt;&lt;/te&gt; và &lt;te href=851032&gt;&lt;color=#c79f49&gt;Vòng Quay Mộng Mị&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       <c r="M104" t="inlineStr">
         <is>
           <t>Mục Tiêu Giai Đoạn khó đạt hơn.
-&lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mơ Trao đổi&lt;/color&gt;&lt;/te&gt; Echoes xuất hiện nhiều hơn.
+&lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mơ Trao Đổi&lt;/color&gt;&lt;/te&gt; Echo xuất hiện nhiều hơn.
 Bắt đầu với đạo cụ &lt;te href=851033&gt;&lt;color=#c79f49&gt;Pháo Hoa Mộng Ảo&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
@@ -7561,7 +7561,7 @@
       <c r="M105" t="inlineStr">
         <is>
           <t>Mục Tiêu Giai Đoạn khó đạt hơn.
-&lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; Echoes xuất hiện nhiều hơn.
+&lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; Echo xuất hiện nhiều hơn.
 Bắt đầu với đạo cụ &lt;te href=851058&gt;&lt;color=#c79f49&gt;Khối Hòa Trộn&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
@@ -7631,7 +7631,7 @@
         <is>
           <t>Mục tiêu Giai đoạn khó đạt hơn rồi.
 Chế độ Vô Tận sẽ mở khóa sau khi hoàn thành Mục tiêu Giai đoạn.
-Hãy bắt đầu với đạo cụ &lt;te href=851035&gt;&lt;color=#c79f49&gt;Surprise Box&lt;/color&gt;&lt;/te&gt; và &lt;te href=851036&gt;&lt;color=#c79f49&gt;Đèn Lồng Cơ Khí&lt;/color&gt;&lt;/te&gt;.</t>
+Hãy bắt đầu với đạo cụ &lt;te href=851035&gt;&lt;color=#c79f49&gt;Hộp Bất Ngờ&lt;/color&gt;&lt;/te&gt; và &lt;te href=851036&gt;&lt;color=#c79f49&gt;Đèn Lồng Cơ Khí&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Echo Giấc Mơ mang &lt;te href=851001&gt;&lt;color=#c79f49&gt;Giấc Mơ Nuốt Chửng&lt;/color&gt;&lt;/te&gt; và &lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mơ Trao đổi&lt;/color&gt;&lt;/te&gt; có tỷ lệ xuất hiện cao hơn.</t>
+          <t>Tiếng Vọng Giấc Mơ mang &lt;te href=851001&gt;&lt;color=#c79f49&gt;Giấc Mơ Nuốt Chửng&lt;/color&gt;&lt;/te&gt; và &lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mơ Trao Đổi&lt;/color&gt;&lt;/te&gt; có tỷ lệ xuất hiện cao hơn.</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7764,7 @@
       <c r="M108" t="inlineStr">
         <is>
           <t>Mục tiêu Giai đoạn khó đạt hơn rồi.
-Tacet Discord mang &lt;te href=851001&gt;&lt;color=#c79f49&gt;Dream of Devouring&lt;/color&gt;&lt;/te&gt; và &lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mộng Trao đổi&lt;/color&gt;&lt;/te&gt; sẽ xuất hiện nhiều hơn.
+Tacet Discord mang &lt;te href=851001&gt;&lt;color=#c79f49&gt;Giấc Mộng Nuốt Chửng&lt;/color&gt;&lt;/te&gt; và &lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mộng Trao Đổi&lt;/color&gt;&lt;/te&gt; sẽ xuất hiện nhiều hơn.
 Hãy bắt đầu với đạo cụ &lt;te href=851037&gt;&lt;color=#c79f49&gt;Mô Hình: Excarat&lt;/color&gt;&lt;/te&gt; và &lt;te href=851038&gt;&lt;color=#c79f49&gt;Tàu Hỏa Mộng Ảo&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Echo Giấc Mơ mang &lt;te href=851000&gt;&lt;color=#c79f49&gt;Giấc Mơ Phân Tầng&lt;/color&gt;&lt;/te&gt; và &lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; có tỷ lệ xuất hiện cao hơn.</t>
+          <t>Tiếng Vọng Giấc Mơ mang &lt;te href=851000&gt;&lt;color=#c79f49&gt;Giấc Mơ Phân Tầng&lt;/color&gt;&lt;/te&gt; và &lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; có tỷ lệ xuất hiện cao hơn.</t>
         </is>
       </c>
     </row>
@@ -7898,8 +7898,8 @@
       <c r="M110" t="inlineStr">
         <is>
           <t>Mục tiêu Giai đoạn khó đạt hơn rồi.
-Tacet Discord mang &lt;te href=851000&gt;&lt;color=#c79f49&gt;Giấc Mộng Gradation&lt;/color&gt;&lt;/te&gt; và &lt;te href=851003&gt;&lt;color=#c79f49&gt;Dream of Integration&lt;/color&gt;&lt;/te&gt; sẽ xuất hiện nhiều hơn.
-Hãy bắt đầu với đạo cụ &lt;te href=851039&gt;&lt;color=#c79f49&gt;Stamp Book&lt;/color&gt;&lt;/te&gt; và &lt;te href=851040&gt;&lt;color=#c79f49&gt;Mô Hình: Clang Bang&lt;/color&gt;&lt;/te&gt;.</t>
+Tacet Discord mang &lt;te href=851000&gt;&lt;color=#c79f49&gt;Giấc Mộng Phân Cấp&lt;/color&gt;&lt;/te&gt; và &lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mộng Hòa Nhập&lt;/color&gt;&lt;/te&gt; sẽ xuất hiện nhiều hơn.
+Hãy bắt đầu với đạo cụ &lt;te href=851039&gt;&lt;color=#c79f49&gt;Sổ Tem&lt;/color&gt;&lt;/te&gt; và &lt;te href=851040&gt;&lt;color=#c79f49&gt;Mô Hình: Clang Bang&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Resilience&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Lần đầu tiên Resonator này chịu đòn chí mạng trong Battle Stage, nó sẽ trụ lại thêm {0} giây trước khi bị hạ gục.</t>
+          <t>&lt;color=#e4c69b&gt;Kiên Cường&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Lần đầu tiên Cộng Hưởng Giả này chịu đòn chí mạng trong Giai Đoạn Chiến Đấu, nó sẽ trụ lại thêm {0} giây trước khi bị hạ gục.</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Nạp Năng&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Mỗi lần sử dụng Biến Hóa, bạn nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Năng Lượng.</t>
+          <t>&lt;color=#e4c69b&gt;Nạp Năng&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Mỗi lần sử dụng Biến Hóa, bạn nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm SapTag=0} Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Conversion&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Mỗi khi sử dụng Biến Đổi, bạn rút một lá bài và sau đó đặt một lá bài trên tay trở lại bộ bài.</t>
+          <t>&lt;color=#e4c69b&gt;Conversion&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Mỗi khi sử dụng Transform, bạn rút một lá bài và sau đó đặt một lá bài trên tay trở lại bộ bài.</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>&lt;color=#e4c69b&gt;Đa Dạng&lt;/color&gt; &lt;color=#fb6464&gt;(Unactivated)&lt;/color&gt; - Khi Đa Dạng được kích hoạt, Resonator này có thể được Điều Chỉnh bởi bất kỳ Resonator Thường nào mà không bị hạn chế.</t>
+          <t>&lt;color=#e4c69b&gt;Đa Dạng&lt;/color&gt; &lt;color=#fb6464&gt;(Chưa kích hoạt)&lt;/color&gt; - Khi Đa Dạng được kích hoạt, Cộng Hưởng Giả này có thể được Điều Chỉnh bởi bất kỳ Cộng Hưởng Giả Thường nào mà không bị hạn chế.</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Một tấm phiếu có họa tiết vòng đu quay, tượng trưng cho vinh quang đã mất của Dreamland. Bằng cách thu thập những tấm phiếu này, các Echoes hy vọng sẽ khôi phục lại nơi đây như thuở hoàng kim.</t>
+          <t>Một tấm phiếu có họa tiết vòng đu quay, tượng trưng cho vinh quang đã mất của Dreamland. Bằng cách thu thập những tấm phiếu này, các Echo hy vọng sẽ khôi phục lại nơi đây như thuở hoàng kim.</t>
         </is>
       </c>
     </row>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>&lt;te href=851005&gt;&lt;color=#c79f49&gt;Gradation&lt;/color&gt;&lt;/te&gt;: Gradation xảy ra mỗi {0} ngày và tăng tiến trình Gradation của các Echoes có thể Gradation (không bao gồm chính nó) cùng hàng lên {1}. Hiệu ứng này có thể được kích hoạt tối đa {2} lần mỗi ngày.</t>
+          <t>&lt;color=#c79f49&gt;Phân Tầng&lt;/color&gt;: Hiện tượng Phân Tầng xảy ra mỗi {0} ngày và tăng tiến trình Phân Tầng của các Echo có thể Phân Tầng (trừ chính nó) cùng hàng lên {1}. Hiệu ứng này có thể kích hoạt tối đa {2} lần mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>&lt;te href=851005&gt;&lt;color=#c79f49&gt;Gradation&lt;/color&gt;&lt;/te&gt;: Gradation diễn ra mỗi {0} ngày một lần và tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của các Echoes cùng hàng thêm {1}.</t>
+          <t>&lt;te href=851005&gt;&lt;color=#c79f49&gt;Gradation&lt;/color&gt;&lt;/te&gt;: Gradation diễn ra mỗi {0} ngày một lần và tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của các Echo cùng hàng thêm {1}.</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>&lt;te href=851005&gt;&lt;color=#c79f49&gt;Gradation&lt;/color&gt;&lt;/te&gt;: Gradation diễn ra mỗi {0} ngày một lần và tặng {1} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>&lt;te href=851005&gt;&lt;color=#c79f49&gt;Gradation&lt;/color&gt;&lt;/te&gt;: Gradation diễn ra mỗi {0} ngày một lần và tặng {1} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupon&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>&lt;te href=851005&gt;&lt;color=#c79f49&gt;Gradation&lt;/color&gt;&lt;/te&gt;: Gradation xảy ra mỗi {0} ngày và tạo ra một &lt;te href=851015&gt;&lt;color=#c79f49&gt;Dream Block: Gravel&lt;/color&gt;&lt;/te&gt; trên khối trống hiện tại.</t>
+          <t>&lt;color=#c79f49&gt;Phân Tầng&lt;/color&gt;: Hiện tượng Phân Tầng xảy ra mỗi {0} ngày và tạo ra một &lt;color=#c79f49&gt;Khối Mộng: Sỏi Đá&lt;/color&gt; trên ô trống hiện tại.</t>
         </is>
       </c>
     </row>
@@ -8809,7 +8809,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>&lt;te href=851005&gt;&lt;color=#c79f49&gt;Gradation&lt;/color&gt;&lt;/te&gt;: Gradation diễn ra mỗi {0} ngày một lần, tặng số &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; bằng số lượng &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystal&lt;/color&gt;&lt;/te&gt; hiện tại nhân {1}, và tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; theo số lượng Frequency Crystal hiện có.</t>
+          <t>&lt;te href=851005&gt;&lt;color=#c79f49&gt;Gradation&lt;/color&gt;&lt;/te&gt;: Gradation diễn ra mỗi {0} ngày một lần, tặng số &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupon&lt;/color&gt;&lt;/te&gt; bằng số lượng &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystal&lt;/color&gt;&lt;/te&gt; hiện tại nhân {1}, và tăng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; theo số lượng Frequency Crystal hiện có.</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>&lt;te href=851005&gt;&lt;color=#c79f49&gt;Gradation&lt;/color&gt;&lt;/te&gt;: Gradation xảy ra mỗi {0} ngày và tặng &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Couponss&lt;/color&gt;&lt;/te&gt; với số lượng bằng số &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystal&lt;/color&gt;&lt;/te&gt; sở hữu x{1}.</t>
+          <t>&lt;color=#c79f49&gt;Phân Tầng&lt;/color&gt;: Hiện tượng Phân Tầng xảy ra mỗi {0} ngày và tặng &lt;color=#c79f49&gt;Phiếu Mộng Điền&lt;/color&gt; bằng số &lt;color=#c79f49&gt;Tinh Thể Tần Số&lt;/color&gt; sở hữu x{1}.</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Hồi Âm này không thể bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;. Khi bất kỳ Hồi Âm &lt;te href=851055&gt;&lt;color=#c79f49&gt;kế cận&lt;/color&gt;&lt;/te&gt; bị Nuốt Chửng, có {0}% cơ hội tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;Prism&lt;/color&gt;&lt;/te&gt; {Cus:Sap,S=ngẫu nhiên P=ngẫu nhiên SapTag=1} trên ô trống.</t>
+          <t>Hồi Âm này không thể bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;. Khi bất kỳ Hồi Âm &lt;te href=851055&gt;&lt;color=#c79f49&gt;kế cận&lt;/color&gt;&lt;/te&gt; bị Nuốt Chửng, có {0}% cơ hội tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;Lăng Kính&lt;/color&gt;&lt;/te&gt; {Cus:Sap,S=ngẫu nhiên P=ngẫu nhiên SapTag=1} trên ô trống.</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Khi một &lt;te href=851055&gt;&lt;color=#c79f49&gt;Echoes Lân Cận&lt;/color&gt;&lt;/te&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;Prism&lt;/color&gt;&lt;/te&gt; bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;, có {0}% cơ hội tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; Echoes Prism ngẫu nhiên trên ô trống.</t>
+          <t>Khi một &lt;te href=851055&gt;&lt;color=#c79f49&gt;Echo Lân Cận&lt;/color&gt;&lt;/te&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;Prism&lt;/color&gt;&lt;/te&gt; bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;, có {0}% cơ hội tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; Echo Prism ngẫu nhiên trên ô trống.</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Khi một &lt;te href=851055&gt;&lt;color=#c79f49&gt;Echo Lân Cận&lt;/color&gt;&lt;/te&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;Prism&lt;/color&gt;&lt;/te&gt; bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;, nhận được {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Khi một &lt;te href=851055&gt;&lt;color=#c79f49&gt;Echo Lân Cận&lt;/color&gt;&lt;/te&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;Prism&lt;/color&gt;&lt;/te&gt; bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;, nhận được {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Dreamland&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Vào đầu mỗi ngày, có {0}% cơ hội tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=1} hiếm cấp xám có cùng Thuộc Tính Giấc Mơ trên ô trống.</t>
+          <t>Vào đầu mỗi ngày, có {0}% cơ hội tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echoes SapTag=1} hiếm cấp xám có cùng Thuộc Tính Giấc Mơ trên ô trống.</t>
         </is>
       </c>
     </row>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Hồi Âm này không thể bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;. Mỗi ngày, các Hồi Âm &lt;te href=851055&gt;&lt;color=#c79f49&gt;kế cận&lt;/color&gt;&lt;/te&gt; Dreamborne: Kerasaur sẽ được coi là kế cận lẫn nhau. Có {0}% cơ hội tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;Prism&lt;/color&gt;&lt;/te&gt; {Cus:Sap,S=ngẫu nhiên P=ngẫu nhiên SapTag=1} trên ô trống.</t>
+          <t>Hồi Âm này không thể bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;. Mỗi ngày, các Hồi Âm &lt;te href=851055&gt;&lt;color=#c79f49&gt;kế cận&lt;/color&gt;&lt;/te&gt; Dreamborne: Kerasaur sẽ được coi là kế cận lẫn nhau. Có {0}% cơ hội tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; &lt;te href=851050&gt;&lt;color=#c79f49&gt;Lăng Kính&lt;/color&gt;&lt;/te&gt; {Cus:Sap,S=ngẫu nhiên P=ngẫu nhiên SapTag=1} trên ô trống.</t>
         </is>
       </c>
     </row>
@@ -9265,8 +9265,8 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Mỗi Rover đều có một Mã Kế Hoạch độc nhất chứa cấu hình Quản Lý Echo. Những cấu hình này được cập nhật thủ công vào mã.
-Nhập Mã Kế Hoạch để áp dụng Kế Hoạch Quản Lý Echo của Rover khác. Tất cả các kế hoạch nhập vào sẽ được đặt ở trạng thái Kích Hoạt theo mặc định.</t>
+          <t>Mỗi Vận Mệnh Giả đều có một Mã Kế Hoạch độc nhất chứa cấu hình Quản Lý Echo. Những cấu hình này được cập nhật thủ công vào mã.
+Nhập Mã Kế Hoạch để áp dụng Kế Hoạch Quản Lý Echo của Vận Mệnh Giả khác. Tất cả các kế hoạch nhập vào sẽ được đặt ở trạng thái Kích Hoạt theo mặc định.</t>
         </is>
       </c>
     </row>
@@ -9338,12 +9338,12 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>[Quản Lý Echo]
-Bạn có thể tạo nhiều kế hoạch quản lý Echo dựa trên COST, Sonata Effect và Mainstats.
-Khi nhận được Echo mới, nó sẽ tự động bị khóa hoặc đánh dấu để loại bỏ theo các kế hoạch đã kích hoạt.
-Kế hoạch Quản Lý Echo không ảnh hưởng đến các Echo upgraded.
+          <t>[Quản Lý Tiếng Vọng]
+Bạn có thể tạo nhiều kế hoạch quản lý Tiếng Vọng dựa trên COST, Hiệu Ứng Sonata và Chỉ Số Chính.
+Khi nhận được Tiếng Vọng mới, nó sẽ tự động bị khóa hoặc đánh dấu để loại bỏ theo các kế hoạch đã kích hoạt.
+Kế hoạch Quản Lý Tiếng Vọng không ảnh hưởng đến các Tiếng Vọng đã nâng cấp.
 [Mẫu Có Sẵn, Chia Sẻ &amp; Nhập]
-Bạn có thể nhập các kế hoạch quản lý gợi ý qua tính năng Kế Hoạch Gợi Ý, hoặc nhập cấu hình của các Rover khác qua tính năng Chia Sẻ &amp; Nhập.
+Bạn có thể nhập các kế hoạch quản lý gợi ý qua tính năng Kế Hoạch Gợi Ý, hoặc nhập cấu hình của các Vận Mệnh Giả khác qua tính năng Chia Sẻ &amp; Nhập.
 Sau khi nhập, tất cả các kế hoạch cục bộ sẽ bị ghi đè và kích hoạt.
 Khi nhập kế hoạch chia sẻ bằng mã, nếu kế hoạch nhập vào chưa được cập nhật, hãy đợi một lúc rồi thử lại.</t>
         </is>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>&lt;te href=851007&gt;&lt;color=#c79f49&gt;Exchange&lt;/color&gt;&lt;/te&gt;: Sau {0} ngày, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;Remove&lt;/color&gt;&lt;/te&gt; bản thân như một &lt;te href=851013&gt;&lt;color=#c79f49&gt;Item of Exchange&lt;/color&gt;&lt;/te&gt;. Khi bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Devoured&lt;/color&gt;&lt;/te&gt; hoặc Exchange, có {2}% cơ hội tạo ra một &lt;te href=851061&gt;&lt;color=#c79f49&gt;Mourning Aix&lt;/color&gt;&lt;/te&gt; và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Couponss&lt;/color&gt;&lt;/te&gt; với số lượng bằng số &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupons&lt;/color&gt;&lt;/te&gt; hiện tại × {1}. Echo này không thể nhận được thông qua &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Trao Đổi: Sau {0} ngày, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;loại bỏ&lt;/color&gt;&lt;/te&gt; khỏi danh sách &lt;te href=851013&gt;&lt;color=#c79f49&gt;Vật Phẩm Trao Đổi&lt;/color&gt;&lt;/te&gt;. Khi bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt; hoặc Trao Đổi, có {2}% cơ hội tạo ra một &lt;te href=851061&gt;&lt;color=#c79f49&gt;Mourning Aix&lt;/color&gt;&lt;/te&gt; và nhận được &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Mộng Ảnh&lt;/color&gt;&lt;/te&gt; bằng số lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; hiện tại nhân {1}. Không thể nhận được Tiếng Vọng này qua &lt;te href=851012&gt;&lt;color=#c79f49&gt;Tuyển Mộ Tiếng Vọng&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>&lt;te href=851007&gt;&lt;color=#c79f49&gt;Exchange&lt;/color&gt;&lt;/te&gt;: Sau {0} ngày, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;Remove&lt;/color&gt;&lt;/te&gt; bản thân. Khi Echo này bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Devoured&lt;/color&gt;&lt;/te&gt; hoặc tự Remove, có {1}% cơ hội tạo ra một &lt;te href=851062&gt;&lt;color=#c79f49&gt;Dreamborne: Roseshroom&lt;/color&gt;&lt;/te&gt; và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Couponss&lt;/color&gt;&lt;/te&gt; với số lượng bằng sản lượng hiện tại của &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupons&lt;/color&gt;&lt;/te&gt; × {2}.</t>
+          <t>Trao Đổi: Sau {0} ngày, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;loại bỏ&lt;/color&gt;&lt;/te&gt;. Khi Tiếng Vọng này bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt; hoặc tự loại bỏ, có {1}% cơ hội tạo ra một &lt;te href=851062&gt;&lt;color=#c79f49&gt;Dreamborne: Roseshroom&lt;/color&gt;&lt;/te&gt; và nhận được &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Mộng Ảnh&lt;/color&gt;&lt;/te&gt; bằng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; hiện tại nhân {2}.</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>&lt;te href=851007&gt;&lt;color=#c79f49&gt;Exchange&lt;/color&gt;&lt;/te&gt;: Sau {0} ngày, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;Remove&lt;/color&gt;&lt;/te&gt; bản thân như một &lt;te href=851013&gt;&lt;color=#c79f49&gt;Item of Exchange&lt;/color&gt;&lt;/te&gt;. Echo này luôn xuất hiện trên cùng một ô. Khi được Exchange, có {1}% cơ hội tạo ra một &lt;te href=851061&gt;&lt;color=#c79f49&gt;Mourning Aix&lt;/color&gt;&lt;/te&gt; trên một ô trống. Echo này không thể nhận được thông qua &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Trao Đổi: Sau {0} ngày, tự &lt;te href=851041&gt;&lt;color=#c79f49&gt;loại bỏ&lt;/color&gt;&lt;/te&gt; khỏi danh sách &lt;te href=851013&gt;&lt;color=#c79f49&gt;Vật Phẩm Trao Đổi&lt;/color&gt;&lt;/te&gt;. Tiếng Vọng này luôn xuất hiện trên cùng một ô. Khi được Trao Đổi, có {1}% cơ hội tạo ra một &lt;te href=851061&gt;&lt;color=#c79f49&gt;Mourning Aix&lt;/color&gt;&lt;/te&gt; trên ô trống. Không thể nhận được Tiếng Vọng này qua &lt;te href=851012&gt;&lt;color=#c79f49&gt;Tuyển Mộ Tiếng Vọng&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Mỗi ngày, có {0}% cơ hội tạo ra &lt;te href=851013&gt;&lt;color=#c79f49&gt;Vật Phẩm Trao đổi&lt;/color&gt;&lt;/te&gt; trên một ô trống. Nếu đặt lên &lt;te href=851048&gt;&lt;color=#c79f49&gt;Ô Mộng: Hắc Diện Thạch&lt;/color&gt;&lt;/te&gt;, tỷ lệ tăng thêm {1}%.</t>
+          <t>Mỗi ngày, có {0}% cơ hội tạo ra &lt;te href=851013&gt;&lt;color=#c79f49&gt;Vật Phẩm Trao Đổi&lt;/color&gt;&lt;/te&gt; trên một ô trống. Nếu đặt lên &lt;te href=851048&gt;&lt;color=#c79f49&gt;Ô Mộng: Hắc Diện Thạch&lt;/color&gt;&lt;/te&gt;, tỷ lệ tăng thêm {1}%.</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Echo này luôn xuất hiện trên cùng một khối. Sau {0} ngày, nó sẽ &lt;te href=851041&gt;&lt;color=#c79f49&gt;tự biến mất&lt;/color&gt;&lt;/te&gt;, và có {1}% cơ hội tạo ra &lt;te href=851047&gt;&lt;color=#c79f49&gt;Roseshroom&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Echo này luôn xuất hiện trên cùng một khối. Sau {0} ngày, nó sẽ &lt;te href=851041&gt;&lt;color=#c79f49&gt;tự biến mất&lt;/color&gt;&lt;/te&gt;, và có {1}% cơ hội tạo ra &lt;te href=851047&gt;&lt;color=#c79f49&gt;Nấm Hồng&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Vào đầu mỗi ngày, hiệu ứng &lt;te href=851014&gt;&lt;color=#c79f49&gt;Bén Rễ&lt;/color&gt;&lt;/te&gt; sẽ được áp dụng lên các Echoes &lt;te href=851055&gt;&lt;color=#c79f49&gt;lân cận&lt;/color&gt;&lt;/te&gt; trong 1 ngày.</t>
+          <t>Vào đầu mỗi ngày, hiệu ứng &lt;te href=851014&gt;&lt;color=#c79f49&gt;Bén Rễ&lt;/color&gt;&lt;/te&gt; sẽ được áp dụng lên các Echo &lt;te href=851055&gt;&lt;color=#c79f49&gt;lân cận&lt;/color&gt;&lt;/te&gt; trong 1 ngày.</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Khi một Echo &lt;te href=851055&gt;&lt;color=#c79f49&gt;Lân Cận&lt;/color&gt;&lt;/te&gt; &lt;te href=851041&gt;&lt;color=#c79f49&gt;Tự Loại Bỏ&lt;/color&gt;&lt;/te&gt;, nhận được {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Khi một Echo &lt;te href=851055&gt;&lt;color=#c79f49&gt;Lân Cận&lt;/color&gt;&lt;/te&gt; &lt;te href=851041&gt;&lt;color=#c79f49&gt;Tự Loại Bỏ&lt;/color&gt;&lt;/te&gt;, nhận được {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Dreamland&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận Echo &lt;te href=851000&gt;&lt;color=#c79f49&gt;Dream of Gradation&lt;/color&gt;&lt;/te&gt; cấp xám hoặc lam. Bạn có thể chọn 1 đến 3 Echo để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
+          <t>Mở Hộp Giấc Mơ để nhận Tiếng Vọng &lt;te href=851000&gt;&lt;color=#c79f49&gt;Dream of Gradation&lt;/color&gt;&lt;/te&gt; cấp xám hoặc lam. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận Echo &lt;te href=851000&gt;&lt;color=#c79f49&gt;Dream of Gradation&lt;/color&gt;&lt;/te&gt; cấp xám hoặc lam, với xác suất nhỏ nhận được Echo cấp tím. Bạn có thể chọn 1 đến 3 Echo để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
+          <t>Mở Hộp Giấc Mơ để nhận Tiếng Vọng &lt;te href=851000&gt;&lt;color=#c79f49&gt;Dream of Gradation&lt;/color&gt;&lt;/te&gt; cấp xám hoặc lam, với xác suất nhỏ nhận được Tiếng Vọng cấp tím. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
         </is>
       </c>
     </row>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận Echo &lt;te href=851000&gt;&lt;color=#c79f49&gt;Dream of Gradation&lt;/color&gt;&lt;/te&gt; cấp xám, lam hoặc tím, với xác suất nhỏ nhận được Echo cấp vàng. Bạn có thể chọn 1 đến 3 Echo để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
+          <t>Mở Hộp Giấc Mơ để nhận Tiếng Vọng &lt;te href=851000&gt;&lt;color=#c79f49&gt;Dream of Gradation&lt;/color&gt;&lt;/te&gt; cấp xám, lam hoặc tím, với xác suất nhỏ nhận được Tiếng Vọng cấp vàng. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận Echo &lt;te href=851000&gt;&lt;color=#c79f49&gt;Dream of Gradation&lt;/color&gt;&lt;/te&gt; với mọi cấp độ hiếm, đảm bảo có ít nhất một Echo cấp vàng. Bạn có thể chọn 1 đến 3 Echo để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
+          <t>Mở Hộp Giấc Mơ để nhận Tiếng Vọng &lt;te href=851000&gt;&lt;color=#c79f49&gt;Dream of Gradation&lt;/color&gt;&lt;/te&gt; với mọi cấp độ hiếm, đảm bảo có ít nhất một Tiếng Vọng cấp vàng. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận Echo &lt;te href=851001&gt;&lt;color=#c79f49&gt;Dream of Devouring&lt;/color&gt;&lt;/te&gt; cấp xám hoặc lam. Bạn có thể chọn 1 đến 3 Echo để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
+          <t>Mở Hộp Giấc Mơ để nhận Tiếng Vọng &lt;te href=851001&gt;&lt;color=#c79f49&gt;Dream of Devouring&lt;/color&gt;&lt;/te&gt; cấp xám hoặc lam. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
         </is>
       </c>
     </row>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận Echo &lt;te href=851001&gt;&lt;color=#c79f49&gt;Dream of Devouring&lt;/color&gt;&lt;/te&gt; cấp xám hoặc lam, với xác suất nhỏ nhận được Echo cấp tím. Bạn có thể chọn 1 đến 3 Echo để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
+          <t>Mở Hộp Giấc Mơ để nhận Tiếng Vọng &lt;te href=851001&gt;&lt;color=#c79f49&gt;Dream of Devouring&lt;/color&gt;&lt;/te&gt; cấp xám hoặc lam, với xác suất nhỏ nhận được Tiếng Vọng cấp tím. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận Echo &lt;te href=851001&gt;&lt;color=#c79f49&gt;Dream of Devouring&lt;/color&gt;&lt;/te&gt; cấp xám, lam hoặc tím, với xác suất nhỏ nhận được Echo cấp vàng. Bạn có thể chọn 1 đến 3 Echo để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
+          <t>Mở Hộp Giấc Mơ để nhận Tiếng Vọng &lt;te href=851001&gt;&lt;color=#c79f49&gt;Dream of Devouring&lt;/color&gt;&lt;/te&gt; cấp xám, lam hoặc tím, với xác suất nhỏ nhận được Tiếng Vọng cấp vàng. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận Echo &lt;te href=851001&gt;&lt;color=#c79f49&gt;Dream of Devouring&lt;/color&gt;&lt;/te&gt; với mọi cấp độ hiếm, đảm bảo có ít nhất một Echo cấp vàng. Bạn có thể chọn 1 đến 3 Echo để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
+          <t>Mở Hộp Giấc Mơ để nhận Tiếng Vọng &lt;te href=851001&gt;&lt;color=#c79f49&gt;Dream of Devouring&lt;/color&gt;&lt;/te&gt; với mọi cấp độ hiếm, đảm bảo có ít nhất một Tiếng Vọng cấp vàng. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
         </is>
       </c>
     </row>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận được Echo &lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mơ Trao đổi&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám hoặc Lam. Bạn có thể chọn 1 đến 3 Echo để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
+          <t>Mở Hộp Giấc Mơ để nhận được Tiếng Vọng &lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mơ Trao Đổi&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám hoặc Lam. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận được Echo &lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mơ Trao đổi&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám hoặc Lam, và có xác suất nhỏ nhận được Echo cấp Tím. Bạn có thể chọn 1 đến 3 Echo để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
+          <t>Mở Hộp Giấc Mơ để nhận được Tiếng Vọng &lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mơ Trao Đổi&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám hoặc Lam, và có xác suất nhỏ nhận được Tiếng Vọng cấp Tím. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận được Echo &lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mơ Trao đổi&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám, Lam hoặc Tím, và có xác suất nhỏ nhận được Echo cấp Vàng. Bạn có thể chọn 1 đến 3 Echo để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
+          <t>Mở Hộp Giấc Mơ để nhận được Tiếng Vọng &lt;te href=851002&gt;&lt;color=#c79f49&gt;Giấc Mơ Trao Đổi&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám, Lam hoặc Tím, và có xác suất nhỏ nhận được Tiếng Vọng cấp Vàng. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận Echo &lt;te href=851002&gt;&lt;color=#c79f49&gt;Dream of Exchange&lt;/color&gt;&lt;/te&gt; với mọi cấp độ hiếm, đảm bảo có ít nhất một Echo cấp vàng. Bạn có thể chọn 1 đến 3 Echo để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
+          <t>Mở Hộp Giấc Mơ để nhận Tiếng Vọng &lt;te href=851002&gt;&lt;color=#c79f49&gt;Dream of Exchange&lt;/color&gt;&lt;/te&gt; với mọi cấp độ hiếm, đảm bảo có ít nhất một Tiếng Vọng cấp vàng. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi vào chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động đứng ngoài).</t>
         </is>
       </c>
     </row>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận được Echo &lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám hoặc Lam. Bạn có thể chọn 1 đến 3 Echo để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
+          <t>Mở Hộp Giấc Mơ để nhận được Tiếng Vọng &lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám hoặc Lam. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
         </is>
       </c>
     </row>
@@ -10710,7 +10710,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận được Echo &lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám hoặc Lam, và có xác suất nhỏ nhận được Echo cấp Tím. Bạn có thể chọn 1 đến 3 Echo để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
+          <t>Mở Hộp Giấc Mơ để nhận được Tiếng Vọng &lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám hoặc Lam, và có xác suất nhỏ nhận được Tiếng Vọng cấp Tím. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận được Echo &lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám, Lam hoặc Tím, và có xác suất nhỏ nhận được Echo cấp Vàng. Bạn có thể chọn 1 đến 3 Echo để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
+          <t>Mở Hộp Giấc Mơ để nhận được Tiếng Vọng &lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; hiếm cấp Xám, Lam hoặc Tím, và có xác suất nhỏ nhận được Tiếng Vọng cấp Vàng. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Mở Hộp Giấc Mơ để nhận được Echo &lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; với mọi cấp hiếm, và chắc chắn sẽ có Echo cấp Vàng. Bạn có thể chọn 1 đến 3 Echo để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
+          <t>Mở Hộp Giấc Mơ để nhận được Tiếng Vọng &lt;te href=851003&gt;&lt;color=#c79f49&gt;Giấc Mơ Hòa Nhập&lt;/color&gt;&lt;/te&gt; với mọi cấp hiếm, và chắc chắn sẽ có Tiếng Vọng cấp Vàng. Bạn có thể chọn 1 đến 3 Tiếng Vọng để triệu hồi lên chiến trường (nếu chiến trường đã đầy, chúng sẽ tự động được đặt ngoài chiến trường).</t>
         </is>
       </c>
     </row>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Khi Resonator &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hòa Nhập&lt;/color&gt;&lt;/te&gt; Echo này, nhận được 1 &lt;te href=851044&gt;&lt;color=#c79f49&gt;Crownless&lt;/color&gt;&lt;/te&gt;, cùng {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Couponss&lt;/color&gt;&lt;/te&gt; và {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh thể Tần số&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Khi Cộng Hưởng Giả &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hòa Nhập&lt;/color&gt;&lt;/te&gt; Echo này, nhận được 1 &lt;te href=851044&gt;&lt;color=#c79f49&gt;Crownless&lt;/color&gt;&lt;/te&gt;, cùng {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; và {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh thể Tần số&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Khi Resonator &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hòa Nhập&lt;/color&gt;&lt;/te&gt; Echo này, nhận được 1 &lt;te href=851043&gt;&lt;color=#c79f49&gt;Rage Against the Statue&lt;/color&gt;&lt;/te&gt;, cùng {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Couponss&lt;/color&gt;&lt;/te&gt; và {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh thể Tần số&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Khi Cộng Hưởng Giả &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hòa Nhập&lt;/color&gt;&lt;/te&gt; Echo này, nhận được 1 &lt;te href=851043&gt;&lt;color=#c79f49&gt;Rage Against the Statue&lt;/color&gt;&lt;/te&gt;, cùng {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; và {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh thể Tần số&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11035,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Khi Resonator &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hòa Nhập&lt;/color&gt;&lt;/te&gt; Echo này, nhận được 1 &lt;te href=851042&gt;&lt;color=#c79f49&gt;Stonewall Bracer&lt;/color&gt;&lt;/te&gt;, cùng {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Couponss&lt;/color&gt;&lt;/te&gt; và {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh thể Tần số&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Khi Cộng Hưởng Giả &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hòa Nhập&lt;/color&gt;&lt;/te&gt; Echo này, nhận được 1 &lt;te href=851042&gt;&lt;color=#c79f49&gt;Stonewall Bracer&lt;/color&gt;&lt;/te&gt;, cùng {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; và {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh thể Tần số&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -11100,7 +11100,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Khi các Echoes cùng hàng trải qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt;, có {0}% cơ hội tạo ra một &lt;te href=851045&gt;&lt;color=#c79f49&gt;Hình Thái Basic&lt;/color&gt;&lt;/te&gt; của Echoes đang &lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Khi các Echo cùng hàng trải qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hợp Nhất&lt;/color&gt;&lt;/te&gt;, có {0}% cơ hội tạo ra một &lt;te href=851045&gt;&lt;color=#c79f49&gt;Hình Thái Cơ Bản&lt;/color&gt;&lt;/te&gt; của Echo đang &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hợp Nhất&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -11165,7 +11165,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Khi các Echoes cùng hàng trải qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt;, nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; bằng với sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của Echoes này.</t>
+          <t>Khi các Echo cùng hàng trải qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hợp Nhất&lt;/color&gt;&lt;/te&gt;, nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Giấc Mơ&lt;/color&gt;&lt;/te&gt; bằng với sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của Echo này.</t>
         </is>
       </c>
     </row>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Khi các Echoes cùng hàng trải qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt;, tạo ra 1 &lt;te href=851016&gt;&lt;color=#c79f49&gt;Dream Block: Mảnh Băng&lt;/color&gt;&lt;/te&gt; trên ô trống.</t>
+          <t>Khi các Echo cùng hàng trải qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hợp Nhất&lt;/color&gt;&lt;/te&gt;, tạo ra 1 &lt;te href=851016&gt;&lt;color=#c79f49&gt;Khối Giấc Mơ: Mảnh Băng&lt;/color&gt;&lt;/te&gt; trên ô trống.</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Khi các Echoes cùng hàng trải qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt;, nhận {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Khi các Echo cùng hàng trải qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hợp Nhất&lt;/color&gt;&lt;/te&gt;, nhận {0} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Giấc Mơ&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>&lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt;: Khi có {0} Echoes cùng Attribute Giấc Mơ và độ hiếm với Echoes này trên cùng một hàng, Integration chúng thành 1 &lt;te href=851044&gt;&lt;color=#c79f49&gt;Crownless&lt;/color&gt;&lt;/te&gt; và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; bằng {1} + tổng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; x{2}. Sản lượng Daily Coupon của Echoes mới sẽ bằng tổng sản lượng Daily Coupon của tất cả các Echoes đã Integration.</t>
+          <t>&lt;te href=851008&gt;&lt;color=#c79f49&gt;Hợp Nhất&lt;/color&gt;&lt;/te&gt;: Khi có {0} Echo cùng Thuộc tính Giấc Mơ và độ hiếm với Echo này trên cùng một hàng, Hợp Nhất chúng thành 1 &lt;te href=851044&gt;&lt;color=#c79f49&gt;Crownless&lt;/color&gt;&lt;/te&gt; và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Giấc Mơ&lt;/color&gt;&lt;/te&gt; bằng {1} + tổng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; x{2}. Sản lượng Phiếu Hằng Ngày của Echo mới sẽ bằng tổng sản lượng Phiếu Hằng Ngày của tất cả các Echo đã Hợp Nhất.</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11425,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>&lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt;: Khi có {0} Echoes cùng Attribute Giấc Mơ và độ hiếm với Echoes này trên cùng một hàng, Integration chúng thành 1 &lt;te href=851044&gt;&lt;color=#c79f49&gt;Crownless&lt;/color&gt;&lt;/te&gt; và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; bằng {1} + tổng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; x{2}.</t>
+          <t>&lt;te href=851008&gt;&lt;color=#c79f49&gt;Hợp Nhất&lt;/color&gt;&lt;/te&gt;: Khi có {0} Echo cùng Thuộc tính Giấc Mơ và độ hiếm với Echo này trên cùng một hàng, Hợp Nhất chúng thành 1 &lt;te href=851044&gt;&lt;color=#c79f49&gt;Crownless&lt;/color&gt;&lt;/te&gt; và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Giấc Mơ&lt;/color&gt;&lt;/te&gt; bằng {1} + tổng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; x{2}.</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>&lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt;: Khi có {0} Echoes cùng Attribute Giấc Mơ và độ hiếm với Echoes này trên cùng một hàng, Integration chúng thành 1 &lt;te href=851043&gt;&lt;color=#c79f49&gt;Rage Against the Statue&lt;/color&gt;&lt;/te&gt; và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; bằng {1} + tổng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; x{2}.</t>
+          <t>&lt;te href=851008&gt;&lt;color=#c79f49&gt;Hợp Nhất&lt;/color&gt;&lt;/te&gt;: Khi có {0} Echo cùng Thuộc tính Giấc Mơ và độ hiếm với Echo này trên cùng một hàng, Hợp Nhất chúng thành 1 &lt;te href=851043&gt;&lt;color=#c79f49&gt;Rage Against the Statue&lt;/color&gt;&lt;/te&gt; và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Giấc Mơ&lt;/color&gt;&lt;/te&gt; bằng {1} + tổng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; x{2}.</t>
         </is>
       </c>
     </row>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>&lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt;: Khi có {0} Echoes cùng Attribute Giấc Mơ và độ hiếm với Echoes này trên cùng một hàng, Integration chúng thành 1 &lt;te href=851042&gt;&lt;color=#c79f49&gt;Stonewall Bracer&lt;/color&gt;&lt;/te&gt; và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; bằng {1} + tổng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; x{2}.</t>
+          <t>&lt;te href=851008&gt;&lt;color=#c79f49&gt;Hợp Nhất&lt;/color&gt;&lt;/te&gt;: Khi có {0} Echo cùng Thuộc tính Giấc Mơ và độ hiếm với Echo này trên cùng một hàng, Hợp Nhất chúng thành 1 &lt;te href=851042&gt;&lt;color=#c79f49&gt;Stonewall Bracer&lt;/color&gt;&lt;/te&gt; và nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Giấc Mơ&lt;/color&gt;&lt;/te&gt; bằng {1} + tổng sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; x{2}.</t>
         </is>
       </c>
     </row>
@@ -11621,8 +11621,8 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Sản phẩm của một Quả Cầu Sonoro sụp đổ, xuất hiện khắp nơi trên thế giới. Nó ghi lại những ký ức nguyên vẹn của quá khứ.
-Dùng Grapple để móc và tiếp cận nhanh các Rương Sonance ở Septimont. Những Plushie Echoes ở Dãy Border Mountains đang thu thập chúng—có lẽ ghé thăm sẽ khám phá thêm điều gì đó.</t>
+          <t>Sản phẩm của một Sonoro Sphere sụp đổ, xuất hiện khắp nơi trên thế giới. Nó ghi lại những ký ức nguyên vẹn của quá khứ.
+Dùng Móc Câu để móc và tiếp cận nhanh các Rương Sonance ở Septimont. Những Plushie Echo ở Dãy Núi Biên Giới đang thu thập chúng—có lẽ ghé thăm sẽ khám phá thêm điều gì đó.</t>
         </is>
       </c>
     </row>
@@ -11757,10 +11757,10 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Biểu đồ dạng sóng của Resonators Phrolova cho thấy dao động hình răng cưa và kim nhọn. Mô hình miền Thời gian thường xuyên xuất hiện hoạt động dữ dội và hỗn loạn. Trong quá trình thử nghiệm, dữ liệu miền Thời gian cho thấy biến dạng đáng kể, và giá trị đỉnh vẫn chưa xác định được.
+          <t>Biểu đồ dạng sóng của Resonator Phrolova cho thấy dao động hình răng cưa và kim nhọn. Mô hình miền Thời gian thường xuyên xuất hiện hoạt động dữ dội và hỗn loạn. Trong quá trình thử nghiệm, dữ liệu miền Thời gian cho thấy biến dạng đáng kể, và giá trị đỉnh vẫn chưa xác định được.
 Mức độ Nguy hiểm Cộng hưởng: Cực thấp.
-Tần số của Resonators Phrolova thể hiện sự bất ổn cực kỳ thấp. Ghi nhận cô có tiền sử Tăng tốc Quá mức.
-Tuy nhiên, cô luôn kiểm soát tốt tình trạng Tăng tốc Quá mức của mình, cho thấy tiềm năng khám phá phương pháp ổn định và kéo dài trạng thái Tăng tốc Quá mức ở Resonators thông thường bằng cách tận dụng sự ổn định tinh thần này.</t>
+Tần số của Resonator Phrolova thể hiện sự bất ổn cực kỳ thấp. Ghi nhận cô có tiền sử Tăng tốc Quá mức.
+Tuy nhiên, cô luôn kiểm soát tốt tình trạng Tăng tốc Quá mức của mình, cho thấy tiềm năng khám phá phương pháp ổn định và kéo dài trạng thái Tăng tốc Quá mức ở các Resonator thông thường bằng cách tận dụng sự ổn định tinh thần này.</t>
         </is>
       </c>
     </row>
@@ -11825,7 +11825,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Dodget mặt cô bình thản, nhưng đôi tay lại vung vẩy cuồng nhiệt, phóng đại từng cử chỉ, quét qua từng bản nhạc. Lý trí chao đảo, rồi bị xé nát, chìm nghỉm trong cơn bão cảm xúc. Những nốt nhạc vỡ vụn, rồi tái sinh méo mó, biến dạng thành âm thanh quái dị.</t>
+          <t>Nét mặt cô bình thản, nhưng đôi tay lại vung vẩy cuồng nhiệt, phóng đại từng cử chỉ, quét qua từng bản nhạc. Lý trí chao đảo, rồi bị xé nát, chìm nghỉm trong cơn bão cảm xúc. Những nốt nhạc vỡ vụn, rồi tái sinh méo mó, biến dạng thành âm thanh quái dị.</t>
         </is>
       </c>
     </row>
@@ -12035,7 +12035,7 @@
       <c r="M173" t="inlineStr">
         <is>
           <t>Khán giả chìm đắm trong màn trình diễn. Người thì ngồi như hóa đá, kẻ thì run rẩy, lắc lư như lau sậy trong cơn bão. Trong bóng tối, vô số ánh mắt dán chặt vào bóng dáng cô độc, mảnh mai mà mạnh mẽ ấy, đôi mắt họ như bị thôi miên bởi nhịp đưa tay lên xuống của cô, như những nốt nhạc lạc loài trong khúc bi ca cuồng loạn.
-Giai điệu sôi sục của presto châm ngòi cho ngọn lửa khát khao trong lồng ngực họ. Những cảm xúc bị kìm Dodgen bùng lên. Không kiểm soát. Không giam cầm. Họ nghẹn ngào trong đỉnh điểm điên loạn của bản nhạc, bị kéo đến bờ vực lý trí cùng cô. Trên mép vực thẳm thăm thẳm, họ khao khát những đóa hoa hủy diệt và tái sinh.
+Giai điệu sôi sục của presto châm ngòi cho ngọn lửa khát khao trong lồng ngực họ. Những cảm xúc bị kìm nén bùng lên. Không kiểm soát. Không giam cầm. Họ nghẹn ngào trong đỉnh điểm điên loạn của bản nhạc, bị kéo đến bờ vực lý trí cùng cô. Trên mép vực thẳm thăm thẳm, họ khao khát những đóa hoa hủy diệt và tái sinh.
 Thế nhưng, ngay trước khi bước nhảy ấy được thực hiện, người chỉ huy bất ngờ dừng tay dưới ánh đèn sân khấu. Âm nhạc chấm dứt với sự kết thúc đột ngột, gần như tàn nhẫn.
 Cô đứng bất động như tượng, lồng ngực phập phồng. Sợi dây lý trí cuối cùng níu giữ cô đã đứt, tan biến vào biển cảm xúc nơi cô trôi dạt một mình. Ánh mắt cô hướng lên trần nhà, không một lần hạ xuống để nhìn khán giả dưới kia.
 Đó có phải là kết thúc?
@@ -12191,7 +12191,7 @@
         <is>
           <t>Nàng ngước nhìn bầu trời. Nó xanh biếc. Nhưng nàng nhớ rõ nó từng đỏ sẫm như máu.
 Nàng trèo qua hàng rào, lên đường tìm kiếm, trong khi những giọng nói vang vọng xung quanh níu giữ nàng lại. "Con chỉ nằm mơ thôi," họ nói.
-Vậy ra tất cả chỉ là một giấc mơ... Like những đám mây trôi lơ lửng trên cao, chiếc váy trắng của nàng bay phấp phới trên thảo nguyên, hướng về thị trấn. Mặt trời vẫn mọc như thường lệ, và thị trấn vẫn lặp lại những làn khói từ ống khói cùng tiếng cười ngày qua ngày... Ngày qua ngày, sự tầm thường ấy ngấm vào nàng, cùng với cảm giác ngột ngạt này. Âm nhạc của nàng không còn tiến triển, và suy nghĩ của mọi người cũng không còn thay đổi. Ngày qua ngày...
+Vậy ra tất cả chỉ là một giấc mơ... Giống như những đám mây trôi lơ lửng trên cao, chiếc váy trắng của nàng bay phấp phới trên thảo nguyên, hướng về thị trấn. Mặt trời vẫn mọc như thường lệ, và thị trấn vẫn lặp lại những làn khói từ ống khói cùng tiếng cười ngày qua ngày... Ngày qua ngày, sự tầm thường ấy ngấm vào nàng, cùng với cảm giác ngột ngạt này. Âm nhạc của nàng không còn tiến triển, và suy nghĩ của mọi người cũng không còn thay đổi. Ngày qua ngày...
 Đã bao lâu rồi không ai dám bước ra khỏi rìa thị trấn? Thức ăn từ đâu mà có? Làm sao họ có thể cung cấp vô tận những nhu yếu phẩm hàng ngày? Đó là những câu hỏi nàng tự hỏi khi bước đi xa hơn.
 Tới gần rìa thị trấn, nàng thấy một bóng người đỏ thẫm đứng trước làn sương mờ ảo. Nó đã đợi rất lâu, như thể đoán trước được nàng sẽ đến.
 Trực giác mách bảo nàng tránh xa, nhưng vì lý do nào đó, nàng vẫn đưa tay đặt vào lòng bàn tay nó, chỉ để nắm được một nắm máu.
@@ -13439,7 +13439,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Sau 1 ngày, sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của tất cả Echoes trên chiến trường tăng thêm {0}. Hiệu ứng chỉ có thể kích hoạt một lần.</t>
+          <t>Sau 1 ngày, sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của tất cả Echo trên chiến trường tăng thêm {0}. Hiệu ứng chỉ có thể kích hoạt một lần.</t>
         </is>
       </c>
     </row>
@@ -13504,7 +13504,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Sau 1 ngày, kích hoạt &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=0} thuộc một trong các Thuộc Tính Giấc Mơ ngẫu nhiên trên ô trống trong Giai Đoạn này. Hiệu ứng chỉ có thể kích hoạt một lần.</t>
+          <t>Sau 1 ngày, kích hoạt &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echoes SapTag=0} thuộc một trong các Thuộc Tính Giấc Mơ ngẫu nhiên trên ô trống trong Giai Đoạn này. Hiệu ứng chỉ có thể kích hoạt một lần.</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Mỗi khi nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=0} (không tính từ &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echoes Recruitment&lt;/color&gt;&lt;/te&gt;, Shop hoặc Phantasma Blessing), nhận {1} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Couponss&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Mỗi khi nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echo SapTag=0} (không tính từ &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt;, Shop hoặc Phantasma Blessing), nhận {1} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Mỗi khi nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=0} (không tính từ &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echoes Recruitment&lt;/color&gt;&lt;/te&gt;, Shop hoặc Phantasma Blessing), nhận {1} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Couponss&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Mỗi khi nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echo SapTag=0} (không tính từ &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt;, Shop hoặc Phantasma Blessing), nhận {1} &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -13699,7 +13699,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Mỗi khi nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=0} (không tính từ &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echoes Recruitment&lt;/color&gt;&lt;/te&gt;, Shop hoặc Phantasma Blessing), nhận {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystals&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Mỗi khi nhận được &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echo SapTag=0} (không tính từ &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt;, Shop hoặc Phantasma Blessing), nhận {1} &lt;te href=851011&gt;&lt;color=#c79f49&gt;Frequency Crystals&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -13764,7 +13764,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; tương đương số lượng &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh thể Tần số&lt;/color&gt;&lt;/te&gt; trong mỗi Giai đoạn.</t>
+          <t>Nhận &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupon&lt;/color&gt;&lt;/te&gt; tương đương số lượng &lt;te href=851011&gt;&lt;color=#c79f49&gt;Tinh thể Tần số&lt;/color&gt;&lt;/te&gt; trong mỗi Giai đoạn.</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=1} thuộc một trong các Thuộc Tính Giấc Mơ kích hoạt trong Giai Đoạn này trên khối trống sau mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=0}.</t>
+          <t>Tạo ra &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echoes SapTag=1} thuộc một trong các Thuộc Tính Giấc Mơ kích hoạt trong Giai Đoạn này trên khối trống sau mỗi &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=ngày P=ngày SapTag=0}.</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Có {0}% xác suất nhận thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=1} trong &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echoes Recruitment&lt;/color&gt;&lt;/te&gt;.</t>
+          <t>Có {0}% xác suất nhận thêm &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echoes SapTag=1} trong &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt;.</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Nhận thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; lần làm mới &lt;te href=851012&gt;&lt;color=#c79f49&gt;Echo Recruitment&lt;/color&gt;&lt;/te&gt; miễn phí {Cus:Sap,S=cơ hội P=cơ hội SapTag=0} bắt đầu từ giai đoạn tiếp theo.</t>
+          <t>Nhận thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; lượt &lt;te href=851012&gt;&lt;color=#c79f49&gt;làm mới Echo Tuyển Dụng&lt;/color&gt;&lt;/te&gt; miễn phí &lt;Cus:Sap,S=từ P=từ SapTag=0&gt; giai đoạn tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Sau 1 ngày, kích hoạt &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=0} thuộc một trong các Thuộc Tính Giấc Mơ ngẫu nhiên trên ô trống trong Giai Đoạn này. Hiệu ứng chỉ có thể kích hoạt một lần.</t>
+          <t>Sau 1 ngày, kích hoạt &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echoes SapTag=0} thuộc một trong các Thuộc Tính Giấc Mơ ngẫu nhiên trên ô trống trong Giai Đoạn này. Hiệu ứng chỉ có thể kích hoạt một lần.</t>
         </is>
       </c>
     </row>
@@ -14089,7 +14089,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Sau 1 ngày, tiến trình &lt;te href=851005&gt;&lt;color=#c79f49&gt;Độ Đậm Nhạt&lt;/color&gt;&lt;/te&gt; của tất cả Echoes trên chiến trường tăng thêm {0}. Hiệu ứng chỉ có thể kích hoạt một lần.</t>
+          <t>Sau 1 ngày, tiến trình &lt;te href=851005&gt;&lt;color=#c79f49&gt;Độ Đậm Nhạt&lt;/color&gt;&lt;/te&gt; của tất cả Echo trên chiến trường tăng thêm {0}. Hiệu ứng chỉ có thể kích hoạt một lần.</t>
         </is>
       </c>
     </row>
@@ -14219,7 +14219,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Khi một Echo trải qua &lt;te href=851005&gt;&lt;color=#c79f49&gt;Tiến Hóa&lt;/color&gt;&lt;/te&gt;, tiến trình &lt;te href=851005&gt;&lt;color=#c79f49&gt;Tiến Hóa&lt;/color&gt;&lt;/te&gt; của nó sẽ tăng thêm {0}.</t>
+          <t>Khi một Tổ Tacet trải qua &lt;te href=851005&gt;&lt;color=#c79f49&gt;Tiến Hóa&lt;/color&gt;&lt;/te&gt;, tiến trình &lt;te href=851005&gt;&lt;color=#c79f49&gt;Tiến Hóa&lt;/color&gt;&lt;/te&gt; của nó sẽ tăng thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Tiếng vọng có khả năng &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt; có {0}% cơ hội sử dụng thêm kỹ năng &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1} mỗi ngày.</t>
+          <t>Echo có khả năng &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt; có {0}% cơ hội sử dụng thêm kỹ năng &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=1} mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của Echo trên Dream Block này tạm thời tăng thêm {0}. Phần thưởng sẽ bị hủy khi nó rời khỏi Dream Block này.</t>
+          <t>Sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của Echo trên Khối Mộng này tạm thời tăng thêm {0}. Phần thưởng sẽ bị hủy khi nó rời khỏi Khối Mộng này.</t>
         </is>
       </c>
     </row>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Khi sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; Echoes của Dream Block này tăng lên, nó sẽ tăng thêm {0}. Chỉ kích hoạt một lần mỗi ngày.</t>
+          <t>Khi sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; Echoes của Khối Giấc Mơ này tăng lên, nó sẽ tăng thêm {0}. Chỉ kích hoạt một lần mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Khi một Echo hiếm cấp xám hoặc xanh bị &lt;te href=851041&gt;&lt;color=#c79f49&gt;Loại Bỏ&lt;/color&gt;&lt;/te&gt; trên Dream Block này, có {0}% cơ hội tạo ra một &lt;te href=851045&gt;&lt;color=#c79f49&gt;Hình Thái Basic&lt;/color&gt;&lt;/te&gt; thay thế.</t>
+          <t>Khi một Echo hiếm cấp xám hoặc xanh bị &lt;te href=851041&gt;&lt;color=#c79f49&gt;Loại Bỏ&lt;/color&gt;&lt;/te&gt; trên Khối Mộng này, có {0}% cơ hội tạo ra một &lt;te href=851045&gt;&lt;color=#c79f49&gt;Hình Thái Cơ Bản&lt;/color&gt;&lt;/te&gt; thay thế.</t>
         </is>
       </c>
     </row>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; của Echo trên Dream Block này tạm thời tăng thêm {0}. Phần thưởng sẽ bị hủy khi nó rời khỏi Dream Block này.</t>
+          <t>Sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; của Echo trên Khối Mộng này tạm thời tăng thêm {0}. Phần thưởng sẽ bị hủy khi nó rời khỏi Khối Mộng này.</t>
         </is>
       </c>
     </row>
@@ -14674,7 +14674,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Có {0}% xác suất biến đổi &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=Echoes P=Echoes SapTag=1} liền kề thành một Echoes hiếm hơn cùng thuộc tính Giấc Mơ.</t>
+          <t>Có {0}% xác suất biến đổi &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echoes SapTag=1} liền kề thành một Echo hiếm hơn cùng thuộc tính Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Khi bị đánh bại, Discord này giải phóng Ô Nhiễm Tần Số tại chỗ. Các ô bị ô nhiễm không thể triển khai Chiến Cỗ Máy, và các Chiến Cỗ Máy đang hoạt động trên đó sẽ bị vô hiệu hóa.</t>
+          <t>Khi bị đánh bại, Tacet Discord này giải phóng Ô Nhiễm Tần Số tại chỗ. Các ô bị ô nhiễm không thể triển khai Chiến Cỗ Máy, và các Chiến Cỗ Máy đang hoạt động trên đó sẽ bị vô hiệu hóa.</t>
         </is>
       </c>
     </row>
@@ -14807,10 +14807,10 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Domain - Barrier
-Discords trong phạm vi nhất định sẽ nhận được Shield. Khi được bảo vệ bởi Shield, chúng miễn nhiễm với trạng thái Chậm.
+          <t>Tổ Tacet - Rào Chắn
+Các Tacet Discord trong phạm vi nhất định sẽ nhận được Khiên. Khi được bảo vệ bởi Khiên, chúng miễn nhiễm với trạng thái Chậm.
 Thích Nghi
-Khi bị ảnh hưởng bởi Tê Liệt/Đóng Băng/Mất Phương Hướng, Discord này sẽ miễn nhiễm với các hiệu ứng suy yếu đó trong một khoảng thời gian ngắn.</t>
+Khi bị ảnh hưởng bởi Tê Liệt/Đóng Băng/Mất Phương Hướng, Tacet Discord này sẽ miễn nhiễm với các hiệu ứng suy yếu đó trong một khoảng thời gian ngắn.</t>
         </is>
       </c>
     </row>
@@ -14877,8 +14877,8 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Combat Loại Electro&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
 &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; nảy thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; lần và phạm vi nảy tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -14946,8 +14946,8 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Combat Loại Electro&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
 &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; nảy thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; lần và có &lt;color=Highlight&gt;{1}&lt;/color&gt; xác suất gây Choáng khi nảy.</t>
         </is>
       </c>
@@ -15015,8 +15015,8 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Combat Loại Electro&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
 &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; nảy thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; lần và phạm vi nảy tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
@@ -15084,8 +15084,8 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Silent Lightning&lt;/te&gt;]&lt;/color&gt;
-&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Combat Loại Electro&lt;/te&gt;]&lt;/color&gt;
+          <t>&lt;color=#e8aa32&gt;[&lt;te href=750028&gt;Tia Chớp Vô Thanh&lt;/te&gt;]&lt;/color&gt;
+&lt;color=#e8aa32&gt;[&lt;te href=750025&gt;Máy Chiến Đấu Loại Electro&lt;/te&gt;]&lt;/color&gt;
 &lt;color=Highlight&gt;Sấm Chớp Liên Hoàn&lt;/color&gt; nảy thêm &lt;color=Highlight&gt;{0}&lt;/color&gt; lần và có &lt;color=Highlight&gt;{1}&lt;/color&gt; xác suất gây Choáng khi nảy.</t>
         </is>
       </c>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Dùng để loại bỏ Ô Nhiễm Tần Số trong một phạm vi nhất định, cho phép triển khai lại Combat Machines tại đó.
+          <t>Dùng để loại bỏ Ô Nhiễm Tần Số trong một phạm vi nhất định, cho phép triển khai lại Máy Chiến Đấu tại đó.
 Vật phẩm này sẽ tự động được sử dụng khi triển khai máy trong các tần số bị ô nhiễm.</t>
         </is>
       </c>
@@ -15413,7 +15413,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Cấp độ Máy Combat tối đa tăng thêm &lt;color=#fde7a1ff&gt;1&lt;/color&gt;. Unlock các mô-đun có thể chọn với hiệu ứng bổ sung sau khi nâng cấp Cấp độ Máy Combat lên &lt;color=#fde7a1ff&gt;3&lt;/color&gt;.</t>
+          <t>Cấp độ Máy Chiến Đấu tối đa tăng thêm &lt;color=#fde7a1ff&gt;1&lt;/color&gt;. Mở khóa các mô-đun có thể chọn với hiệu ứng bổ sung sau khi nâng cấp Cấp độ Máy Chiến Đấu lên &lt;color=#fde7a1ff&gt;3&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Kịch Bản Mô Phỏng: Nhận được tín hiệu cầu cứu từ đội đặc nhiệm. Cấu trúc ngầm đang điều tra đã bị Tacet Discord tràn ngập, chặn đường tiến vào các tầng dưới. Triển khai Combat Machines tại các vị trí đánh dấu và dụ Tacet Discord ra xa để đảm bảo lối đi an toàn cho đội.</t>
+          <t>Kịch Bản Mô Phỏng: Nhận được tín hiệu cầu cứu từ đội đặc nhiệm. Cấu trúc ngầm đang điều tra đã bị Tacet Discord tràn ngập, chặn đường tiến vào các tầng dưới. Triển khai Máy Chiến Đấu tại các vị trí đánh dấu và dụ Tacet Discord ra xa để đảm bảo lối đi an toàn cho đội.</t>
         </is>
       </c>
     </row>
@@ -15741,8 +15741,8 @@
       <c r="M229" t="inlineStr">
         <is>
           <t>Trong chế độ này, các Tacet Discord sẽ trở nên mạnh mẽ hơn qua mỗi đợt sóng.
-- Sau mỗi đợt sóng, bạn có thể chọn một Tactics để tăng cường Combat Machines của mình.
-- Sau một số đợt sóng nhất định, Shop KU-Money sẽ mở, nơi bạn có thể mua Tactics và vật phẩm.</t>
+- Sau mỗi đợt sóng, bạn có thể chọn một Chiến Thuật để tăng cường Máy Chiến Đấu của mình.
+- Sau một số đợt sóng nhất định, Cửa Hàng KU-Money sẽ mở, nơi bạn có thể mua Chiến Thuật và vật phẩm.</t>
         </is>
       </c>
     </row>
@@ -15810,8 +15810,8 @@
       <c r="M230" t="inlineStr">
         <is>
           <t>Trong chế độ này, các Tacet Discord sẽ trở nên mạnh mẽ hơn qua mỗi đợt sóng.
-- Sau mỗi đợt sóng, bạn có thể chọn một Tactics để tăng cường Combat Machines của mình.
-- Sau một số đợt sóng nhất định, Shop KU-Money sẽ mở, nơi bạn có thể mua Tactics và vật phẩm.</t>
+- Sau mỗi đợt sóng, bạn có thể chọn một Chiến Thuật để tăng cường Máy Chiến Đấu của mình.
+- Sau một số đợt sóng nhất định, Cửa Hàng KU-Money sẽ mở, nơi bạn có thể mua Chiến Thuật và vật phẩm.</t>
         </is>
       </c>
     </row>
@@ -15879,8 +15879,8 @@
       <c r="M231" t="inlineStr">
         <is>
           <t>Trong chế độ này, các Tacet Discord sẽ trở nên mạnh mẽ hơn qua mỗi đợt sóng.
-- Sau mỗi đợt sóng, bạn có thể chọn một Tactics để tăng cường Combat Machines của mình.
-- Sau một số đợt sóng nhất định, Shop KU-Money sẽ mở, nơi bạn có thể mua Tactics và vật phẩm.</t>
+- Sau mỗi đợt sóng, bạn có thể chọn một Chiến Thuật để tăng cường Máy Chiến Đấu của mình.
+- Sau một số đợt sóng nhất định, Cửa Hàng KU-Money sẽ mở, nơi bạn có thể mua Chiến Thuật và vật phẩm.</t>
         </is>
       </c>
     </row>
@@ -15948,8 +15948,8 @@
       <c r="M232" t="inlineStr">
         <is>
           <t>Trong chế độ này, các Tacet Discord sẽ trở nên mạnh mẽ hơn qua mỗi đợt sóng.
-- Sau mỗi đợt sóng, bạn có thể chọn một Tactics để tăng cường Combat Machines của mình.
-- Sau một số đợt sóng nhất định, Shop KU-Money sẽ mở, nơi bạn có thể mua Tactics và vật phẩm.</t>
+- Sau mỗi đợt sóng, bạn có thể chọn một Chiến Thuật để tăng cường Máy Chiến Đấu của mình.
+- Sau một số đợt sóng nhất định, Cửa Hàng KU-Money sẽ mở, nơi bạn có thể mua Chiến Thuật và vật phẩm.</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Các đặc vụ của Black Shores luôn là lực lượng tiên phong trong những thời khắc khủng hoảng. Để giảm thiểu rủi ro khi đối đầu với Echo, Black Shores đã phát triển những thiết bị chiến đấu chuyên dụng nhằm đối phó với mối đe dọa này.
+          <t>Các đặc vụ của Black Shores luôn là lực lượng tiên phong trong những thời khắc khủng hoảng. Để giảm thiểu rủi ro khi đối đầu với Tổ Tacet, Black Shores đã phát triển những thiết bị chiến đấu chuyên dụng nhằm đối phó với mối đe dọa này.
 Hiện Valentina đang dẫn dắt các cuộc thử nghiệm mô phỏng cho thiết bị, và cô ấy rất cần sự hỗ trợ của cậu để đẩy nhanh tiến độ thử nghiệm.</t>
         </is>
       </c>
@@ -16276,7 +16276,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Khi một Echo bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;, có {0}% khả năng tạo ra &lt;te href=851045&gt;&lt;color=#c79f49&gt;Hình Thái Basic&lt;/color&gt;&lt;/te&gt; của nó trên một ô trống.</t>
+          <t>Khi một Tổ Tacet bị &lt;te href=851006&gt;&lt;color=#c79f49&gt;Nuốt Chửng&lt;/color&gt;&lt;/te&gt;, có {0}% khả năng tạo ra &lt;te href=851045&gt;&lt;color=#c79f49&gt;Hình Thái Cơ Bản&lt;/color&gt;&lt;/te&gt; của nó trên một ô trống.</t>
         </is>
       </c>
     </row>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Khi một Echo &lt;te href=851041&gt;&lt;color=#c79f49&gt;Tự Hủy&lt;/color&gt;&lt;/te&gt; hoặc được &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hấp Thu&lt;/color&gt;&lt;/te&gt; vào một new Echo, bạn sẽ nhận thêm &lt;te href=851010&gt;&lt;color=#c79f49&gt;Dreamland Coupons&lt;/color&gt;&lt;/te&gt; bằng với lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; mà nó tạo ra.</t>
+          <t>Khi một Tổ Tacet &lt;te href=851041&gt;&lt;color=#c79f49&gt;Tự Hủy&lt;/color&gt;&lt;/te&gt; hoặc được &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hấp Thu&lt;/color&gt;&lt;/te&gt; vào một Tổ Tacet mới, bạn sẽ nhận thêm &lt;te href=851010&gt;&lt;color=#c79f49&gt;Phiếu Mộng Ảo&lt;/color&gt;&lt;/te&gt; bằng với lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; mà nó tạo ra.</t>
         </is>
       </c>
     </row>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Khi một Echo &lt;te href=851041&gt;&lt;color=#c79f49&gt;Tự Hủy&lt;/color&gt;&lt;/te&gt;, có {0}% khả năng tạo ra &lt;te href=851048&gt;&lt;color=#c79f49&gt;Dream Block: Hắc Diệp Thạch&lt;/color&gt;&lt;/te&gt; trên ô đó.</t>
+          <t>Khi một Tổ Tacet &lt;te href=851041&gt;&lt;color=#c79f49&gt;Tự Hủy&lt;/color&gt;&lt;/te&gt;, có {0}% khả năng tạo ra &lt;te href=851048&gt;&lt;color=#c79f49&gt;Khối Mộng: Hắc Diệp Thạch&lt;/color&gt;&lt;/te&gt; trên ô đó.</t>
         </is>
       </c>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Mỗi {0} Echo hạng xanh trên chiến trường, khi &lt;te href=851013&gt;&lt;color=#c79f49&gt;Vật Phẩm Giao Dịch&lt;/color&gt;&lt;/te&gt; được &lt;te href=851007&gt;&lt;color=#c79f49&gt;Trao đổi&lt;/color&gt;&lt;/te&gt;, có {1}% cơ hội tạo ra một Echo cùng tên, có thể chồng chất tối đa {2} lần.</t>
+          <t>Mỗi {0} Echo hạng xanh trên chiến trường, khi &lt;te href=851013&gt;&lt;color=#c79f49&gt;Vật Phẩm Giao Dịch&lt;/color&gt;&lt;/te&gt; được &lt;te href=851007&gt;&lt;color=#c79f49&gt;Trao Đổi&lt;/color&gt;&lt;/te&gt;, có {1}% cơ hội tạo ra một Echo cùng tên, có thể chồng chất tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Daily Coupon&lt;/color&gt;&lt;/te&gt; từ Echoes tạo ra qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Tích Hợp&lt;/color&gt;&lt;/te&gt; bằng tổng sản lượng Daily Coupon của tất cả các Echoes được Tích Hợp.</t>
+          <t>Sản lượng &lt;te href=851009&gt;&lt;color=#c79f49&gt;Phiếu Hằng Ngày&lt;/color&gt;&lt;/te&gt; từ Echo tạo ra qua &lt;te href=851008&gt;&lt;color=#c79f49&gt;Tích Hợp&lt;/color&gt;&lt;/te&gt; bằng tổng sản lượng Phiếu Hằng Ngày của tất cả các Echo được Tích Hợp.</t>
         </is>
       </c>
     </row>
@@ -16671,10 +16671,10 @@
       <c r="M243" t="inlineStr">
         <is>
           <t>Báo cáo không chính thức do các thành viên của Hội ghi lại sau đợt kiểm tra định kỳ tại Nhà máy Fabricatorium.
-1. Sự hao mòn một phần của lò tinh chế Fallen Grave đã gây ra tình trạng phân rã không hoàn toàn các Tần số Echoes, khiến ý thức còn sót lại bị truyền ngược trở lại. Cần bảo trì khẩn cấp.
-2. Anima Cradle đã bổ sung giao thức phát hiện Echoes theo yêu cầu để ngăn ý thức còn sót ảnh hưởng đến các Echoes mới. Những Echoes mới được tạo ra mang theo ý thức cũ đã được phát hiện kịp thời sẽ được chuyển ngay đến lò tinh chế để phân rã lại.
+1. Sự hao mòn một phần của lò tinh chế Fallen Grave đã gây ra tình trạng phân rã không hoàn toàn các Tần số Echo, khiến ý thức còn sót lại bị truyền ngược trở lại. Cần bảo trì khẩn cấp.
+2. Anima Cradle đã bổ sung giao thức phát hiện Echo theo yêu cầu để ngăn ý thức còn sót ảnh hưởng đến các Echo mới. Những Echo mới được tạo ra mang theo ý thức cũ đã được phát hiện kịp thời sẽ được chuyển ngay đến lò tinh chế để phân rã lại.
 3. Cuộc điều tra khu vực lưu trữ Năng lượng của Energy Hub vẫn đang diễn ra. Bất kỳ Reverberation nào còn tương đối nguyên vẹn sẽ được chiết xuất và phân rã ngay khi phát hiện.
-Ghi chú viết tay thêm sau: Delete hai dòng cuối trong báo cáo chính thức. Đừng quan tâm đến những việc không liên quan đến mình, đừng tiếp xúc với bất kỳ ai mặc đồ đỏ, và nghiên cứu đang được tiến hành ở tháp cao không liên quan gì đến anh. Hãy im lặng và có thể anh sẽ sống lâu hơn.</t>
+Ghi chú viết tay thêm sau: Xóa hai dòng cuối trong báo cáo chính thức. Đừng quan tâm đến những việc không liên quan đến mình, đừng tiếp xúc với bất kỳ ai mặc đồ đỏ, và nghiên cứu đang được tiến hành ở tháp cao không liên quan gì đến anh. Hãy im lặng và có thể anh sẽ sống lâu hơn.</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16806,7 @@
       <c r="M245" t="inlineStr">
         <is>
           <t>Mặt Trăng luôn là chính mình, từ rất lâu trước khi biết mình là Mặt Trăng.
-Nàng không còn nhìn vào tương lai qua ánh sáng rải rác của số phận, bởi nàng hiểu rằng bất cứ nơi nào nàng hướng ánh mắt, tương lai nàng tìm kiếm đều đang chờ đợi. Giữa vô vàn lối mòn định mệnh, nàng chọn trở thành Anchor đích thực cho chính mình.</t>
+Nàng không còn nhìn vào tương lai qua ánh sáng rải rác của số phận, bởi nàng hiểu rằng bất cứ nơi nào nàng hướng ánh mắt, tương lai nàng tìm kiếm đều đang chờ đợi. Giữa vô vàn lối mòn định mệnh, nàng chọn trở thành Điểm Neo đích thực cho chính mình.</t>
         </is>
       </c>
     </row>
@@ -16947,12 +16947,12 @@
       <c r="M247" t="inlineStr">
         <is>
           <t>[
-Báo Cáo Y Tế Hàng Năm Ephor's Palace—Quyền Truy Cập Được Xác Nhận]
-Biểu đồ dạng sóng của đối tượng cho thấy dao động hình elip. Mô hình miền thời gian đều đặn, không có dấu hiệu dao động bất thường. Kết quả test nằm trong phạm vi pha bình thường.
+Báo Cáo Y Tế Hàng Năm Cung Điện Ephor—Quyền Truy Cập Được Xác Nhận]
+Biểu đồ dạng sóng của đối tượng cho thấy dao động hình elip. Mô hình miền thời gian đều đặn, không có dấu hiệu dao động bất thường. Kết quả kiểm tra nằm trong phạm vi pha bình thường.
 Nguy Cơ Cộng Hưởng: Đối tượng này có nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt; ở mức tối thiểu. Dựa trên cường độ sóng, khả năng Quá Tải cũng được loại trừ.
 Hồ sơ ghi nhận không có tiền sử Quá Tải, và hiện tại không cần thiết phải tư vấn tâm lý.
 &lt;i&gt;"Mỗi lần làm cái này, mình lại thấy như đang đo chiều cao của một người phụ nữ trưởng thành vậy, hơi... kỳ cục."&lt;/i&gt;
-&lt;i&gt;"Nhưng đến phần test thể chất thì cậu lúc nào cũng khiến người thiết kế thiết bị phải ngạc nhiên. Hay đúng hơn là sốc luôn ấy."&lt;/i&gt;
+&lt;i&gt;"Nhưng đến phần kiểm tra thể chất thì cậu lúc nào cũng khiến người thiết kế thiết bị phải ngạc nhiên. Hay đúng hơn là sốc luôn ấy."&lt;/i&gt;
 &lt;i&gt;"Haha, vậy à?"&lt;/i&gt;</t>
         </is>
       </c>
@@ -17089,11 +17089,11 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>["Trích từ Sổ Đăng Ký &lt;te href=850152&gt;Nữ Tư Tế&lt;/te&gt;, Tetragon Temple]
-Mục này liên quan đến Nữ Tư Tế thứ 127 của Tetragon Temple.
-Sóng dạng của Nữ Tư Tế này phần lớn vẫn nằm trong phạm vi kiểm soát, không có dấu hiệu rủi ro &lt;te href=850073&gt;Overclocking&lt;/te&gt;. Tuy nhiên, đã ghi nhận nhiều lần gián đoạn với thời lượng khác nhau, kèm theo sự suy giảm tần số dần dần và đều đặn. Điều này cho thấy khả năng cô đang ở trạng thái cạn kiệt kéo dài. Nguyên nhân gốc rễ vẫn chưa được xác định. Nữ Tư Tế từ chối kiểm tra thêm và thể hiện ít thiện chí trong việc thảo luận sâu hơn về vấn đề này.
-&lt;i&gt;Rõ ràng là cô hiểu về tình trạng của mình nhiều hơn những gì cô tiết lộ. Nhưng nếu sóng dạng này tiếp tục suy giảm vượt khỏi phạm vi kiểm soát, thậm chí xuống mức zero… thì điều gì sẽ xảy ra?&lt;/i&gt;
-&lt;i&gt;Liệu cô thực sự không sợ hãi? Hay cô đã tìm ra cách can thiệp?&lt;/i&gt;</t>
+          <t>["Trích từ &lt;te href=850152&gt;Biên Niên Sử Tư Tế&lt;/te&gt;, Đền Tetragon]
+Mục này ghi chép về Tư Tế thứ 127 của Đền Tetragon.
+Sóng tần số của Tư Tế này phần lớn vẫn nằm trong ngưỡng kiểm soát, không có dấu hiệu nguy cơ &lt;te href=850073&gt;Quá Tải&lt;/te&gt;. Tuy nhiên, đã quan sát thấy nhiều lần gián đoạn với thời lượng khác nhau, đi kèm với sự suy giảm tần số dần dần và đều đặn. Điều này cho thấy khả năng cô đang trong trạng thái suy kiệt kéo dài. Nguyên nhân vẫn chưa được xác định. Tư Tế đã từ chối kiểm tra thêm và tỏ ra không mấy sẵn lòng thảo luận sâu về vấn đề này.
+&lt;i&gt;Rõ ràng là cô hiểu về tình trạng của mình hơn những gì cô tiết lộ. Nhưng nếu sóng tần số này tiếp tục suy giảm vượt khỏi ngưỡng kiểm soát, thậm chí về không… thì điều gì sẽ xảy ra?
+Cô thực sự không sợ hãi? Hay cô đã tìm ra cách can thiệp?&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -17385,7 +17385,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Một cành cây gãy mọc lên từ vết thương từng nứt vỡ. Nó giống với Lunarum Bough mà bạn từng tạo ra trong Chaos. Nhưng khi cung của Iuno đã được rèn xong, một cành cây hoàn hảo chẳng còn ý nghĩa gì nữa. Trải qua bao thăng trầm của số phận, nó không còn là vật hiến tế, chỉ là một cành cây bình thường—không định nghĩa, không gánh nặng, tự do như vốn dĩ.
+          <t>Một cành cây gãy mọc lên từ vết thương từng nứt vỡ. Nó giống với Cành Lunarum mà bạn từng tạo ra trong Chaos. Nhưng khi cung của Iuno đã được rèn xong, một cành cây hoàn hảo chẳng còn ý nghĩa gì nữa. Trải qua bao thăng trầm của số phận, nó không còn là vật hiến tế, chỉ là một cành cây bình thường—không định nghĩa, không gánh nặng, tự do như vốn dĩ.
 Vậy là giờ đây, bạn và Iuno cuối cùng cũng có thể cùng nhau ngắm nhìn nó lớn lên trong yên bình, trong tương lai chưa được viết nên sau cái kết cuối cùng.
 Một mầm non mới phù hợp với khởi đầu mới, bắt nguồn từ hy vọng.</t>
         </is>
@@ -17620,7 +17620,7 @@
 Khi thanh kiếm bị đánh văng khỏi tay, ý thức của cô gái cũng chìm vào hỗn loạn.
 Nhiệt nóng rần rật lan khắp tứ chi. Rồi tê cứng. Những dây thần kinh căng quá mức đứt lìa, nhấn chìm cô vào bóng tối lạnh lẽo, im lặng.
 Cô không còn nhớ mình đã ngã xuống bao nhiêu lần. Cô cũng không biết mình còn phải đứng dậy thêm bao nhiêu lần nữa.
-Fear bắt đầu bén rễ trong lồng ngực. Nó quấn lấy ý chí đang tan rã của cô như một cái kén tơ.
+Nỗi sợ bắt đầu bén rễ trong lồng ngực. Nó quấn lấy ý chí đang tan rã của cô như một cái kén tơ.
 Cô sợ hãi. Sợ rằng mình sẽ gục ngã trước khi đạt được điều gì. Sợ rằng mình sẽ sa ngã trên con đường không lối về.
 "Hãy chấp nhận cảm giác này, Augusta..."
 Giọng nói ấy vang lên bên tai, xuyên qua bóng tối như que diêm được quẹt sáng trong hư không.
@@ -17772,7 +17772,7 @@
 "...!"
 Như thể một mũi giáo băng đâm xuyên sống lưng, mắt Augusta bừng mở.
 "Sao thế, Augusta?"
-"Không có gì... Chỉ là..." Nàng đưa tay lên mặt, cau ngươi, cố nhớ lại.
+"Không có gì... Chỉ là..." Nàng đưa tay lên mặt, cau mày, cố nhớ lại.
 "Chỉ là... ta không thể nhớ nổi đối thủ hôm nay trông như thế nào..."
 Vài ngày sau, Augusta nhận được lời mời tham dự đấu trường ngầm. Ngày trước, nàng từng đứng đó như một Võ Sĩ. Giờ đây, họ chào đón nàng như một vị khách quý, ngồi giữa những quý tộc.
 "Hãy nhận lời đi, Augusta. Mở rộng tầm nhìn của con. Chỉ khi bước ra khỏi cái lồng nhỏ bé ấy, con mới có thể vươn tới đỉnh cao của Septimont."
@@ -17790,7 +17790,7 @@
 Lời thì thầm của nàng va chạm với giọng nói ấy, như hai viên đá lửa va vào nhau, và thứ gì đó bên trong nàng bùng cháy.
 Nó đốt cháy máu nàng. Nó đốt cháy những nghi ngờ và câu hỏi mà nàng đã ấp ủ từ lâu.
 "Không cần phải phiền phức thế..."
-&lt;te href=850072&gt;Tacet Mark&lt;/te&gt; trên mu bàn tay nàng bừng sáng. Một luồng gió cắt ngang không trung. Kiếm bay thẳng vào tay nàng.
+&lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; trên mu bàn tay nàng bừng sáng. Một luồng gió cắt ngang không trung. Kiếm bay thẳng vào tay nàng.
 Quý tộc há hốc miệng khi Augusta đứng dậy khỏi chỗ ngồi và nhảy xuống đấu trường.
 "Nếu các ngươi muốn thách đấu ta, không cần quyền gì cả!" Nàng cắm kiếm xuống đất, giọng vang khắp đấu trường.
 "Nếu các ngươi cùng chung giấc mơ, hãy chĩa lưỡi kiếm vào kẻ mà các ngươi muốn đánh bại nhất. Ngay bây giờ!"
@@ -17903,7 +17903,7 @@
         <is>
           <t>"Trước khi ngươi hỏi hết những câu 'tại sao'... cho ta hỏi ngươi một câu trước đã."
 "Ngươi... đến từ Fabianum phải không?"
-"Yes."
+"Đúng vậy."
 "Ta đã nghĩ thế. Ai ngờ một đứa trẻ mồ côi từ Fabianum lại có thể trở thành Nhà Vô Địch của Septimont."
 "Ngươi ngạc nhiên sao?"
 "Không. Chỉ là... tiếc nuối thôi."
@@ -17917,7 +17917,7 @@
 "Nhưng ta có thể tự lừa dối mình, chứ không lừa được thực tại. Này cô gái trẻ... ta đã biết ngươi là ai từ rất lâu. Ngày ngươi được đưa đến Septimont, ta đã biết ngươi là người sống sót cuối cùng của Fabianum."
 "Sự tồn tại của ngươi như một lưỡi kiếm treo trên đầu ta. Và ngày ngươi trở thành Nhà Vô Địch... lưỡi kiếm ấy đã rơi xuống. Ta không thể trốn tránh sai lầm của mình nữa—nhắm mắt làm ngơ trước sự sụp đổ của Fabianum, chỉ để bảo vệ vương miện tầm thường của mình."
 "Ngươi nói thế vì hối hận à?"
-"Maybe. Hoặc có thể... vì hy vọng." Magno đứng dậy, lấy ra một chiếc ly từ ngăn kéo bí mật dưới bàn.
+"Có thể. Hoặc có thể... vì hy vọng." Magno đứng dậy, lấy ra một chiếc ly từ ngăn kéo bí mật dưới bàn.
 "Vương miện đã ban cho ta quyền lực vô biên, nhưng cũng biến ta thành kẻ hèn nhát. Ta không còn là anh hùng mà Septimont cần nữa." Ông giơ chiếc ly rỗng về phía nàng. "Hãy đội vương miện lên, Augusta. Ngươi đã đánh bại mọi đối thủ mà ngươi thấy. Giờ là lúc đối mặt với những kẻ ngươi không thấy được."
 "Vậy ngươi nghĩ ta xứng đáng chỉ vì ta đánh bại ngươi sao?"
 "Không. Không hề nông cạn như vậy." Magno lắc đầu. "Bởi vì ta đã nghe thấy tên của ngươi. Từ đỉnh cao của Septimont đến những ngõ ngách tối tăm, từ những sảnh đường vàng son đến những con hẻm nghèo khó. Dù giàu nghèo, mạnh yếu, sang hèn hay tín ngưỡng khác biệt, người dân đều được kết nối bởi một cái tên duy nhất. Và ta tin rằng, một ngày nào đó, sự kết nối ấy sẽ trở thành sức mạnh mới thúc đẩy Septimont tiến lên."
@@ -17925,14 +17925,14 @@
 "Dù xương cốt có thành tro tàn, cũng đừng khuất phục trước màn đêm giả dối ấy." Trong khoảnh khắc ngắn ngủi, qua vành ly, ánh lửa lại lóe lên trong đôi mắt Magno.
 Đêm hôm ấy, những người hầu dọn dẹp tìm thấy Magno ngồi trên ngai vàng của Ephor. Mặt ông tái nhợt, môi tím ngắt. Họ bảo đó là chất độc. Một chiếc ly vỡ nằm dưới chân, chất lỏng tràn ra lấp lánh chảy xuống các bậc thềm.
 Có người nói đó là thủ đoạn của kẻ thù.
-Kẻ khác bảo đó là món quà của Thượng viện. Một cái chết thanh nhã trong ly rượu.
+Kẻ khác bảo đó là món quà của Thượng viện. Một cái chết thanh tao trong ly rượu.
 Nhưng hầu hết đều đồng ý rằng Septimont cần một "anh hùng" mới.
 Và đúng như Magno đã tiên đoán, tên của Augusta bắt đầu lan truyền khắp Septimont như một cơn gió.
 Mùa xuân nhường chỗ cho mùa thu, và ngai vàng Ephor chào đón chủ nhân mới.
 Augusta đứng tại nơi nàng từng chỉ dám ngước nhìn. Nàng nhìn ngai vàng gai góc đã nuốt chửng biết bao anh hùng. Nàng nghĩ về Magno trong đêm cuối cùng ấy. Và trong tâm trí, nàng thấy ông nâng ly chúc mừng người sẽ ngồi đây một ngày nào đó, rồi uống cạn ly độc dược.
 Augusta không có nhiều suy nghĩ phức tạp trong đầu. Nàng không hề mang lòng thù hận ai. Nàng đã tận mắt chứng kiến bóng tối, nhưng cũng biết ánh sáng trông như thế nào.
 Suy nghĩ của nàng rất đơn giản—
-Chỉ kẻ vượt qua mọi anh hùng mới xứng danh Hero of Heroes.
+Chỉ kẻ vượt qua mọi anh hùng mới xứng danh Anh Hùng Trong Các Anh Hùng.
 Và những chiếc gai trên ngai vàng chỉ là một thử thách khác để vượt qua.
 Nàng ngồi xuống, rồi với đôi tay vững vàng, đặt cả chiếc còng lẫn vương miện lên đầu.
 "Ephor Augusta, Thượng viện gửi thông điệp. Các Thượng nghị sĩ yêu cầu diện kiến... để thảo luận vấn đề khẩn cấp." Người truyền tin cúi đầu trước ngai vàng.
@@ -18043,7 +18043,7 @@
 Cô đã hoàn thành lời tiên tri cổ xưa và trở thành Anh Hùng trong Anh Hùng mà cô từng ngưỡng mộ.
 Cô đã gặp gỡ những người định mệnh kề vai sát cánh, vượt qua những thử thách từng tưởng chừng bất khả thi.
 Nếu viết nên một câu chuyện để lưu truyền hậu thế, có lẽ đây đã là hồi kết. Chương cuối của Anh Hùng trong Anh Hùng, Augusta.
-A perfect ending. Không chừa chỗ cho hối tiếc.
+Một cái kết hoàn hảo. Không chừa chỗ cho hối tiếc.
 Nhưng đời đâu phải là vở kịch. Nó không kết thúc chỉ vì cao trào đã qua.
 Cô phải tự hỏi, và cô muốn tự hỏi—
 Khi Septimont không còn cần đến Augusta, khi mảnh đất này bắt đầu sinh ra những huyền thoại mới—
@@ -18051,13 +18051,13 @@
 Với câu hỏi ấy cứ vương vấn trong đầu, Augusta lặng lẽ rời khỏi Cung điện Ephor.
 Cô không chọn hướng đi. Cô để bản năng dẫn lối.
 Trong lúc lang thang, cô vẫn không ngừng suy nghĩ—
-Liệu cô nên theo đuổi sức mạnh lớn lao hơn? Tìm kiếm những kẻ thù đáng gờm mới? Explore những vùng đất ngoài Septimont? Hay khi mọi chuyện đã an bài, cô sẽ tra kiếm vào vỏ và sống một cuộc đời bình yên, mãn nguyện?
+Liệu cô nên theo đuổi sức mạnh lớn lao hơn? Tìm kiếm những kẻ thù đáng gờm mới? Khám phá những vùng đất ngoài Septimont? Hay khi mọi chuyện đã an bài, cô sẽ tra kiếm vào vỏ và sống một cuộc đời bình yên, mãn nguyện?
 Biết bao nhiêu khả năng. Biết bao nhiêu con đường trải dài trước mắt.
 Đến khi Augusta trở lại với thực tại, cô nhận ra mình đã đi đến đấu trường. Nơi lưu giữ biết bao kỷ niệm của cô.
 Hôm nay là ngày nghỉ. Đấu trường, lần đầu tiên, vắng lặng.
 Không, không hoàn toàn vắng lặng.
 Như bị hút bởi một thỏa thuận thầm lặng, ai đó cũng đã lang thang đến đây.
-Ánh mắt {Male=Cậu ấy;Female=Cô ấy} gặp ánh mắt Augusta. Và cả hai cùng mỉm cười, như thể chia sẻ một bí mật chỉ có hai người biết.
+Ánh mắt {Male=His;Female=Her} gặp ánh mắt Augusta. Và cả hai cùng mỉm cười, như thể chia sẻ một bí mật chỉ có hai người biết.
 Chỉ thế thôi, mọi lo âu của Augusta tan biến.
 Cô chưa có câu trả lời. Nhưng cô vẫn còn thời gian để tìm ra nó.
 Không cần vội vàng.
@@ -18275,29 +18275,29 @@
 Đôi khi, cô nhìn thấy quá khứ. Đôi khi, cô nhìn thấy chính mình. Nhưng thường xuyên hơn, cô chỉ đơn thuần bị buộc phải gánh chịu tất cả một lần nữa, sống lại ký ức như thể đó là hiện tại, hết lần này đến lần khác, cho đến khi mọi thứ chậm lại, cho đến khi sự im lặng nuốt chửng cô hoàn toàn, cho đến khi lần thức tỉnh tiếp theo ập đến.
 Cô dần quen với vòng luẩn quẩn ấy. Nó bắt đầu trở nên gần như bình thường. Nhưng vẫn còn đó một sự phi lý thầm lặng. Không ai khác nhớ những khoảnh khắc bị tước đi ý nghĩa này. Thế mà chúng lại bám riết lấy cô, người đã chọn biến mất. Chỉ riêng cô phải gánh chịu chúng trong những vòng lặp bất tận. Phải chăng đây là trò đùa tàn nhẫn của số phận? Hay sự trừng phạt cho việc cô đã biến mất?
 Nhưng không có câu trả lời. Cô lại tỉnh dậy, và điều đó có nghĩa là một mảnh vỡ khác của quá khứ đã đuổi kịp cô.
-Hôm ấy, mưa nặng hạt và lạnh buốt, nhưng đám đông vẫn tụ tập trong Tetragon Temple. Họ đến để chứng kiến sự xuất hiện của thiên tài được tiên tri từ lâu, sắp gia nhập hàng ngũ &lt;te href=850152&gt;Nữ Tư Tế&lt;/te&gt;. Hôm ấy, Iuno nghe về Nữ Tư Tế nhiều hơn bao giờ hết: sự kính sợ, tôn kính và những lời đồn kỳ bí. Một số người khẳng định Nữ Tư Tế có thể nhìn thấy chân lý tối thượng và tìm ra sự hoàn hảo ẩn sâu trong tuyệt vọng vào giây phút cuối cùng.
-Xét cho cùng, Nữ Tư Tế đứng gần số phận, tương lai, những điều chưa biết và con đường đúng đắn hơn bất kỳ ai. Điều đó thôi cũng đủ khơi dậy lòng ghen tị. Nhưng với Iuno, một nửa những lời đó là dối trá. Và nửa còn lại, là ảo tưởng. Bởi đêm trước hôm ấy, khi nghỉ ngơi trong vườn cùng những người khác, cô đã chứng kiến cái chết của một Nữ Tư Tế.
-Một con bồ câu trắng đậu dưới gốc cây nguyệt quế cổ thụ, đôi cánh run rẩy, gần như không che được tiếng thở yếu ớt. Nữ Tư Tế sắp qua đời quay sang cô, giọng khẽ khàng, thì thầm:
-"Cháu... cháu không giống chúng ta. Cháu sinh ra đã có thể nhìn thấy. Vậy nên hãy đi. Hãy nhìn thấy điều đó giùm chúng ta."
-"Iuno sẽ làm," cô đáp, gần như không thành tiếng.
-Đó là điều cô có thể làm. Nhưng người nghe lời hứa ấy sẽ không bao giờ sống để thấy nó được thực hiện. Vậy đấy, ngay cả những người sánh bước bên số phận, tương lai và những điều chưa biết cũng không phải lúc nào cũng mạnh mẽ hơn người khác. Họ không phải lúc nào cũng nhìn thấy kết cục của chính mình. Và họ cũng khao khát một câu trả lời.
-Lời tiên tri vừa là xiềng xích, vừa là chìa khóa. Iuno muốn nắm giữ chìa khóa. Nhưng nếu có thể, cô cũng muốn đập vỡ xiềng xích. Đó là lý do cô chọn trở thành Nữ Tư Tế, nhưng lại không bị ràng buộc bởi kỳ vọng hay lý tưởng của người khác.
-Hôm ấy, cô không mặc lễ phục, mà khoác một bộ trang phục cổ xưa điểm nhung và vàng. Không phải như kẻ khẩn cầu số phận, mà như người dám đối diện ánh mắt của nó. Cô bước tới, tay cầm giá nến.
-Những lời xì xào lan khắp đám đông. Một Elder, cứng nhắc với truyền thống, lẩm bẩm với vẻ khinh miệt:
-"Vô lễ... Sao cô ta lại thiếu khiêm nhường đến thế?"
-Iuno nghe thấy. Và đó là lần đầu tiên, cũng là lần cuối cùng, cô đáp lời:
-"Kẻ nhìn thấy không cần quỳ gối."
-Cô ngẩng đầu. Đôi mắt xám xanh của cô, với ánh sáng từ mái vòm cao của Đền chiếu rọi, sắc như lưỡi dao, lấp lánh như thể háo hức được rạch thứ gì đó ra.
-Sau ngày hôm ấy, cô bắt đầu cuộc dò tìm bất tận qua dòng chảy hỗn loạn, vươn tay vào những điều chưa biết để tìm kiếm sự sáng tỏ. Cô nhìn thấy nhiều hơn về tương lai. Chúng rời rạc, đáng sợ và không thể tránh khỏi. Cô truyền đạt những khải tượng ấy cho người khác. Những người nhận được chúng coi lời cô như thánh kinh, như niềm hy vọng để bám víu. Nhưng Iuno hiểu rõ hơn. Đó chỉ là những cái nhìn thoáng qua, những mảnh vỡ thoáng qua của số phận lọt qua khe hở.
-Và càng nhìn thấy nhiều, cô càng nhận ra rằng những khải tượng ấy cũng giống như lưỡi dao. Nếu không dùng chúng để rạch thứ gì đó ra, chính bản thân sẽ bị chúng cứa đứt.
-Từ đó, Iuno không bao giờ nhắm mắt lại nữa. Nhưng sâu bên trong, cô bắt đầu cảm thấy có thứ gì đó đang xé rách cô.
-Có lẽ đó là ký ức.
-Có lẽ đó là cái tên mà mọi người gọi cô.
-Có lẽ chỉ là một mảnh của chính cô đang phai nhạt dần mỗi khi nhìn quá sâu vào thế giới.
-Dù vậy, cô không hề sợ hãi.
-Cô đứng trong gió của Septimont, mưa bám trên hàng mi như những sợi bạc.
-Bà &lt;te href=851017&gt;Lillibet&lt;/te&gt; từng nói cô sinh ra để nhìn thấy tất cả. Và cô đã làm vậy. Nhưng giờ đây, cô muốn nhìn thấy điều khác:
-Liệu cô có thể bước khỏi lưỡi dao và sống sót để đến một nơi xa hơn.</t>
+Hôm ấy, mưa nặng hạt và lạnh buốt, nhưng đám đông vẫn tụ tập trong Đền Tetragon. Họ đến để chứng kiến sự xuất hiện của thiên tài được tiên tri từ lâu, sắp gia nhập hàng ngũ &lt;te href=850152&gt;Nữ Tư Tế&lt;/te&gt;. Hôm ấy, Iuno nghe về Nữ Tư Tế nhiều hơn bao giờ hết: awe, reverence, and fantastical rumors. Some claimed that Priestesses could glimpse the ultimate truth and discover perfection buried within despair in their final moments.
+After all, Priestesses stood closer than anyone to fate, to the future, to the unknown, and to the right path. That alone was enough to stir envy. But to Iuno, half of those claims were lies. And the other half, delusion. Because the night before that very day, while resting in the garden with the others, she had witnessed a Priestess's death.
+A white dove had landed beneath the ancient laurel tree, its wings fluttering, barely covering the sound of weakening sighs. The dying Priestess turned to her, voice faint, and whispered:
+"You... you're not like us. You were born able to see. So go. See it for us."
+"I will," Iuno replied, almost inaudibly.
+It was something she could do. But the one who heard her promise would never live to see it fulfilled. So yes, even those who walk beside fate, future, and the unknown in between aren't always stronger than others. They can't always see how it ends for themselves. And they, too, long for an answer.
+Prophecy is both a chain and a key. Iuno wants to hold the key. But if she can, she also wants to break the chain. That was why she chose to become a Priestess, yet was unbound by others' expectations or ideals.
+That day, she wore not the ceremonial robe, but an ancient garment adorned with satin and gold. Not as a supplicant of fate, but as someone who dares to meet its gaze. She stepped forward, candelabrum in hand.
+Whispers stirred through the crowd. An Elder, rigid with tradition, muttered with disdain,
+"Insolence... How can she be so lacking in humility?"
+Iuno heard him. And for the first and last time, she answered:
+"One who sees needs not kneel."
+She raised her head. Her grey-blue eyes, with the light shining down from the Temple's high dome in them, were sharp as blades, gleaming as if eager to cut something open.
+After that day, she began her long, unending dredge through the tide of chaos, reaching into the unknown for clarity. She saw more of the future. They were fragmented, frightening, and inescapable. She passed these visions on. Those who received them treated her words as scripture, a hope to clutch at. But Iuno knew better. They were only glimpses, fleeting slivers of fate slipping through the cracks.
+And the more she saw, the more she realized that these visions were just like blades. If one wielded them without cutting something open, they themselves would be cut instead.
+Since then, Iuno has never closed her eyes again. But deep inside, she begins to feel something tearing at her too.
+Maybe it's memory.
+Maybe it's the name people call her by.
+Maybe it's just a piece of herself that fades a little more each time she looks too closely at the world.
+Still, she is not afraid.
+She stands in the wind of Septimont, rain clinging to her lashes like silver threads.
+Grandmother &lt;te href=851017&gt;Lillibet&lt;/te&gt; once told her she was born to see it all. And she has. But now, she wants to see something else:
+Whether she can walk away from the blade and live to reach somewhere further.</t>
         </is>
       </c>
     </row>
@@ -18396,15 +18396,15 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Trước khi &lt;te href=850159&gt;High Tide Tối&lt;/te&gt; thực sự dâng trào, Iuno đã là người đầu tiên nhìn thấy tương lai thảm khốc ấy.
-Những sinh vật u ám do triều cường sinh ra đen kịt như đêm không trăng. &lt;te href=850164&gt;Các Chiến Binh&lt;/te&gt; đã chiến đấu hết sức, nhưng vô ích. Mỗi lần vũ khí của họ sắp đâm xuyên qua thân thể lũ sinh vật High Tide Tối, chúng lại tan ra và hòa vào dòng triều, rồi tái hợp và hồi sinh. Tất cả những gì chúng để lại chỉ là vệt bùn nhầy nhụa, lấp lánh, chế nhạo dưới chân các Chiến Binh.
+          <t>Trước khi &lt;te href=850159&gt;Triều Cường Tối&lt;/te&gt; thực sự dâng trào, Iuno đã là người đầu tiên nhìn thấy tương lai thảm khốc ấy.
+Những sinh vật u ám do triều cường sinh ra đen kịt như đêm không trăng. &lt;te href=850164&gt;Các Chiến Binh&lt;/te&gt; đã chiến đấu hết sức, nhưng vô ích. Mỗi lần vũ khí của họ sắp đâm xuyên qua thân thể lũ sinh vật Triều Cường Tối, chúng lại tan ra và hòa vào dòng triều, rồi tái hợp và hồi sinh. Tất cả những gì chúng để lại chỉ là vệt bùn nhầy nhụa, lấp lánh, chế nhạo dưới chân các Chiến Binh.
 Có những thứ trên đời này sẽ không cúi mình trước ý chí của ngươi, dù ngươi có nhìn thấy chúng đến với sự rõ ràng hoàn hảo.
-Đêm đó, Iuno hầu như không chợp mắt. Trong giấc mơ, không phải lũ quái vật chìm trong High Tide Tối. Mà là chính cô. Dòng triều nuốt chửng miệng và mũi cô, kéo cô xuống từng chút một. Cô chưa bao giờ biết nó sâu đến đâu. Khi chân cô chạm đáy, mắt cô bắt gặp một phiên bản lạnh lẽo, sắc bén hơn của chính mình đứng ở phía bên kia.
+Đêm đó, Iuno hầu như không chợp mắt. Trong giấc mơ, không phải lũ quái vật chìm trong Triều Cường Tối. Mà là chính cô. Dòng triều nuốt chửng miệng và mũi cô, kéo cô xuống từng chút một. Cô chưa bao giờ biết nó sâu đến đâu. Khi chân cô chạm đáy, mắt cô bắt gặp một phiên bản lạnh lẽo, sắc bén hơn của chính mình đứng ở phía bên kia.
 "Ngươi thực sự tin rằng nhìn thấy là cứu rỗi sao?"
 Phiên bản Iuno kia mỉm cười. Trong mắt cô ấy là vô số phiên bản Septimont tan vỡ—cháy rụi, chìm nghỉm, được xây dựng lại rồi lại sụp đổ.
 "Ngươi có thể nhìn thấy mọi người… ngoại trừ chính mình."
 Iuno cố gắng trả lời, nhưng không thốt nên lời.
-High Tide Tối vẫn cuộn trào trên High Nguyên. Các Chiến Binh liên tục xung phong, nhưng kết quả chẳng đáng là bao. Ngày càng nhiều người tụ tập tại Tetragon Temple, chờ đợi cô và các Nữ Tư Tế khác đưa ra lời tiên tri, điều gì đó hữu ích. Họ nói về việc tìm ra kết thúc bằng cách truy tìm khởi đầu, thay đổi kết cục bằng cách hiểu nguyên nhân. Họ muốn định hình một số phận tốt đẹp hơn, nhưng Iuno lại thấy mình không nói nên lời. Cô nhìn thấy hình bóng mẹ mình trước khi bị High Tide Tối chôn vùi. Cô thấy những tòa nhà sụp đổ, đám đông tán loạn, và mũi tên này đến mũi tên khác rời khỏi cung của cô, mỗi mũi đều bị bóng tối nuốt chửng trước khi kịp trúng đích.
+Triều Cường Tối vẫn cuộn trào trên Cao Nguyên. Các Chiến Binh liên tục xung phong, nhưng kết quả chẳng đáng là bao. Ngày càng nhiều người tụ tập tại Đền Tetragon, chờ đợi cô và các Nữ Tư Tế khác đưa ra lời tiên tri, điều gì đó hữu ích. Họ nói về việc tìm ra kết thúc bằng cách truy tìm khởi đầu, thay đổi kết cục bằng cách hiểu nguyên nhân. Họ muốn định hình một số phận tốt đẹp hơn, nhưng Iuno lại thấy mình không nói nên lời. Cô nhìn thấy hình bóng mẹ mình trước khi bị Triều Cường Tối chôn vùi. Cô thấy những tòa nhà sụp đổ, đám đông tán loạn, và mũi tên này đến mũi tên khác rời khỏi cung của cô, mỗi mũi đều bị bóng tối nuốt chửng trước khi kịp trúng đích.
 Chẳng có gì thay đổi. Cô có thể nhìn thấy. Nhưng đó là tất cả những gì số phận từng cho phép.
 Một đêm trắng khác. Iuno lại ngồi trước bàn tiên tri. Những gợn sóng lan tỏa trên mặt nước. Trong im lặng, cô nghĩ mình nghe thấy tiếng thì thầm:
 "Ngươi có thể nhìn thấy tất cả… nhưng nếu chỉ đứng nhìn, ngươi là gì?"
@@ -18412,17 +18412,17 @@
 Nó chưa bao giờ cho cô câu trả lời. Nhưng lần này, cô không cần.
 "Nếu ta không thể thay đổi những gì mình thấy… thì hãy đập vỡ nó."
 Vậy là cô giơ tay lên và chặt đứt tất cả. Dồn mọi dòng sức mạnh mình có thể điều khiển, với nụ cười ngông cuồng, thách thức, cô phóng mũi tên xuống.
-Mũi tên bắn ra không hề ồn ào, nhưng trong khoảnh khắc đó, nó đã ghim con đường ẩn giấu của High Tide Tối, đóng đinh nó giữa Septimont và định mệnh. Lần đầu tiên, lũ quái vật không thể lẩn trốn vô hình mà bị xé nát từng chút một bởi ánh sáng xanh trắng lóe lên.
-Nhưng cái giá phải trả? Sau trận chiến, tại một trại trên High Nguyên, mọi người nâng ly trong niềm nhẹ nhõm. Lửa reo, tiếng nói chồng chéo, lễ ăn mừng tự phát dâng trào. Iuno đứng ở rìa, xa ngọn lửa sáng nhất.
+Mũi tên bắn ra không hề ồn ào, nhưng trong khoảnh khắc đó, nó đã ghim con đường ẩn giấu của Triều Cường Tối, đóng đinh nó giữa Septimont và định mệnh. Lần đầu tiên, lũ quái vật không thể lẩn trốn vô hình mà bị xé nát từng chút một bởi ánh sáng xanh trắng lóe lên.
+Nhưng cái giá phải trả? Sau trận chiến, tại một trại trên Cao Nguyên, mọi người nâng ly trong niềm nhẹ nhõm. Lửa reo, tiếng nói chồng chéo, lễ ăn mừng tự phát dâng trào. Iuno đứng ở rìa, xa ngọn lửa sáng nhất.
 Có người để ý đến cô.
 "...Ai đấy?"
-"Ngươi ngốc à? Đó là Nữ Tư Tế đó… Khoan, tên gì nhỉ? Iuno?"
-"Nữ Iuno the Priestess á? Ý ngươi là thiên tài mà ai cũng nói đến ấy à?"
-"Lạ nhỉ. Sao ta chưa bao giờ nghe tên tuổi như vậy nhỉ?"
+"Mày ngốc à? Đó là Nữ Tư Tế đó… Khoan, tên gì nhỉ? Iuno?"
+"Nữ Tư Tế Iuno á? Ý mày là thiên tài mà ai cũng nói đến ấy à?"
+"Lạ nhỉ. Sao tao chưa bao giờ nghe tên tuổi như vậy nhỉ?"
 Một Chiến Binh trẻ tiến lại, ngập ngừng. Cậu ta nâng ly với vẻ lịch sự, giọng ngập ngừng. "Chị… chị cũng chiến đấu cùng bọn em lúc nãy phải không? Thôi, cứ đến tham gia ăn mừng đi."
-Iuno nhướn ngươi, không nói gì. Cô chỉ nâng ly lên và chạm nhẹ vào ly của cậu ta.
+Iuno nhướn mày, không nói gì. Cô chỉ nâng ly lên và chạm nhẹ vào ly của cậu ta.
 Sau đó, bên ngoài ánh đèn lồng, cô ngồi một mình bên bờ hồ, cằm đặt trên đầu gối, tiếng cười giấu trong khuỷu tay. Cô nhìn lại con đường mình đã đi và những bóng tối đã theo sau. Một số đang mờ dần, số khác đã nứt vỡ. Cô nghe thấy tiếng gọi phía sau, nhưng không ai gọi tên cô. Cô thấy những ánh mắt từng nhìn cô, giờ đây trôi dạt trong sự bối rối và xa lạ. Chỉ mới đây thôi, họ đã gọi cô là "Iuno" với sự chắc chắn khi cô đưa ra lời tiên tri. Họ đã sát cánh cùng cô trước khi những mũi tên bay đi. Thế mà, tất cả những gì họ đã trải qua và sống sót giờ đây đang phai mờ.
-Bên hồ, cô chạm ngón tay vào mặt nước, những gợn sóng làm vỡ tan hình ảnh phản chiếu. Cô thấy chính mình trong nước. Đường Dodget rõ ràng, nhưng luôn bị che mờ. Cô đưa tay vào nước, cố chạm vào khuôn mặt. Khi ngón tay cô chạm vào, hình ảnh phản chiếu run rẩy, như thể cố chạy trốn.
+Bên hồ, cô chạm ngón tay vào mặt nước, những gợn sóng làm vỡ tan hình ảnh phản chiếu. Cô thấy chính mình trong nước. Đường nét rõ ràng, nhưng luôn bị che mờ. Cô đưa tay vào nước, cố chạm vào khuôn mặt. Khi ngón tay cô chạm vào, hình ảnh phản chiếu run rẩy, như thể cố chạy trốn.
 "Đừng chạy," Iuno cười với mặt nước. "Ngay cả ngươi cũng không nhận ra ta nữa sao?"
 Mặt nước lại gợn sóng, như thể hình ảnh phản chiếu thì thầm đáp lại:
 "Ngươi có muốn được nhớ đến không?"
@@ -18533,7 +18533,7 @@
           <t>Tĩnh lặng. Chìm đắm. Cô độc. Thức tỉnh. 
 Trong vòng luân hồi bất tận này, đôi khi Iuno thấy mình lạc vào những khoảnh khắc không thuộc về quá khứ của nàng.
 Đêm không sao ấy, vầng trăng treo thấp hơn bao giờ hết, gần đến mức như sắp rơi vào lòng bàn tay đang mở của nàng khi ngồi trên mái nhà. Nàng không nhớ mình đã ngủ thiếp đi như thế nào. Hay có lẽ nàng chưa từng ngủ, chỉ đơn thuần trôi dạt, bị ánh trăng đưa đẩy vào một ảo ảnh dịu dàng mà nàng chưa từng mơ tới. Một sự phản kháng lặng lẽ, có lẽ, cho mũi tên nàng từng bắn lên trời… và lời thách thức nàng từng dám thốt ra.
-Nơi đó, không có &lt;te href=851023&gt;Dark Tide&lt;/te&gt;. Không có ngày tận thế. Chỉ có một cánh đồng lạ lùng mà quen thuộc. Trẻ con chạy chân trần dưới ánh mặt trời ban mai. Khói cuộn lên trong hoàng hôn. Một cô gái trạc tuổi nàng, nằm dài trên cành cây trĩu quả, chân đung đưa uể oải, Dodget mặt thư thái, tự do như cá lội trong biển đầy nắng. Iuno gần như có thể thấy nụ cười của cô gái ấy, lan tỏa như những vòng sóng trên mặt nước phẳng lặng.
+Nơi đó, không có &lt;te href=851023&gt;Dark Tide&lt;/te&gt;. Không có ngày tận thế. Chỉ có một cánh đồng lạ lùng mà quen thuộc. Trẻ con chạy chân trần dưới ánh mặt trời ban mai. Khói cuộn lên trong hoàng hôn. Một cô gái trạc tuổi nàng, nằm dài trên cành cây trĩu quả, chân đung đưa uể oải, nét mặt thư thái, tự do như cá lội trong biển đầy nắng. Iuno gần như có thể thấy nụ cười của cô gái ấy, lan tỏa như những vòng sóng trên mặt nước phẳng lặng.
 "Ngươi thấy chứ?" vầng trăng cất tiếng, giọng ấm áp như mật ong. "Đây cũng là một cách để sống."
 Iuno không trả lời. Nàng chỉ lặng nhìn phiên bản khác của mình vẫy tay với ai đó ở xa, rồi nhẹ nhàng đu xuống khỏi cây và khẽ giũ váy một cách tinh nghịch.
 "Đó là ngươi đấy," giọng nói thì thầm. "Ảo ảnh có ma lực như thế. Ngươi có thể nhìn thấy tuyết và biển cả mà mình chưa từng biết… những cuộc đời mình chưa từng sống."
@@ -18664,17 +18664,17 @@
 Vậy nên nàng tiếp tục.
 Trôi từ vòng luân hồi đổ vỡ này sang vòng khác, luân chuyển qua những bản thể mượn tạm trong mơ hồ, cho đến một khoảnh khắc, nàng đưa tay ra. Và lần đầu tiên, hơi ấm của một người khác chạm vào nàng.
 Kẻ Vô Danh. Sinh vật đầu tiên trong hỗn mang này không phải là tiếng vọng của nàng.
-{Male=Anh;Female=Cô} ấy nhìn thấy nàng như chính nàng đang hiện hữu, lơ lửng giữa ánh trăng và Dark Tide.
+{Male=him;Female=her} ấy nhìn thấy nàng như chính nàng đang hiện hữu, lơ lửng giữa ánh trăng và Dark Tide.
 “…Iuno.”
-Mọi thứ thay đổi ngay khoảnh khắc {Male=anh;Female=cô} ấy cất tiếng gọi tên nàng. {Male=Anh;Female=Cô} ấy nhớ ra. Và vì thế, nàng cũng vậy. Hai ngoại lệ, trong một nơi đáng lẽ không nên tồn tại ký ức. Và đột nhiên, hỗn mang không còn cảm giác vô tận nữa.
-“Where are you taking me?” Kẻ Vô Danh bước bên nàng, giọng nói nhẹ nhàng, như hòn đá khẽ chạm mặt nước.
+Mọi thứ thay đổi ngay khoảnh khắc {Male=he;Female=she} ấy cất tiếng gọi tên nàng. {Male=He;Female=She} ấy nhớ ra. Và vì thế, nàng cũng vậy. Hai ngoại lệ, trong một nơi đáng lẽ không nên tồn tại ký ức. Và đột nhiên, hỗn mang không còn cảm giác vô tận nữa.
+“Cậu định đưa tớ đi đâu?” Kẻ Vô Danh bước bên nàng, giọng nói nhẹ nhàng, như hòn đá khẽ chạm mặt nước.
 Iuno mỉm cười nhạt. “Để hoàn thành một điều gì đó. Hoặc có lẽ… để bắt đầu lại.”
 Họ chia tay, chỉ để gặp lại nhau trên chiến trường nơi mọi chuyện bắt đầu. Dưới vầng trăng vỡ, dấu vết của sự hy sinh của nàng vẫn còn đó. Một bằng chứng mà số phận không thể xóa nhòa. Một khe hẹp để nàng bước qua.
-“Nếu cậu bước qua, cậu sẽ trở về khoảnh khắc đó. Với {Male=anh ấy;Female=cô ấy}, cậu sẽ Anchor bản thân đã bị lãng quên. Nhưng tất cả những gì cậu từng Anchor trước đây, tất cả những gì cậu muốn Anchor, thậm chí cả số phận, sẽ cần phải được Anchor lại. Cậu có hiểu điều đó báo hiệu điều gì không?”
+“Nếu cậu bước qua, cậu sẽ trở về khoảnh khắc đó. Với {Male=him;Female=her}, cậu sẽ Anchor bản thân đã bị lãng quên. Nhưng tất cả những gì cậu từng Anchor trước đây, tất cả những gì cậu muốn Anchor, thậm chí cả số phận, sẽ cần phải được Anchor lại. Cậu có hiểu điều đó báo hiệu điều gì không?”
 Nàng nghe thấy chính giọng mình. Nghe như một lời cảnh báo, hoặc một lời thuyết phục.
 Iuno ngẩng mặt, nhìn thẳng vào vầng trăng.
 “…Tớ hiểu.”
-Nàng nói gần như thờ ơ. Vẻ mặt vẫn mang Dodget kiêu hãnh quen thuộc.
+Nàng nói gần như thờ ơ. Vẻ mặt vẫn mang nét kiêu hãnh quen thuộc.
 “Tớ từng nghĩ nếu nhìn thấy nhiều hơn, dự đoán nhiều hơn, tớ có thể thay đổi điều gì đó. Rằng tri thức sẽ cho tớ sức mạnh. Nhưng càng nhìn thấy nhiều, tớ càng bị mắc kẹt bởi nó.”
 Kẻ Vô Danh im lặng, chỉ quan sát nàng.
 Iuno giơ tay lên. Những dấu vết còn sót lại của quá khứ tụ lại thành một hình hài, hiện ra một mũi Moon Arrow khác. Bộ lông vũ của nó phát sáng bạc và xanh nhạt, như khoảnh khắc yên lặng trước bình minh.
@@ -18686,7 +18686,7 @@
 Khi nàng cuối cùng bước ra khỏi khoảng không vô tận của khả năng và trở lại thế giới của lễ hội, cánh hoa rơi từ trên trời như mưa.
 Dưới ánh lửa, ai đó nâng ly rượu lên và bắt gặp ánh mắt nàng. Anh ta chớp mắt đầy bối rối.
 “Cậu, ừm… Kỳ lạ thật. Tớ không nghĩ chúng ta đã gặp nhau, nhưng… tớ có cảm giác như đã biết cậu?”
-Iuno nhướn ngươi, không nói gì, như trước đây. Nàng nâng ly lên và chạm nhẹ vào ly của anh ta.
+Iuno nhướn mày, không nói gì, như trước đây. Nàng nâng ly lên và chạm nhẹ vào ly của anh ta.
 Sau đêm đó, không ai còn nhớ đến cô gái đã bắn một mũi tên xuyên qua số phận. Nhưng từ đó trở đi, mặt trăng của Iuno không còn đơn thuần là tròn khuyết. Nó quay đi quay lại, không phải trong sự lặp lại, mà trong sự đổi mới.
 Nàng đã viết nên ý nghĩa của riêng mình vào vòng luân hồi. Và giờ đây, nó tiếp tục, luôn thay đổi, luôn thuộc về nàng.</t>
         </is>
@@ -21750,7 +21750,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Giữ vững đến Hồi 15 và hoàn thành thành công "Bài Kiểm Tra Defense Toàn Diện" trong "Mô Phỏng Defense Thủy Triều".
+          <t>Giữ vững đến Hồi 15 và hoàn thành thành công "Bài Kiểm Tra Phòng Ngự Toàn Diện" trong "Mô Phỏng Phòng Ngự Thủy Triều".
 Chỉ khả dụng trong thời gian nhận thưởng giới hạn của sự kiện.</t>
         </is>
       </c>
@@ -21817,9 +21817,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>-
-- Xuất hiện &lt;color=HighlightB&gt;Fusion Drake&lt;/color&gt; cấp Common cận chiến với tần suất cao hơn.
-- Lần đầu xuất hiện &lt;color=HighlightB&gt;Tambourinist&lt;/color&gt; cấp Tinh nhuệ tầm xa.</t>
+          <t>- Tăng tần suất xuất hiện &lt;color=HighlightB&gt;Fusion Drake&lt;/color&gt; cấp Common cận chiến.</t>
         </is>
       </c>
     </row>
@@ -21885,8 +21883,8 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>- Tăng tần suất xuất hiện &lt;color=HighlightB&gt;Vitreum Dancers&lt;/color&gt; cận chiến hạng Elite.
-- Lần đầu xuất hiện &lt;color=HighlightB&gt;Rocksteady Guardian&lt;/color&gt; cận chiến hạng Elite.</t>
+          <t>- Tăng tần suất xuất hiện &lt;color=HighlightB&gt;Vitreum Dancers&lt;/color&gt; cận chiến hạng Tinh Anh.
+- Lần đầu xuất hiện &lt;color=HighlightB&gt;Rocksteady Guardian&lt;/color&gt; cận chiến hạng Tinh Anh.</t>
         </is>
       </c>
     </row>
@@ -21953,7 +21951,7 @@
       <c r="M314" t="inlineStr">
         <is>
           <t>- Tăng tần suất xuất hiện kẻ địch tầm xa hạng Phổ Thông &lt;color=HighlightB&gt;Whiff Whaff&lt;/color&gt;.
-- Lần đầu xuất hiện &lt;color=HighlightB&gt;Chasm Guardian&lt;/color&gt; cận chiến hạng Elite.</t>
+- Lần đầu xuất hiện &lt;color=HighlightB&gt;Chasm Guardian&lt;/color&gt; cận chiến hạng Tinh Anh.</t>
         </is>
       </c>
     </row>
@@ -22020,7 +22018,7 @@
       <c r="M315" t="inlineStr">
         <is>
           <t>- Tăng tần suất xuất hiện kẻ địch tầm xa hạng Phổ Thông &lt;color=HighlightB&gt;Devotee's Flesh&lt;/color&gt;.
-- Lần đầu xuất hiện &lt;color=HighlightB&gt;Pilgrim's Shell&lt;/color&gt; tầm xa hạng Elite.</t>
+- Lần đầu xuất hiện &lt;color=HighlightB&gt;Pilgrim's Shell&lt;/color&gt; tầm xa hạng Tinh Anh.</t>
         </is>
       </c>
     </row>
@@ -22156,7 +22154,7 @@
       <c r="M317" t="inlineStr">
         <is>
           <t>Một mảnh ghi chép còn dang dở bỏ lại tại trại. Nó chứa đựng những quan sát, lời khuyên thực tế và những mảnh ký ức cá nhân của một thợ săn.
-1. Các Nữ Tư Tế của Tetragon Temple đã nói: Đại Triều sắp tới sẽ mang theo sự gia tăng bất thường cả về số lượng lẫn hung dữ của lũ Dark Tide. Điều đó có nghĩa là trong chuyến săn này, mỗi người chúng ta phải hạ gấp đôi số lượng thông thường. Thời gian không còn nhiều, và nhiệm vụ này thật khó khăn.
+1. Các Nữ Tư Tế của Đền Tetragon đã nói: Đại Triều sắp tới sẽ mang theo sự gia tăng bất thường cả về số lượng lẫn hung dữ của lũ Dark Tide. Điều đó có nghĩa là trong chuyến săn này, mỗi người chúng ta phải hạ gấp đôi số lượng thông thường. Thời gian không còn nhiều, và nhiệm vụ này thật khó khăn.
 2. Đội vận chuyển từ Atilius Canyon cũng đã tăng tốc, đảm bảo cung cấp đầy đủ vật tư cho chúng ta. Họ thậm chí còn mang theo loại nước tăng lực mới đang thịnh hành mà ai cũng bàn tán. Ta thử một ngụm… vị thật kỳ lạ. Có lẽ ta sẽ để phần còn lại cho đám trẻ.
 3. Số lượng tân binh ở Hunter's Den nhiều hơn ta tưởng. Những đấu sĩ mới từ Agons thường gặp khó khăn khi ra ngoài hoang dã. Họ thiếu kinh nghiệm và bản lĩnh cho những chuyến săn thực sự, và nguy cơ mất mạng ngay trong lần đầu ra trận là rất cao. Có lẽ ta cần dành thời gian chia sẻ những gì mình đã học được.</t>
         </is>
@@ -22427,7 +22425,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Mã thông báo của &lt;te href=260001&gt;Internal Security Agency&lt;/te&gt; Mingting mà Qiuyuan luôn mang theo. Lẽ ra nó phải bị tịch thu cùng bộ đồng phục khi anh rời khỏi cơ quan, nhưng ai đó trong Mingting đã đảm bảo anh được giữ lại.
+          <t>Mã thông báo của &lt;te href=260001&gt;Cơ quan An ninh Nội bộ&lt;/te&gt; Mingting mà Qiuyuan luôn mang theo. Lẽ ra nó phải bị tịch thu cùng bộ đồng phục khi anh rời khỏi cơ quan, nhưng ai đó trong Mingting đã đảm bảo anh được giữ lại.
 "...Ta giao phó vật này cho ngươi. Hãy để tất cả quan chức các bang biết: kẻ nào mang mã thông báo này, kẻ đó mang theo uy quyền của ta."</t>
         </is>
       </c>
@@ -22637,8 +22635,8 @@
         <is>
           <t>Một món đồ thủ công do Galbrena làm, dệt từ chính lông vũ của cô cùng những vật liệu thông thường được lựa chọn cẩn thận. Mỗi chi tiết đều mang theo một điều ước thầm lặng.
 Đối với Galbrena, một giấc ngủ yên bình là điều xa xỉ hiếm có. Cô thường bị quấy rối bởi những Tacet Discord bên trong mình, buộc phải giao tranh với chúng hết lần này đến lần khác trong những giấc mơ chồng chất. Cô từng cố tìm cách thoát khỏi vòng luẩn quẩn, hy vọng món đồ thủ công này có thể bảo vệ những khoảnh khắc nghỉ ngơi ngắn ngủi của mình... Nhưng kết quả thường không như ý.
-Thế rồi mọi thứ thay đổi khi cô bắt đầu tặng chúng cho trẻ em. Sức mạnh thật sự của món đồ thủ công mới lộ diện: trong giấc mơ của chúng, mỗi khi "Nightmare" ập đến, một người phụ nữ áo trắng sẽ xuất hiện, xua đuổi quái vật, dẫn dắt bọn trẻ thoát khỏi bóng tối và canh giữ cho đến khi bình minh.
-Chimera giải thích với Galbrena rằng lông vũ mang theo tần số của cô, có thể đẩy lùi "Nightmare Tacet Discord". Nhưng đối với những kẻ đã trú ngụ bên trong cô, chúng chẳng thể làm gì.
+Thế rồi mọi thứ thay đổi khi cô bắt đầu tặng chúng cho trẻ em. Sức mạnh thật sự của món đồ thủ công mới lộ diện: trong giấc mơ của chúng, mỗi khi "Ác Mộng" ập đến, một người phụ nữ áo trắng sẽ xuất hiện, xua đuổi quái vật, dẫn dắt bọn trẻ thoát khỏi bóng tối và canh giữ cho đến khi bình minh.
+Chimera giải thích với Galbrena rằng lông vũ mang theo tần số của cô, có thể đẩy lùi "Tacet Discord Ác Mộng". Nhưng đối với những kẻ đã trú ngụ bên trong cô, chúng chẳng thể làm gì.
 Suy nghĩ ấy mang đến cho cô một nỗi buồn lặng lẽ... nhưng cũng là một sự thanh thản. Ít ra, số phận của cô không chỉ toàn là nỗi sợ hãi.</t>
         </is>
       </c>
@@ -22721,9 +22719,9 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>"Mỗi ngọn núi đều là một thử thách. Vượt qua được nó, cậu có thể tự chọn con đường của mình. Fail… thì ngọn núi này sẽ giữ lại tất cả những gì cậu có."
+          <t>"Mỗi ngọn núi đều là một thử thách. Vượt qua được nó, cậu có thể tự chọn con đường của mình. Thất bại… thì ngọn núi này sẽ giữ lại tất cả những gì cậu có."
 Đó là những lời đầu tiên Qiuyuan nghe từ ông lão cách đây năm năm, giữa địa ngục lửa và máu. Những lời không thể nào quên.
-Cậu gọi ông là Master, dù chưa bao giờ thấy mặt ông. Một lão già râu trắng trong bộ quần áo rách rưới, có lẽ thế. Ông lão đã huấn luyện Qiuyuan không ngừng nghỉ, dạy cậu võ công sắc bén đến mức có thể "nhìn" thấy rừng trúc lay động trong tâm trí.
+Cậu gọi ông là Sư phụ, dù chưa bao giờ thấy mặt ông. Một lão già râu trắng trong bộ quần áo rách rưới, có lẽ thế. Ông lão đã huấn luyện Qiuyuan không ngừng nghỉ, dạy cậu võ công sắc bén đến mức có thể "nhìn" thấy rừng trúc lay động trong tâm trí.
 Tin đồn về sư phụ cậu lan truyền như sương mù. Người thì bảo ông là Kiếm Ma của Chongzhou, kẻ sát nhân để lại hàng dài xác chết sau lưng. Kẻ thì thì thầm rằng ông từng là danh tướng của &lt;te href=260009&gt;Mingting&lt;/te&gt;, chinh phục bao vùng đất rộng lớn, quyền uy gần sánh ngang với Huanglong, rồi lặng lẽ biến mất sau một lần sa cơ. Cũng có người bảo ông chỉ là huyền thoại. Ai mà tin được một kẻ phàm trần có thể diệt cả núi Tacet Discord chỉ bằng một cây trúc?
 Nhưng Qiuyuan tin. Năm năm qua, cậu giành vô số chiến thắng, nhưng chưa bao giờ đánh bại được sư phụ mình.
 "Năm năm trước, sư phụ cũng nói y như vậy."
@@ -22837,7 +22835,7 @@
           <t>"Hah… bao nhiêu sức mạnh phí hoài nơi hoang dã. Ngươi sẽ trả lời thế nào cho những sinh mạng đã ngã xuống dưới lưỡi kiếm của mình?"
 "Ngươi nhầm người rồi. Thưa bác sĩ, lại có bệnh nhân đến rồi đấy."
 Qiuyuan phớt lờ người đàn ông lớn tuổi và tiếp tục nhóm lửa dưới bếp. Ban đầu, ông ta chỉ ghé qua trò chuyện phiếm với bác sĩ Trương. Nhưng dần dà, ông ta xuất hiện thường xuyên hơn, thốt ra những câu đố và lời vô nghĩa.
-Lần này, đột nhiên ông ta Dodgem một khối sắt to bằng nắm tay về phía Qiuyuan. Bản năng đã chiếm lấy anh. Qiuyuan giơ tay lên, đỡ lấy nó ngay trước trán mà không hề nao núng.
+Lần này, đột nhiên ông ta ném một khối sắt to bằng nắm tay về phía Qiuyuan. Bản năng đã chiếm lấy anh. Qiuyuan giơ tay lên, đỡ lấy nó ngay trước trán mà không hề nao núng.
 "Ông là bạn của bác sĩ, sao lại đối xử với tôi như vậy?"
 "Ngươi nên nhận ra thứ mình đang cầm."
 Cái đầu thú bằng thép tinh xảo tỏa ra hơi lạnh thấu xương. Đúng rồi, không thể nhầm lẫn được.
@@ -22850,16 +22848,16 @@
 "…"
 "Máu phải trả bằng máu. Đó là quy luật tự nhiên. Có lẽ cái thòng lọng là kết cục của ngươi, nhưng trước đó, ngươi ít nhất cũng có thể chuộc lại phần nào những gì mình đã gây ra."
 "Đi theo ta. Ta không thể tha cho ngươi khỏi án tử hình, nhưng ta có thể hứa với ngươi điều này—ngươi sẽ không phải thối rữa trong ngục tối, cũng không phải chết dần chết mòn trên giường bệnh."
-Qiuyuan quá rõ sức mạnh của &lt;te href=260009&gt;Mingting&lt;/te&gt; ISA. Cái đầu sắt của mãnh thú Qiongqi, được ban tặng bởi quyền lực tối cao của &lt;te href=850093&gt;Huanglong&lt;/te&gt;, chính là hiện thân của Hoàng đế. Bất cứ nơi nào nó xuất hiện, các quan chức đều phải cúi đầu. Những sứ giả của nó đi khắp nơi không bị ràng buộc bởi bất kỳ tòa án nào, chỉ nghe lệnh từ ngai vàng, được giao phó những nhiệm vụ trọng đại nhất. Nếu họ muốn lấy mạng ai, thì ngay cả cái chết cũng không dám can thiệp.
-"Ngươi có thể vung kiếm vì bản thân, nhưng cũng có thể vì đại nghĩa. Phục vụ Mingting, trừng phạt kẻ ác, bảo vệ người vô tội."
+Qiuyuan quá rõ sức mạnh của &lt;te href=260009&gt;Minh Đình&lt;/te&gt; ISA. Cái đầu sắt của mãnh thú Qiongqi, được ban tặng bởi quyền lực tối cao của &lt;te href=850093&gt;Huanglong&lt;/te&gt;, chính là hiện thân của Hoàng đế. Bất cứ nơi nào nó xuất hiện, các quan chức đều phải cúi đầu. Những sứ giả của nó đi khắp nơi không bị ràng buộc bởi bất kỳ tòa án nào, chỉ nghe lệnh từ ngai vàng, được giao phó những nhiệm vụ trọng đại nhất. Nếu họ muốn lấy mạng ai, thì ngay cả cái chết cũng không dám can thiệp.
+"Ngươi có thể vung kiếm vì bản thân, nhưng cũng có thể vì đại nghĩa. Phục vụ Minh Đình, trừng phạt kẻ ác, bảo vệ người vô tội."
 "Tôi chỉ là một kẻ mù lòa. Gánh nặng của đại nghĩa quá sức chịu đựng của tôi."
 Người đàn ông nhặt một khúc củi lên và nhìn chằm chằm vào bếp lửa.
-"Ngươi có biết tại sao bác sĩ Trương rời Mingting không?"
+"Ngươi có biết tại sao bác sĩ Trương rời Minh Đình không?"
 "…Không. Ông ấy chưa bao giờ nói, và tôi cũng không hỏi."
 "Để cứu tất cả, thay vì chỉ cứu một người."
-Người đàn ông Dodgem khúc củi vào bếp và không nói thêm lời nào.
+Người đàn ông ném khúc củi vào bếp và không nói thêm lời nào.
 Ba ngày sau, Qiuyuan đứng cùng người đàn ông trước cửa lều. Sương núi trong thung lũng sâu Trùng Châu vẫn chưa thấm ướt vành nón rơm của họ. Không có khói bốc lên từ ống khói. Chỉ có ánh bình minh nhạt nhòa chạm vào họ.
-"Hẳn ông ấy đã nói cho ngươi biết lý do ta rời Mingting rồi… Hừm.
+"Hẳn ông ấy đã nói cho ngươi biết lý do ta rời Minh Đình rồi… Hừm.
 Kẻ từ Cơ Quan An Ninh Nội Bộ đó… cũng giống ta, cứng đầu cứng cổ. Nhưng có lẽ chính vì thế mà hắn mới thuyết phục được ngươi đi theo.
 Thế giới này rộng lớn. Ta chỉ có thể cố gắng hết sức để cứu nhiều mạng hơn. Nhưng hắn, Lương Đông Nguyên… mới là người có thể 'cứu' người ta trong chốn công đường.
 Giờ đã đến. Đi đi. Ở lại đây lâu, ngươi chỉ khiến bệnh nhân của ta sợ hãi mà thôi."
@@ -22967,14 +22965,14 @@
 "Nhưng thưa Ngài Bộ Trưởng, buổi hành quyết sắp bắt đầu—"
 "Mở ra."
 Cánh cửa sắt kẽo kẹt khi trượt mở. Một người đàn ông bước vào, mang theo hương thơm thoang thoảng của rượu và thức ăn.
-"Giờ thì sao? Ngươi đến đây để giám sát thay cho &lt;te href=260002&gt;Ministry of Sentinel Affairs&lt;/te&gt; à?"
+"Giờ thì sao? Ngươi đến đây để giám sát thay cho &lt;te href=260002&gt;Bộ Sự Vụ Cảnh Vệ&lt;/te&gt; à?"
 "Tha lỗi cho tôi, thưa Bộ Trưởng… Tôi chỉ đang thi hành nhiệm vụ."
-"Very well. Vậy thì ngươi hẳn biết Ministry of Sentinel Affairs phải thẩm vấn mọi tội nhân trước khi hành quyết. Giờ ta cũng phải làm tròn bổn phận của mình. Đi đi. Tất cả các ngươi."
+"Được thôi. Vậy thì ngươi hẳn biết Bộ Sự Vụ Cảnh Vệ phải thẩm vấn mọi tội nhân trước khi hành quyết. Giờ ta cũng phải làm tròn bổn phận của mình. Đi đi. Tất cả các ngươi."
 "Tuân lệnh…"
 "Và khóa cửa lại. Ta sẽ gọi khi xong việc."
 Tiếng bước chân vội vã dần xa, chỉ còn lại hai người trong ngục.
 "Buổi hành quyết được ấn định vào giờ Ngọ, phút thứ bốn mươi lăm. Ngươi đến sớm hơn một tiếng rưỡi đấy."
-"…Ngài đến đây để tiễn biệt ta sao, Master Lâm?"
+"…Ngài đến đây để tiễn biệt ta sao, Sư phụ Lâm?"
 "Trước hết, uống cái này đi. Cùng nâng ly tưởng nhớ ông ấy."
 Qiuyuan từ từ đứng dậy, xiềng xích nặng nề kéo lê trên mặt đất. Hắn cầm lấy chén rượu, nhưng thay vì uống, lại đổ rượu xuống đất—một lễ vật dâng người đã khuất.
 "Than ôi… Chỉ có mình ngươi chứng kiến cái chết thảm thương của Đông Nguyên. Vụ này nghiêm trọng đến mức ngay cả cấp trên cũng phải để mắt. Không còn dấu vết của hung thủ thật sự, Ủy Ban Tư Pháp đành phải lấy ngươi làm vật tế thần."
@@ -22983,13 +22981,13 @@
 "Ta sẽ không bao giờ quên tần số của hắn, dù hắn đã bị thiêu thành tro bụi."
 "Bộ đã lục soát mọi hồ sơ, nhưng không hề có ghi chép nào về một Resonator có thể chiếm đoạt hình hài và thân thể người khác."
 "…Ta không dám chắc liệu có còn mảnh linh hồn nào của Đại sư phụ Lương sót lại trong khoảnh khắc đó."
-"Có lẽ Đông Nguyên đã không còn là chính mình khi hắn giao cho ngươi vụ án ở Jinzhou. Một người chính trực như hắn sẽ không bao giờ ra lệnh truy đuổi một quan nhỏ chỉ vì giết Echo để bảo vệ dân lành."
+"Có lẽ Đông Nguyên đã không còn là chính mình khi hắn giao cho ngươi vụ án ở Jinzhou. Một người chính trực như hắn sẽ không bao giờ ra lệnh truy đuổi một quan nhỏ chỉ vì giết Tổ Tacet để bảo vệ dân lành."
 "Đó là lý do ta tha cho hắn—Gia Thư Lâm. Đại sư phụ Lương mà ta biết sẽ không bao giờ đưa ra mệnh lệnh như vậy."
 "Đông Nguyên chưa bao giờ nhìn nhầm người. Nếu ngươi muốn biết sự thật về cái chết của hắn, chỉ có thể bắt đầu từ vụ án đó. Dù ta e rằng… ngươi có thể sẽ không bao giờ làm sáng tỏ mọi chuyện."
 "Ta đã vấy máu quá nhiều. Nhưng nhờ ngươi, Đại sư phụ Lương và Bác sĩ Trương, ta đã được sống một cuộc đời khác, dù chỉ trong chốc lát… Ta chỉ có thể báo đáp niềm tin ấy trong kiếp sau thôi."
 Bộ Trưởng tiến về phía cửa ngục. Vẻ mặt ông nghiêm nghị, nhưng ánh mắt lại đầy sự vững chãi.
 "Đông Nguyên từng hứa rằng ngươi sẽ không chết trong ngục tối hay trên giường bệnh."
-"Theo luật pháp của &lt;te href=260009&gt;Mingting&lt;/te&gt;, để hành quyết một tội nhân như ngươi, Ủy Ban Tư Pháp phải nhận được chiếu chỉ do Hoàng Đế và &lt;te href=850083&gt;Cảnh Vệ&lt;/te&gt; phê chuẩn, chuyển qua Ministry of Sentinel Affairs. Việc hành quyết chỉ được tiến hành một giờ sau khi nhận chiếu chỉ."
+"Theo luật pháp của &lt;te href=260009&gt;Minh Đình&lt;/te&gt;, để hành quyết một tội nhân như ngươi, Ủy Ban Tư Pháp phải nhận được chiếu chỉ do Hoàng Đế và &lt;te href=850083&gt;Cảnh Vệ&lt;/te&gt; phê chuẩn, chuyển qua Bộ Sự Vụ Cảnh Vệ. Việc hành quyết chỉ được tiến hành một giờ sau khi nhận chiếu chỉ."
 "Nếu chiếu chỉ chưa được trả về, không ai dám động tay đến ngươi."
 "Vì vậy, Qiuyuan, hãy nhớ: từ giờ trở đi, con đường phía trước chỉ có một mình ngươi. Dù phải đánh đổi cả mạng sống, ngươi cũng phải làm sáng tỏ vụ án này. Nếu ngươi phải chết, hãy chết trên con đường báo thù cho Đông Nguyên."</t>
         </is>
@@ -23085,12 +23083,12 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Năm năm đã trôi qua kể từ khi hắn trốn khỏi &lt;te href=260009&gt;Mingting&lt;/te&gt; và trở thành kẻ đào vong bị truy nã khắp sáu thành phố.
-Trong khi Mingting vẫn không đổi—nhộn nhịp và phồn vinh, thì quần áo của hắn đã sờn rách, bám đầy bụi và sương giá của cuộc hành trình bất tận qua Huanglong. Thượng thư Lâm của &lt;te href=260002&gt;Bộ Sự Vụ Cảnh Giới&lt;/te&gt; đã lâm bệnh và từ quan. Chàng trai từng sống sót sau lưỡi kiếm của hắn giờ đã trở thành tướng quân trấn giữ biên cương, nhưng rồi cũng gục ngã trước cơn điên loạn của Threnodian.
+          <t>Năm năm đã trôi qua kể từ khi hắn trốn khỏi &lt;te href=260009&gt;Minh Đình&lt;/te&gt; và trở thành kẻ đào vong bị truy nã khắp sáu thành phố.
+Trong khi Minh Đình vẫn không đổi—nhộn nhịp và phồn vinh, thì quần áo của hắn đã sờn rách, bám đầy bụi và sương giá của cuộc hành trình bất tận qua Huanglong. Thượng thư Lâm của &lt;te href=260002&gt;Bộ Sự Vụ Cảnh Giới&lt;/te&gt; đã lâm bệnh và từ quan. Chàng trai từng sống sót sau lưỡi kiếm của hắn giờ đã trở thành tướng quân trấn giữ biên cương, nhưng rồi cũng gục ngã trước cơn điên loạn của Threnodian.
 Sư phụ từng dạy hắn khi nào nên rút kiếm, khi nào nên tra kiếm vào vỏ. Thế nhưng khi hắn kiềm chế, mọi thứ đã rơi xuống vực thẳm.
 Vị lương y từng nói rằng kiếm có thể giết người, cũng có thể cứu người. Nhưng hắn đã không cứu được người mình muốn.
 Số phận xoay vần không ngừng. Mọi thứ đã đổi thay, nhưng dường như chẳng có gì thực sự thay đổi. Hắn vẫn chưa tìm ra kẻ đã sát hại Sư tổ Lương. Nhưng hắn chưa bao giờ ngừng truy tìm sự thật.
-Nếu Thượng thư Lâm không gửi tin báo về manh mối từ &lt;te href=260008&gt;Grand Marshal&lt;/te&gt;, người đứng đầu &lt;te href=260010&gt;Ministry of War&lt;/te&gt;, có lẽ hắn đã không dám trở lại Mingting.
+Nếu Thượng thư Lâm không gửi tin báo về manh mối từ &lt;te href=260008&gt;Đại Nguyên Soái&lt;/te&gt;, người đứng đầu &lt;te href=260010&gt;Bộ Chiến Tranh&lt;/te&gt;, có lẽ hắn đã không dám trở lại Minh Đình.
 "Ngươi đến rồi à."
 Giữa cơn mưa như trút, một bóng người đội nón lá hiện ra từ dưới bóng cầu, khuôn mặt khuất sau vành nón.
 "Scar, Giám sát viên Fractsidus, đã trốn khỏi nhà lao Jinzhou cách đây không lâu.
@@ -23104,15 +23102,15 @@
 "Cô ấy có thể sẽ không gặp ta."
 "Sẽ gặp. Các ngươi là gia đình. Cô ấy sẽ tin lời ngươi. Ngoài ra… {PlayerName} cũng đang ở Rinascita."
 "…{PlayerName} đó sao?"
-"Đúng. Ngươi có thể hỏi {Male=anh ấy;Female=cô ấy} về những gì đã xảy ra ở Jinzhou."
+"Đúng. Ngươi có thể hỏi {Male=him;Female=her} về những gì đã xảy ra ở Jinzhou."
 "…Ta hiểu rồi. Đưa ta hồ sơ. Ta sẽ lên đường ngay."
 Cửu Uyên quay người đi, nhưng bóng người kia gọi lại.
-"Khoan! Vì ngươi đã trở về, hãy ghé thăm Đông Uyên. Ta biết ngươi vẫn dâng hương cho mộ ông ấy mỗi năm."
+"Đợi đã! Vì ngươi đã trở về, hãy ghé thăm Đông Uyên. Ta biết ngươi vẫn dâng hương cho mộ ông ấy mỗi năm."
 "Ta sẽ tìm manh mối trước, rồi trở về thắp hương cho ông ấy. Còn tên tội phạm ngươi nhắc tới…"
 "Bắt được thì bắt, không thì giết. Ta sẽ lo liệu với Ủy ban Tư pháp."
 "Ta hiểu rồi."
 Cửu Uyên gật đầu, rồi biến mất vào màn mưa mà không nói thêm lời nào.
-Hắn biết mình đang gánh vác những âm mưu chốn cung đình vô hình. Mingting thậm chí còn không chính thức cử người đi bắt Scar. Một kẻ đào vong như hắn lại được giao trọng trách ấy. Nhưng hắn không quan tâm. Mục tiêu của hắn rất đơn giản: tìm ra sự thật mà hắn đã bị từ chối.
+Hắn biết mình đang gánh vác những âm mưu chốn cung đình vô hình. Minh Đình thậm chí còn không chính thức cử người đi bắt Scar. Một kẻ đào vong như hắn lại được giao trọng trách ấy. Nhưng hắn không quan tâm. Mục tiêu của hắn rất đơn giản: tìm ra sự thật mà hắn đã bị từ chối.
 Và khi ngày đó đến—khi mối thù đã trả, nợ nần đã đền đáp—thì liệu đó có phải là vỏ kiếm mà hắn hằng tìm kiếm?
 Có lẽ, khi về già, hắn sẽ biết.</t>
         </is>
@@ -23209,7 +23207,7 @@
       <c r="M329" t="inlineStr">
         <is>
           <t>Hoàng hôn. Cát bụi. Khói lửa. Bãi săn này chẳng tàn khốc hơn những nơi trước kia.
-Cô gái ngày nào giờ đã trở thành một người phụ nữ đầy sẹo. Dưới lớp áo rách nát, sát khí tỏa ra dữ dội đến mức ngay cả &lt;te href=850081&gt;Discord&lt;/te&gt; cũng phải tránh xa khi nàng đến gần.
+Cô gái ngày nào giờ đã trở thành một người phụ nữ đầy sẹo. Dưới lớp áo rách nát, sát khí tỏa ra dữ dội đến mức ngay cả &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; cũng phải tránh xa khi nàng đến gần.
 Thế nhưng, ngay cả nàng cũng chỉ như hạt cát trước thân hình sắt thép của Dullahan, hiệp sĩ không đầu đang tàn phá mảnh đất này. Hắn xuất hiện không một lời cảnh báo. Kiếm thép va chạm. Trong khoảnh khắc đó, Galbrena hiểu tại sao nàng không thể cảm nhận được hắn. Tần số của hắn quá mạnh, mạnh đến mức ngay cả &lt;te href=851023&gt;Dark Tide&lt;/te&gt; cũng không dám bén mảng. Nàng đã thả &lt;te href=260005&gt;Chimera&lt;/te&gt; ra từ lâu, để hắn tự do tàn sát... Nhưng ngay cả sự hung dữ của hắn cũng chỉ có thể làm chậm bước tiến của chiến mã.
 Chạy trốn? Ý nghĩ đó đã lướt qua đầu nàng không chỉ một lần. Nhưng chỉ cách vài trăm mét sau lưng, một người mẹ và đứa con đang chạy trốn để bảo toàn mạng sống. Mỗi giây nàng đứng lại là thêm một giây họ được sống. Họ sẽ mang lời cảnh báo đến bộ tộc ở phía xa, và có lẽ sẽ kêu gọi được viện binh để chặn bước tiến của Dullahan trước khi hắn đến gần cổng thành văn minh. Vì lý do đó, sự lựa chọn đã rõ ràng. Đây không phải về chiến thắng. Mà là về việc đứng vững, bất kể cái giá phải trả.
 Nàng không sợ chết, nhưng nàng từ chối gục ngã ở đây. Đôi cánh sắc bén của Harpyia đã gãy vụn. Giờ đây, vũ khí duy nhất còn lại của "Galbrena" là ngọn lửa địa ngục đang tàn lụi. Và trên chiến trường cằn cỗi này, chẳng còn chút hận thù nào để nuôi dưỡng ngọn lửa ấy.
@@ -23222,9 +23220,9 @@
 Nếu Beholder nói rằng giáp trụ của Dullahan không thể phá vỡ, thì hãy tin vào 'đôi mắt' của chính ngươi."
 Nàng không biết giọng nói đó thuộc về ai. Nhưng những lời ấy vang lên chân thật, thúc giục nàng tin vào bản năng, như nàng vẫn luôn làm.
 Hận thù và ngọn lửa trào dâng nơi đầu ngón tay. Mờ nhạt, nhưng đủ sắc bén để xuyên qua vết thương, đốt cháy máu thịt và thân thể nàng.
-Lưỡi đại kiếm của Dullahan lại một lần nữa giáng xuống. Nhưng lần này, nàng không đối đầu trực diện. Nàng lao thẳng vào khoảng trống nơi đầu hắn lẽ ra phải có, Dodgem mình vào bên trong bộ giáp rỗng tuếch. Ngọn lửa thiêu đốt nuốt chửng nàng. Nhưng như nàng đã đoán, đây chính là điểm yếu của hắn: ngọn lửa bên trong hắn yếu ớt hơn của nàng rất nhiều. Hai ngọn lửa va chạm, gầm rú bên trong bộ giáp sắt. Thân hình đồ sộ ấy run rẩy... Cho đến khi, cuối cùng, im lặng bao trùm.
+Lưỡi đại kiếm của Dullahan lại một lần nữa giáng xuống. Nhưng lần này, nàng không đối đầu trực diện. Nàng lao thẳng vào khoảng trống nơi đầu hắn lẽ ra phải có, ném mình vào bên trong bộ giáp rỗng tuếch. Ngọn lửa thiêu đốt nuốt chửng nàng. Nhưng như nàng đã đoán, đây chính là điểm yếu của hắn: ngọn lửa bên trong hắn yếu ớt hơn của nàng rất nhiều. Hai ngọn lửa va chạm, gầm rú bên trong bộ giáp sắt. Thân hình đồ sộ ấy run rẩy... Cho đến khi, cuối cùng, im lặng bao trùm.
 Lần tiếp theo nàng mở mắt, nàng đang nằm trong vòng tay của người mẹ và đứa trẻ.
-Alive? Galbrena biết ơn số phận. Nàng châm lửa nơi đầu ngón tay một lần nữa, sẵn sàng thiêu đốt chính mình—vui mừng vì vẫn còn có thể dùng lại chiêu thức ấy. Họ ngăn nàng lại, nhắc nhở rằng hiệp sĩ không đầu đã biến mất. Sau này, nàng sẽ nghe kể rằng khi viện binh đến, tất cả những gì họ thấy chỉ là một bình minh vàng rực trên chân trời. Và Galbrena, gục ngã một mình trên cát.
+Còn sống sao? Galbrena biết ơn số phận. Nàng châm lửa nơi đầu ngón tay một lần nữa, sẵn sàng thiêu đốt chính mình—vui mừng vì vẫn còn có thể dùng lại chiêu thức ấy. Họ ngăn nàng lại, nhắc nhở rằng hiệp sĩ không đầu đã biến mất. Sau này, nàng sẽ nghe kể rằng khi viện binh đến, tất cả những gì họ thấy chỉ là một bình minh vàng rực trên chân trời. Và Galbrena, gục ngã một mình trên cát.
 Mãi cho đến khi có người chỉ ra, nàng mới nhận ra cơ thể mình đã thay đổi. Trong cuộc đọ sức nội tại thuần khiết ấy, nàng đã chiến thắng. Tần số của Dullahan đã hòa vào máu thịt và xương cốt nàng. Sức mạnh tái sinh của hiệp sĩ không đầu đã chữa lành cơ thể gần như tan nát của nàng, xóa sạch cả những vết sẹo cũ kỹ nhất. Ác Quỷ Lửa Bất Tử, một cái tên giờ đây đã trở thành sự thật. Nhưng Galbrena không cảm nhận được chút ấm áp nào trong cuộc sống mới này. Tất cả những gì nàng biết là nàng có thể dùng lại chiêu thức ấy hết lần này đến lần khác, không bao giờ dứt.
 Bộ quần áo vốn đã rách nát giờ đây đã bị thiêu rụi. Một số người cố nhặt những chiếc lông vũ trắng vương vãi trên mặt đất, hy vọng dệt thành quần áo mới cho nàng. Nhưng nàng chỉ chạm vào những chiếc lông đen trên vai mình và nói, "Thế này là đủ rồi."
 Có lẽ Dullahan cũng đã sợ hãi bình minh rực rỡ ấy. Còn ai đã mang nó đến, nàng không biết. Có lẽ chỉ là trò đùa của tạo hóa? Còn những chiếc lông vũ trắng? Chỉ là di vật của những con chim bay ngang qua. Chúng chẳng liên quan gì đến nàng. Hơn nữa, màu đen hợp với nàng hơn nhiều.
@@ -23232,11 +23230,11 @@
 "Đó," hắn đáp, "là con quỷ cổ xưa và mạnh mẽ nhất bên trong ngươi."
 "Còn cổ xưa hơn cả ngươi sao?"
 "Tất nhiên. Nó đã là một phần của thân thể và linh hồn ngươi từ thuở ban đầu. Nếu không có nó, ta đã nuốt chửng ngươi từ lâu rồi. Chính nó đã giúp ngươi đánh bại 'Galbrena'."
-"Ta không nhớ đã hấp thụ Discord nào như vậy."
-"Không phải Discord... Ngươi thực sự không biết tên nó sao?"
+"Ta không nhớ đã hấp thụ Tacet Discord nào như vậy."
+"Không phải Tacet Discord... Ngươi thực sự không biết tên nó sao?"
 "Không."
 "...Sự thiếu hiểu biết của ngươi quả là đáng kinh ngạc. Làm sao ngươi có thể sống sót đến giờ?"
-"Đừng vòng vo nữa. Tell me."
+"Đừng vòng vo nữa. Nói đi."
 "...Thiên Thần. Tên nó... là Thiên Thần."</t>
         </is>
       </c>
@@ -23339,37 +23337,37 @@
       <c r="M330" t="inlineStr">
         <is>
           <t>Cô từng chĩa súng vào chính mình, nhưng đây không phải là giấc mơ của cô.
-Cô đã tiêu diệt vô số Tidespawn trong bóng tối vô tận. At last, kiệt sức và loạng choạng, cô gục ngã trên mặt nước đen kịt. Một lần nữa, cô lại sa vào lưới định mệnh.
-"Không… Ta không thể gục ngã ở đây. Vẫn còn quá nhiều việc chưa hoàn thành. Ta đã hứa với {Male=anh ấy;Female=cô ấy}… Ta không được gục ngã ở đây."
+Cô đã tiêu diệt vô số Tidespawn trong bóng tối vô tận. Cuối cùng, kiệt sức và loạng choạng, cô gục ngã trên mặt nước đen kịt. Một lần nữa, cô lại sa vào lưới định mệnh.
+"Không… Ta không thể gục ngã ở đây. Vẫn còn quá nhiều việc chưa hoàn thành. Ta đã hứa với {Male=him;Female=her}… Ta không được gục ngã ở đây."
 Khi mở mắt ra lần nữa, &lt;te href=260006&gt;Fabianum&lt;/te&gt; hiện ra trước mắt. Những đối thủ, bạn bè, gia đình… tất cả đều mỉm cười ấm áp khi bước về phía cô.
 Nhưng đây có phải là ảo ảnh khác do &lt;te href=850074&gt;Threnodian&lt;/te&gt; tạo ra? Liệu Leviathan có nghĩ cô sợ hạnh phúc? Hay đúng hơn, một hạnh phúc không xứng đáng? Bởi làm sao một kẻ mang trong mình sức mạnh đen tối như cô có thể được nhìn nhận, được chấp nhận, và được yêu thương?
 Đã có lúc cô vật lộn với câu hỏi đó. Nhưng giờ đây, cô không còn cần câu trả lời nữa. Cô chỉ cần nhớ mục tiêu của mình. Cô đứng dậy, thắp sáng ngọn lửa, nạp đạn vào nòng, và chĩa súng vào "người bạn cũ" trước mặt.
 "Hahaha! Cô bé à, xem ra ngươi đã tôi luyện mình thành một lưỡi dao sắc bén rồi đấy."
 Nếu đây là giấc mơ, tiếng cười của chú Filo nghe quá chân thật. Nhưng khi nhìn thấy dấu vết của sự tha hóa từ Dark Tide trên họ, cô cuối cùng cũng hiểu ra: những người từng trao cho cô mọi tần số của họ, những người đáng lẽ đã trở thành đồng loại của Leviathan, vẫn đang chống lại sự ôm ấp của Hắn. Suốt mấy thập kỷ, họ đã từ chối "món quà" ấy. Và vì thế, Leviathan đã đẩy họ vào vực sâu nhất của Dark Tide, kết án họ chịu đựng khổ đau vô tận.
 Cô im lặng. Trên hành trình của mình, cô đã dao động. Cô đã do dự. Có lẽ, nếu cô cố gắng hơn, cô đã có thể làm chủ sức mạnh này sớm hơn. Có thể đã quay về sớm hơn, cứu được nhiều mạng hơn. Có lẽ...
-"Hunter ơi, ngươi đã làm đủ rồi."
-"Hãy sống kiêu hãnh, ngẩng cao đầu. Free và không ràng buộc. Đó luôn là mong ước của chúng ta."
+"Thợ săn ơi, ngươi đã làm đủ rồi."
+"Hãy sống kiêu hãnh, ngẩng cao đầu. Tự do và không ràng buộc. Đó luôn là mong ước của chúng ta."
 "Ngươi sẽ mãi là niềm tự hào của chúng ta."
 Tất cả đều trả lời bằng những nụ cười rạng rỡ. Và mẹ cô đã lên tiếng với câu hỏi mà cô đã mang theo trong im lặng từ lâu. Một câu hỏi cô chưa bao giờ dám, hay chưa bao giờ có cơ hội, hỏi.
 "Nhưng con ơi, con biết đây không phải là nhà của con."
 "Hành trình của con vẫn phải tiếp tục. Có người vẫn đang chờ con."
 "Nhớ lại khi chúng ta chiến đấu chứ? Hãy cho Leviathan nếm trải sức mạnh đó! Hãy làm điều đó vì tất cả chúng ta! Hãy trả thù cho chúng ta với niềm vui!"
-"Tạm biệt, Angel. Lần này… có lẽ sẽ là mãi mãi."
+"Tạm biệt, Thiên thần. Lần này… có lẽ sẽ là mãi mãi."
 "Đừng quên, chúng ta sẽ luôn ở bên con."
-At last, cha cô làm một động tác, giơ tay lên tạo thành chữ "V" chiến thắng một cách vụng về, quá lố. "Ông già ngốc nghếch…" cô cười cay đắng trong lòng. Nhưng cô hiểu ý nghĩa đằng sau đó. Không cần ôm hôn. Không cần ngoảnh lại. Đó vừa là lời an ủi, vừa là lời từ biệt.
+Cuối cùng, cha cô làm một động tác, giơ tay lên tạo thành chữ "V" chiến thắng một cách vụng về, quá lố. "Ông già ngốc nghếch…" cô cười cay đắng trong lòng. Nhưng cô hiểu ý nghĩa đằng sau đó. Không cần ôm hôn. Không cần ngoảnh lại. Đó vừa là lời an ủi, vừa là lời từ biệt.
 Hình ảnh của họ tan biến thành những đốm sáng, chỉ lối cho cô về một hướng thoáng qua… Đó là lý do họ đến. Họ không còn sức lực để cho đi, nhưng một lần nữa, họ đã cứu cô.
 Thật nực cười khi trò lừa của Leviathan lại phản tác dụng. Hắn muốn kéo cô xuống vực sâu vô tận của &lt;te href=851023&gt;Dark Tide&lt;/te&gt;, nhưng thay vào đó, Hắn lại giúp cô hoàn thành lời từ biệt mà cô đã bị từ chối từ lâu.
 &lt;te href=260006&gt;Fabianum&lt;/te&gt; tan biến trước mắt cô, sụp đổ và biến mất. Nhưng cô không còn là cô bé ngày nào. Quá khứ có đẹp đẽ, nhưng cô sẽ không chìm đắm trong đó. Trái tim có mềm yếu, nhưng cô sẽ tôi luyện bản thân sắc bén hơn.
 Và thế là, không chút do dự, cô quay lưng bước vào bóng tối vô tận.
 Một lần nữa, &lt;te href=260005&gt;Chimera&lt;/te&gt; đứng trước mặt cô.
-Cô chưa bao giờ mong đợi Discord man rợ này hiểu được nhân tính, hay trở thành bạn của cô. Cô chỉ mong rằng, một khi con đường của cô đã rõ ràng, hắn sẽ thôi gây phiền toái cho cô. Và để làm được điều đó, chỉ có một giải pháp: cô phải chế ngự hắn.
-Cô chuẩn bị chiến đấu. Nhưng lần này, Chimera không tấn công. Hắn chỉ im lặng nhìn cô tiến lại gần, cháy bừng trong ngọn lửa của cô—ngọn lửa của Angel. &lt;i&gt;Ngọn lửa của cô.&lt;/i&gt;
-At last, bao nhiêu câu hỏi cũng đã có câu trả lời.
+Cô chưa bao giờ mong đợi Tacet Discord man rợ này hiểu được nhân tính, hay trở thành bạn của cô. Cô chỉ mong rằng, một khi con đường của cô đã rõ ràng, hắn sẽ thôi gây phiền toái cho cô. Và để làm được điều đó, chỉ có một giải pháp: cô phải chế ngự hắn.
+Cô chuẩn bị chiến đấu. Nhưng lần này, Chimera không tấn công. Hắn chỉ im lặng nhìn cô tiến lại gần, cháy bừng trong ngọn lửa của cô—ngọn lửa của Thiên thần. &lt;i&gt;Ngọn lửa của cô.&lt;/i&gt;
+Cuối cùng, bao nhiêu câu hỏi cũng đã có câu trả lời.
 "Không chịu nổi một ngọn lửa nhỏ à?"
 "Thật là trò đùa tồi tệ! Đừng chết ở đây. Đây không phải nơi kết thúc cuộc săn của chúng ta."
 "Chúng ta đã vượt qua những điều tồi tệ hơn trước đây, phải không?"
 Không có con quỷ nào không thể bị săn đuổi. Threnodian chỉ là kẻ mạnh nhất trong số chúng. Và hơn hết, cô không đơn độc trong cuộc chiến này.
-Chimera không nói thêm lời nào và bước sang một bên. Đằng sau hắn, vô số Discord mà cô từng nuốt chửng hiện ra hình hài. Cô đã chiến đấu với chúng đến chết, hết lần này đến lần khác trong những giấc mơ vô tận, cưỡng đoạt sức mạnh của chúng bằng vũ lực. Nhưng giờ đây…
+Chimera không nói thêm lời nào và bước sang một bên. Đằng sau hắn, vô số Tacet Discord mà cô từng nuốt chửng hiện ra hình hài. Cô đã chiến đấu với chúng đến chết, hết lần này đến lần khác trong những giấc mơ vô tận, cưỡng đoạt sức mạnh của chúng bằng vũ lực. Nhưng giờ đây…
 Cô bước qua chúng mà không chút sợ hãi. Một con đường rực lửa mở ra dưới chân cô. Hai bên đường, những sinh vật từng gieo rắc nỗi kinh hoàng cho vô số linh hồn giờ đây cúi đầu tôn kính, như thể hộ tống chủ nhân của chúng ra chiến trường. Chúng cúi đầu trước một con quỷ mạnh hơn chúng? Hay trước một thứ gì đó mà ngay cả quỷ cũng phải khiếp sợ?
 Điều đó không còn quan trọng nữa. Sức mạnh của cô đã vượt xa chúng từ lâu. Cô không cần sự thừa nhận. Chỉ cần sự phục tùng.
 Và cô sẽ sử dụng sức mạnh bị nguyền rủa này để săn đuổi những tội ác lớn hơn—như lời cô đã thề từ thuở ấu thơ, một lời thề không bao giờ phai mờ cho đến chết.
@@ -25726,7 +25724,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;&lt;te href=851106&gt;Combo - Hỗ Trợ Missile: Enhanced&lt;/te&gt;&lt;/color&gt; giờ bắn &lt;color=Highlight&gt;{1}&lt;/color&gt; tên lửa mỗi lần trong &lt;color=Highlight&gt;{0}&lt;/color&gt; giây.</t>
+          <t>&lt;color=Highlight&gt;&lt;te href=851106&gt;Combo - Support Missile: Enhanced&lt;/te&gt;&lt;/color&gt; giờ bắn &lt;color=Highlight&gt;{1}&lt;/color&gt; tên lửa mỗi lần trong &lt;color=Highlight&gt;{0}&lt;/color&gt; giây.</t>
         </is>
       </c>
     </row>
@@ -25791,7 +25789,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;&lt;te href=851107&gt;Combo - Hỏa Tiễn Hỗ Trợ&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851106&gt;Combo - Hỏa Tiễn Hỗ Trợ: Cường Hóa&lt;/te&gt;&lt;/color&gt; ngoài ra còn áp &lt;color=Highlight&gt;{0}&lt;/color&gt; tầng &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Ác Nghiệt Sóng Dữ&lt;/te&gt;&lt;/color&gt; khi trúng mục tiêu, kích hoạt &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=1} mỗi giây.</t>
+          <t>&lt;color=Highlight&gt;&lt;te href=851107&gt;Combo - Hỏa Tiễn Hỗ Trợ&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851106&gt;Combo - Hỏa Tiễn Hỗ Trợ: Cường Hóa&lt;/te&gt;&lt;/color&gt; ngoài ra còn áp &lt;color=Highlight&gt;{0}&lt;/color&gt; tầng &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Ác Nghiệt Sóng Dữ&lt;/te&gt;&lt;/color&gt; khi trúng mục tiêu, kích hoạt &lt;color=Highlight&gt;&lt;SapTag=1&gt;{1}&lt;/SapTag&gt;&lt;/color&gt; {Cus:Sap,S=lần P=lần SapTag=1} mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -26685,9 +26683,9 @@
       <c r="M380" t="inlineStr">
         <is>
           <t>Buổi chiều, mưa phùn lất phất đập vào khung cửa sổ.
-Chisa đứng bên cửa sổ trần của Kho Spacetrek Archive. Năm mười tám tuổi, cuối cùng cô cũng có thời gian để lắng nghe nhịp điệu của cơn mưa—không phải là tiếng mưa đơn điệu lặp đi lặp lại của Honami, mà là những hạt mưa tự nhiên của Lahai-Roi. Tươi mới, sống động, thoang thoảng vị ngọt nhẹ trong không khí. Loại mưa có thể dễ dàng làm ướt bộ đồng phục phơi trên ban công, hay làm ướt sũng một học sinh vô tình trên đường về.
+Chisa đứng bên cửa sổ trần của Kho Lưu Trữ Spacetrek. Năm mười tám tuổi, cuối cùng cô cũng có thời gian để lắng nghe nhịp điệu của cơn mưa—không phải là tiếng mưa đơn điệu lặp đi lặp lại của Honami, mà là những hạt mưa tự nhiên của Lahai-Roi. Tươi mới, sống động, thoang thoảng vị ngọt nhẹ trong không khí. Loại mưa có thể dễ dàng làm ướt bộ đồng phục phơi trên ban công, hay làm ướt sũng một học sinh vô tình trên đường về.
 Hơi nước nhẹ nhàng bốc lên từ tách cà phê trên bàn. Với chiếc kéo, cô mở gói đường... Đúng vậy, cô vẫn mang chúng đi khắp nơi, dù giờ đây chúng được dùng để tỉa cây cảnh hay mở bưu kiện. Đường tan vào mặt tối của tách cà phê. Bên ngoài cửa sổ, vài học sinh trong áo mưa vàng tươi vui giẫm lên vũng nước. Màu sắc rực rỡ của họ xuyên qua màn mưa xám xịt, gợi lại những kỷ niệm về những ngày đối mặt với vòng lặp bất tận và những khởi đầu không ngừng—về một người từng sát cánh cùng cô đến đích của vòng lặp vô tận, rẽ đường xuyên qua đêm dài; và về một người chọn bước đi trên vô số con đường giả dối một mình, biến mình thành nền tảng của sự thật.
-Khi mưa ngớt, Chisa bước ra khỏi Kho Archive với một cuốn sách trong tay. Gió chiều ẩm ướt thổi bay mái tóc mới cắt của cô. Khuôn viên trường trải dài trước mắt, lung linh trong ánh sáng nhẹ nhàng sau cơn mưa. Một nhóm sinh viên Khoa Kỹ Thuật đang tranh luận sôi nổi về một thiết bị bay lơ lửng. Ai đó nhìn thấy cô qua màn sương mỏng, vẫy tay rạng rỡ và gọi cô tham gia—
+Khi mưa ngớt, Chisa bước ra khỏi Kho Lưu Trữ với một cuốn sách trong tay. Gió chiều ẩm ướt thổi bay mái tóc mới cắt của cô. Khuôn viên trường trải dài trước mắt, lung linh trong ánh sáng nhẹ nhàng sau cơn mưa. Một nhóm sinh viên Khoa Kỹ Thuật đang tranh luận sôi nổi về một thiết bị bay lơ lửng. Ai đó nhìn thấy cô qua màn sương mỏng, vẫy tay rạng rỡ và gọi cô tham gia—
 Cô nhìn những tâm hồn trẻ trung, nhiệt huyết ấy, những người đồng hành dưới cùng một bầu trời, tất cả đều hướng về cùng một biển sao. Và cô nhận ra, với sự rõ ràng đến ngỡ ngàng, rằng mình không còn là kẻ lang thang lạc lối trong vòng lặp vô tận nữa. Cuộc đời cô, sau một thời gian đình trệ, đã hòa lại vào dòng sông cuồn cuộn đưa mọi người tiến về phía trước.
 Cô đã thực sự rời xa mùa hè bất tận ấy.
 Bước đi vững chãi, cô tiến về tương lai mới của mình.</t>
@@ -26772,10 +26770,10 @@
         <is>
           <t>Trên phố chính của thành &lt;te href=850091&gt;Jinzhou&lt;/te&gt;, một chủ quán vẫn đang lướt diễn đàn thì một cô gái tóc đỏ rực dừng chân trước quầy. Bà ngước mắt qua gọng kính tuột, mỉm cười.
 "Này chị, thử tí gì không? Trừ tà, bói toán, xem vận mệnh… Chị gọi, tôi ‘lấp lánh’—à khoan, chị là &lt;te href=850087&gt;Tuần Tra Viên&lt;/te&gt; à?"
-"Đúng rồi! Chixia, &lt;te href=850112&gt;Jinzhou Patroller&lt;/te&gt;!" Chixia ưỡn ngực tự hào khi được nhận ra, rồi nhanh chóng lấy lại vẻ nghiêm túc. "Tôi nhận được báo cáo về việc chị bày quầy không phép, bói toán cho bất cứ ai qua đường. Gần như là—"
+"Đúng rồi! Chixia, &lt;te href=850112&gt;Tuần Tra Viên Jinzhou&lt;/te&gt;!" Chixia ưỡn ngực tự hào khi được nhận ra, rồi nhanh chóng lấy lại vẻ nghiêm túc. "Tôi nhận được báo cáo về việc chị bày quầy không phép, bói toán cho bất cứ ai qua đường. Gần như là—"
 "Lừa đảo?" Buling cười không chút nao núng.
 "…Tôi không nói nặng thế. Nhưng chị nên ghé qua &lt;te href=850089&gt;Đồn Tuần Tra&lt;/te&gt; để làm việc về… hoạt động kinh doanh của mình."
-"Trời ơi, chị ơi, toàn là việc tử tế, xây dựng tình cảm thôi mà. Như anh chàng từ &lt;te href=850092&gt;Huaxu Academy&lt;/te&gt; hôm qua ấy. Anh ấy nhờ tôi bói về đề tài nghiên cứu. Giờ này chắc anh ấy đang trên đường đến cảm ơn tôi đây."
+"Trời ơi, chị ơi, toàn là việc tử tế, xây dựng tình cảm thôi mà. Như anh chàng từ &lt;te href=850092&gt;Học viện Huaxu&lt;/te&gt; hôm qua ấy. Anh ấy nhờ tôi bói về đề tài nghiên cứu. Giờ này chắc anh ấy đang trên đường đến cảm ơn tôi đây."
 "Thật à?" Chixia bắt đầu nghi ngờ, nhưng chưa kịp nói hết, một thanh niên mặc áo blouse lao đến quầy.
 "Cảm ơn sư phụ! Thí nghiệm của em cuối cùng cũng thành công—dữ liệu khớp hoàn hảo! Em có thể công bố bài báo rồi!"
 "Khỏi cảm ơn," Buling vẫy tay. "Đó là thành quả của sự chăm chỉ và kiên trì của cậu thôi."
@@ -26783,7 +26781,7 @@
 "Cậu ấy chỉ cần thêm chút tự tin vào nghiên cứu của mình thôi," Buling nói, đẩy chiếc kính tròn lên.
 Cả buổi chiều, Chixia theo sát người chủ quầy khả nghi này khi cô hướng dẫn một nhân viên &lt;te href=850090&gt;Lollo Logistics&lt;/te&gt; lo lắng về công việc, bán bùa phát tài cho một thương nhân lưu động, và xem chỉ tay cho một người dân địa phương về chuyện tình duyên. Mỗi yêu cầu đều khác nhau, câu trả lời của Buling cũng đa dạng, nhưng mọi khách hàng đều ra về với vẻ hài lòng.
 Khi mặt trời lặn, Buling bắt đầu thu dọn quầy. Cô liếc về phía bóng cây gần đó và gọi: "Thư giãn đi. Hôm nay kiếm đủ rồi, tạm nghỉ bán hàng một thời gian. Nhưng tôi đói quá, đi ăn tối ở chỗ dì của cậu nhé? Tôi mời. Nhưng nhớ đừng gọi đồ cay đấy."
-"Khoan—sao chị biết dì Panhua là… Chị cũng bói luôn à?" Chixia bước ra từ bóng tối.
+"Đợi đã—sao chị biết dì Panhua là… Chị cũng bói luôn à?" Chixia bước ra từ bóng tối.
 "À cái đó à?" Buling cười toe toét. "Dì ấy tự kể cho tôi nghe lúc ăn trưa."
 Không lâu sau đó, Buling—đạo sĩ lang thang của &lt;te href=850154&gt;Mengzhou&lt;/te&gt;—và Chixia—"Tia Chớp" nổi tiếng của Jinzhou—sẽ hợp tác điều tra một vụ "ma ám" trên phố chính. Nhưng đó, tất nhiên, là một câu chuyện khác.</t>
         </is>
@@ -26870,14 +26868,14 @@
         <is>
           <t xml:space="preserve">Đêm ấy, mây dày đặc che khuất ánh trăng, nhấn chìm thế giới vào bóng tối.
 "Thầy ơi, nó ở ngay đó!"
-Nghe tiếng đệ tử trẻ kêu lên, lão đạo sĩ lập tức kết ấn bằng một tay, tay kia chĩa thanh kiếm đào gỗ ra phía trước. Ánh vàng lóe lên từ lưỡi kiếm, phóng thẳng về góc tường. Nó va vào một vật vô hình, bùng lên rồi tràn ngập con hẻm bằng thứ ánh sáng chói lòa như ban ngày—phơi bày một Discord &lt;te href=850081&gt;Whisperin&lt;/te&gt; đang núp trong bóng tối.
+Nghe tiếng đệ tử trẻ kêu lên, lão đạo sĩ lập tức kết ấn bằng một tay, tay kia chĩa thanh kiếm đào gỗ ra phía trước. Ánh vàng lóe lên từ lưỡi kiếm, phóng thẳng về góc tường. Nó va vào một vật vô hình, bùng lên rồi tràn ngập con hẻm bằng thứ ánh sáng chói lòa như ban ngày—phơi bày một Tacet Discord &lt;te href=850081&gt;Whisperin&lt;/te&gt; đang núp trong bóng tối.
 Ánh mắt ông lướt về phía đệ tử. Cô bé đã rút bùa ra và bắt đầu niệm chú:
 "Thân ấn hợp nhất, sấm truyền lệnh... Tà ma, tiêu diệt!"
-Lời vừa dứt, một tia sét bổ xuống từ trời, giáng thẳng vào Discord. Bị cuốn trong luồng điện sáng rực, sinh vật ấy bắt đầu tan biến. Dù bùa đã hết hiệu lực, cô bé vẫn cảnh giác, móc ra một đồng xu đồng từ túi áo và tiến lại gần.
+Lời vừa dứt, một tia sét bổ xuống từ trời, giáng thẳng vào Tacet Discord. Bị cuốn trong luồng điện sáng rực, sinh vật ấy bắt đầu tan biến. Dù bùa đã hết hiệu lực, cô bé vẫn cảnh giác, móc ra một đồng xu đồng từ túi áo và tiến lại gần.
 "...Cuối cùng... cũng về nhà..."
 Tiếng thì thào đứt quãng khiến cô đứng sững.
-"Bình tĩnh lại, Bùi Linh," giọng trầm ấm của sư phụ vang lên. "Discord chỉ là một con quái vật. Nó không phải hồn ma, càng không phải con người."
-Cô gật đầu, tung đồng xu lên không trung, và một tia sét nữa lại xé toang bóng tối. Discord biến mất hoàn toàn. Lão đạo sĩ nhíu ngươi nhẹ nhõm, quay về phía ngôi nhà với cánh cổng đóng chặt.
+"Bình tĩnh lại, Bùi Linh," giọng trầm ấm của sư phụ vang lên. "Tacet Discord chỉ là một con quái vật. Nó không phải hồn ma, càng không phải con người."
+Cô gật đầu, tung đồng xu lên không trung, và một tia sét nữa lại xé toang bóng tối. Tacet Discord biến mất hoàn toàn. Lão đạo sĩ nhíu mày nhẹ nhõm, quay về phía ngôi nhà với cánh cổng đóng chặt.
 Ba tiếng gõ đều đặn. Cánh cổng kẽo kẹt mở ra, một cụ già tóc bạc bước ra.
 "Thưa sư phụ, có thật là... con trai lão đã trở về?"
 Đây là lần đầu Bùi Linh theo sư phụ xuống núi để "trừ tà". Trên đường về, cô không khỏi thắc mắc:
@@ -26967,19 +26965,19 @@
       <c r="M383" t="inlineStr">
         <is>
           <t>Giải Vô Địch Võ Thuật năm đó diễn ra trên một đỉnh núi cô độc nằm giữa biên giới &lt;te href=850154&gt;Mengzhou&lt;/te&gt; và &lt;te href=850091&gt;Jinzhou&lt;/te&gt;. Rìa gần nhất của &lt;te href=270001&gt;Xứ Tuyên Phòng&lt;/te&gt; cũng cách đó cả trăm dặm, thế mà các môn phái võ học từ khắp nơi vẫn đổ về núi này. Tin đồn rằng ngay cả một cao thủ ẩn cư từ Tuyên Phòng cũng có thể hạ sơn để quan sát.
-"Hehe, đệ tử của ta là đứa trẻ thẳng tính, chỉ biết đấm đá thôi. Xin hãy bảo đệ tử của ngươi nhẹ tay với nó," Master Thạch Lăng vuốt bộ râu dài, mỉm cười.
-"À, ta nghe nói phái Phong Y Quyền toàn nhân tài, mà Kiếm Tâm thì quả là vô song. Đệ tử của ta chỉ biết nghịch tiền xu và bùa chú, chẳng đáng để ai chú ý đâu," Master Cửu Phong cũng không chịu kém cạnh.
+"Hehe, đệ tử của ta là đứa trẻ thẳng tính, chỉ biết đấm đá thôi. Xin hãy bảo đệ tử của ngươi nhẹ tay với nó," Sư phụ Thạch Lăng vuốt bộ râu dài, mỉm cười.
+"À, ta nghe nói phái Phong Y Quyền toàn nhân tài, mà Kiếm Tâm thì quả là vô song. Đệ tử của ta chỉ biết nghịch tiền xu và bùa chú, chẳng đáng để ai chú ý đâu," Sư phụ Cửu Phong cũng không chịu kém cạnh.
 Trên đài, Bố Linh và Kiếm Tâm đối mặt nhau.
 "Nghe thấy chưa, Kiếm Tâm? Họ đang đấu khẩu qua chúng ta đấy," Bố Linh thì thầm. "Hay là mình bỏ cuộc đi—"
 "Hiểu rồi," Kiếm Tâm đã vào thế "Tĩnh Khí" của Phong Y Quyền. "Hãy đối mặt với trận đấu này bằng sự tôn trọng xứng đáng. Xin mời."
-Bố Linh thở dài và kết ấn thủ. Trước kỹ thuật hoàn hảo của Kiếm Tâm, cô chỉ có một cơ hội duy nhất. Cỗ Hòm Fate của cô bung ra—bùa chú xoáy như bão, sấm chớp xé trời, và Bát Quái Trận Pháp Ngũ Lôi lập tức khóa chặt Kiếm Tâm. Một hơi thở sau, Kiếm Tâm đã lao tới. Gió mây theo sau những cú đấm của nàng. Trong khoảnh khắc tiếp theo, bùa chú vỡ vụn, trận pháp tan tành. Đến hơi thở thứ ba, nắm đấm của nàng đã dừng lại bên sườn Bố Linh.
+Bố Linh thở dài và kết ấn thủ. Trước kỹ thuật hoàn hảo của Kiếm Tâm, cô chỉ có một cơ hội duy nhất. Cỗ Hòm Định Mệnh của cô bung ra—bùa chú xoáy như bão, sấm chớp xé trời, và Bát Quái Trận Pháp Ngũ Lôi lập tức khóa chặt Kiếm Tâm. Một hơi thở sau, Kiếm Tâm đã lao tới. Gió mây theo sau những cú đấm của nàng. Trong khoảnh khắc tiếp theo, bùa chú vỡ vụn, trận pháp tan tành. Đến hơi thở thứ ba, nắm đấm của nàng đã dừng lại bên sườn Bố Linh.
 "Đánh hay lắm, Bố Linh. Thêm hiệp nữa không?" Kiếm Tâm nói, cúi chào khi lùi lại.
 "Không cần đâu. Ta chịu thua." Bố Linh giơ tay đầu hàng.
-Sau đó, Bố Linh tìm được một chỗ ngồi đẹp trên khán đài, vừa nhai bỏng ngô New Federation vừa xem các võ sinh trẻ thi đấu. Kiếm Tâm như cơn gió lốc quét qua đối thủ, nhanh chóng tiến gần đến nhà vô địch đương kim.
+Sau đó, Bố Linh tìm được một chỗ ngồi đẹp trên khán đài, vừa nhai bỏng ngô Liên Bang Mới vừa xem các võ sinh trẻ thi đấu. Kiếm Tâm như cơn gió lốc quét qua đối thủ, nhanh chóng tiến gần đến nhà vô địch đương kim.
 "Sao cô lại không ra đòn mạnh hơn?"
-Giọng nói lạnh lẽo mà trong veo. Bố Linh giật mình, vì cô thậm chí còn không nghe thấy ai đến gần. Một người phụ nữ mặc áo trắng ngồi bên cạnh, ôm cây cổ cầm, Dodget mặt thanh thản, xa cách, chẳng giống một võ sĩ bình thường chút nào.
+Giọng nói lạnh lẽo mà trong veo. Bố Linh giật mình, vì cô thậm chí còn không nghe thấy ai đến gần. Một người phụ nữ mặc áo trắng ngồi bên cạnh, ôm cây cổ cầm, nét mặt thanh thản, xa cách, chẳng giống một võ sĩ bình thường chút nào.
 "Nếu cô kích hoạt bùa chú phía sau cô ấy, có lẽ trận đấu đã khác rồi."
-"Lúc đó em không nghĩ xa đến thế… Master," Bố Linh cười gượng.
+"Lúc đó em không nghĩ xa đến thế… Sư phụ," Bố Linh cười gượng.
 Người phụ nữ chỉ gật đầu. Bà không nói thêm gì, chỉ ngồi bên Bố Linh và im lặng theo dõi những trận đấu còn lại.</t>
         </is>
       </c>
@@ -27057,11 +27055,11 @@
       <c r="M384" t="inlineStr">
         <is>
           <t>Buling đã kết bạn với Encore trong một dịp bất ngờ.
-Hồi đó, cô vừa vượt qua bài test của Camellya và lần đầu đặt chân đến quần đảo &lt;te href=850109&gt;Bờ Đen&lt;/te&gt; với tư cách là một Tư Vấn Viên. Người Trồng Cây đón cô có nhắc đến một tin đồn: ở Khu Vực Mầm Non, mọi người xì xào về những tiếng khóc nữ buồn thảm vẳng ra từ ký túc xá lúc nửa đêm.
-Chuyện chưa nghiêm trọng đến mức phải điều tra chính thức, có lẽ chỉ là một Reverberation lạc loài đang lang thang. Nhưng trên một hòn đảo được tạc từ khối Tacetite khổng lồ, ngay cả một Reverberation ngẫu nhiên cũng có thể biến thành &lt;te href=850081&gt;Discord&lt;/te&gt; nguy hiểm. Ai đó phải test. Buling, nổi tiếng với đôi tai thính, đã xung phong.
+Hồi đó, cô vừa vượt qua bài kiểm tra của Camellya và lần đầu đặt chân đến quần đảo &lt;te href=850109&gt;Bờ Đen&lt;/te&gt; với tư cách là một Tư Vấn Viên. Người Trồng Cây đón cô có nhắc đến một tin đồn: ở Khu Vực Mầm Non, mọi người xì xào về những tiếng khóc nữ buồn thảm vẳng ra từ ký túc xá lúc nửa đêm.
+Chuyện chưa nghiêm trọng đến mức phải điều tra chính thức, có lẽ chỉ là một Reverberation lạc loài đang lang thang. Nhưng trên một hòn đảo được tạc từ khối Tacetite khổng lồ, ngay cả một Reverberation ngẫu nhiên cũng có thể biến thành &lt;te href=850081&gt;Tacet Discord&lt;/te&gt; nguy hiểm. Ai đó phải kiểm tra. Buling, nổi tiếng với đôi tai thính, đã xung phong.
 Đêm đó, cô ngồi chờ ở hành lang ký túc xá, lướt forum giết thời gian thì nghe thấy tiếng bước chân nhẹ. Ngẩng đầu lên, cô suýt làm rơi thiết bị: hai "Vệ Sĩ Ma Lông" đen trắng đang đứng trước mặt với vẻ dữ tợn.
-"Hooray Các chiến binh lông xù dũng cảm đã tìm được thành viên mới rồi!" Một giọng nói vui vẻ vang lên. Encore thò đầu ra từ sau hai con thú nhồi bông, cười toe toét.
-Sự thật hóa ra đơn giản: một &lt;te href=850110&gt;Terminal Tethys&lt;/te&gt; ở Khu Vực Mầm Non đã bắt được băng cassette cũ về chuyện ma. Mô-đun tín hiệu bị lỗi vô tình phát sóng qua loa ký túc xá, tạo nên "hiện tượng ma ám".
+"Hoan hô! Các chiến binh lông xù dũng cảm đã tìm được thành viên mới rồi!" Một giọng nói vui vẻ vang lên. Encore thò đầu ra từ sau hai con thú nhồi bông, cười toe toét.
+Sự thật hóa ra đơn giản: một &lt;te href=850110&gt;Thiết bị đầu cuối Tethys&lt;/te&gt; ở Khu Vực Mầm Non đã bắt được băng cassette cũ về chuyện ma. Mô-đun tín hiệu bị lỗi vô tình phát sóng qua loa ký túc xá, tạo nên "hiện tượng ma ám".
 Sáng hôm sau, một bài đăng trên forum nội bộ Bờ Đen trở nên viral với tiêu đề bắt mắt:
 "Hóa ra, tiếng khóc ma quái lúc nửa đêm ở Khu Vực Mầm Non thực chất là..."
 ID người đăng là "Thần Tiên Trần Gian", và bình luận đầu tiên đầy hào hứng đến từ "Cừu Thiên Đường".
@@ -27138,11 +27136,11 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>So với ngôi đền tĩnh lặng trên núi, thế giới bên ngoài rộng lớn và hỗn loạn biết bao, tràn ngập hàng ngàn tiếng nói. Những ngày đầu rời xa mái ấm của sư phụ, Buling cảm thấy bất an và bực bội. Nếu không giải cứu nhà nghiên cứu của &lt;te href=850092&gt;Huaxu Academy&lt;/te&gt; khỏi &lt;te href=850154&gt;Mengzhou&lt;/te&gt;, người đã tặng cô một chiếc tai nghe nguyên mẫu giúp chặn đứng những cảm giác xâm lấn, có lẽ cô đã phải chịu đựng những lời thì thầm bất tận ấy lâu hơn nhiều.
+          <t>So với ngôi đền tĩnh lặng trên núi, thế giới bên ngoài rộng lớn và hỗn loạn biết bao, tràn ngập hàng ngàn tiếng nói. Những ngày đầu rời xa mái ấm của sư phụ, Buling cảm thấy bất an và bực bội. Nếu không giải cứu nhà nghiên cứu của &lt;te href=850092&gt;Học viện Huaxu&lt;/te&gt; khỏi &lt;te href=850154&gt;Mengzhou&lt;/te&gt;, người đã tặng cô một chiếc tai nghe nguyên mẫu giúp chặn đứng những cảm giác xâm lấn, có lẽ cô đã phải chịu đựng những lời thì thầm bất tận ấy lâu hơn nhiều.
 Cô lang thang qua những con phố đông đúc, dần học cách hòa nhập với nhịp sống hiện đại của thành phố. Lời dạy của sư phụ về sự linh hoạt trở thành kim chỉ nam: thời thế thay đổi, môn phái cũng phải thay đổi theo. Bùa chú và công cụ cần tiến hóa cùng thế giới. Thỉnh thoảng, cô gửi về cho sư phụ những món đồ trừ tà mà cô mua hoặc cải tiến: lò luyện đan vi sóng, chuông trừ tà tích hợp đồng hồ báo thức, hay cây phất trần phát sáng neon trong đêm. Tác phẩm khiến cô tự hào nhất là thanh kiếm gỗ đào điều khiển bằng giọng nói, có thể đổi hướng giữa không trung chỉ bằng một mệnh lệnh, tiện lợi hơn nhiều so với kỹ thuật cưỡi kiếm xưa cũ.
-Sự kiên nhẫn của sư phụ cuối cùng cũng cạn. Một ngày nọ, một bức thư gửi đến với chỉ hai chữ đậm Dodget viết bằng thư pháp tinh tế: "VÔ LÝ TỘT ĐỈNH." Nhưng khi Buling trở về đền, cô thấy ông đang đợi sẵn—với chính thanh kiếm ấy đeo trên lưng.
-Hành trình tu luyện của cô tiếp tục, một con đường quanh co đầy tự nghiệm. Cô đã đi qua phần lớn &lt;te href=850093&gt;Huanglong&lt;/te&gt;, đặt chân lên &lt;te href=850109&gt;Black Shores&lt;/te&gt;, và thậm chí mạo hiểm vào Liên bang New. Cô ngỡ ngàng trước những dòng nước bất tận của Mengzhou, đương đầu với những đỉnh núi gồ ghề của Chongzhou, bước qua những quốc gia có luật lệ chặt chẽ, và lang thang nơi đất vô pháp, nơi chỉ kẻ mạnh mới tồn tại.
-Nhiều năm sau, tại &lt;te href=850096&gt;Rinascita&lt;/te&gt;, cô nhận được một nhiệm vụ qua hệ thống &lt;te href=850110&gt;Tethys&lt;/te&gt;: hỗ trợ một Bloom Bearer đến từ Black Shores, người cũng đã đi xa như cô. Ngay từ đầu, cô đã cảm nhận được thân phận của {Male=anh;Female=chị} ấy phức tạp hơn nhiều so với hồ sơ ghi chép, vì những đường định mệnh của {Male=anh;Female=chị} ấy rối bời đến mức không thể bói toán. Con đường của họ giao nhau hết lần này đến lần khác: tại Thành phố Septimont với hai mặt sáng tối, trong những khu săn bắn bị ám ảnh bởi &lt;te href=851023&gt;Dark Tide&lt;/te&gt;, và trong đống đổ nát của Honami City đã bị hủy diệt. Không nơi nào trong số đó có thể gọi là bình yên.
+Sự kiên nhẫn của sư phụ cuối cùng cũng cạn. Một ngày nọ, một bức thư gửi đến với chỉ hai chữ đậm nét viết bằng thư pháp tinh tế: "VÔ LÝ TỘT ĐỈNH." Nhưng khi Buling trở về đền, cô thấy ông đang đợi sẵn—với chính thanh kiếm ấy đeo trên lưng.
+Hành trình tu luyện của cô tiếp tục, một con đường quanh co đầy tự nghiệm. Cô đã đi qua phần lớn &lt;te href=850093&gt;Huanglong&lt;/te&gt;, đặt chân lên &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt;, và thậm chí mạo hiểm vào Liên bang Mới. Cô ngỡ ngàng trước những dòng nước bất tận của Mengzhou, đương đầu với những đỉnh núi gồ ghề của Chongzhou, bước qua những quốc gia có luật lệ chặt chẽ, và lang thang nơi đất vô pháp, nơi chỉ kẻ mạnh mới tồn tại.
+Nhiều năm sau, tại &lt;te href=850096&gt;Rinascita&lt;/te&gt;, cô nhận được một nhiệm vụ qua hệ thống &lt;te href=850110&gt;Tethys&lt;/te&gt;: hỗ trợ một Bloom Bearer đến từ Bờ Biển Đen, người cũng đã đi xa như cô. Ngay từ đầu, cô đã cảm nhận được thân phận của {Male=him;Female=her} ấy phức tạp hơn nhiều so với hồ sơ ghi chép, vì những đường định mệnh của {Male=anh;Female=chị} ấy rối bời đến mức không thể bói toán. Con đường của họ giao nhau hết lần này đến lần khác: tại Thành phố Septimont với hai mặt sáng tối, trong những khu săn bắn bị ám ảnh bởi &lt;te href=851023&gt;Dark Tide&lt;/te&gt;, và trong đống đổ nát của Thành phố Honami đã bị hủy diệt. Không nơi nào trong số đó có thể gọi là bình yên.
 Buling tự nhận mình là một linh hồn tự do, lang thang theo ý thích. Nhưng Rover kia lại khác—không phải kẻ phiêu lưu vô tư, mà là người mãi chạy trốn từ cơn bão này đến cơn bão khác. Thế nhưng, vì lý do cô không thể gọi tên, cô vẫn muốn thấy {Male=anh;Female=chị} ấy mỉm cười, như thể {Male=anh;Female=chị} ấy cũng có thể tận hưởng khoảnh khắc trên hành trình. Buổi tụ họp yên tĩnh tại quán cà phê Shashou là một trong những khoảnh khắc hiếm hoi không gánh nặng như thế.
 Liệu hành trình của họ sẽ giao nhau ở đâu tiếp theo? Tay Buling đưa lên bộ bói toán, rồi lại buông xuống. Khi thời điểm đến, định mệnh sẽ lại đưa họ gặp nhau. Và khi ấy, cô sẽ ở đó, đưa tay ra đỡ lấy {Male=anh;Female=chị} ấy, như cô vẫn luôn làm.</t>
         </is>
@@ -29362,7 +29360,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;&lt;te href=851107&gt;Combo - Hỏa Tiễn Hỗ Trợ&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851106&gt;Combo - Hỏa Tiễn Hỗ Trợ: Cường Hóa&lt;/te&gt;&lt;/color&gt; ngoài ra còn áp &lt;color=Highlight&gt;&lt;te href=851108&gt;Status - Ác Nghiệt Sóng Dữ&lt;/te&gt;&lt;/color&gt; khi trúng mục tiêu.</t>
+          <t>&lt;color=Highlight&gt;&lt;te href=851107&gt;Combo - Hỏa Tiễn Hỗ Trợ&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=851106&gt;Combo - Hỏa Tiễn Hỗ Trợ: Cường Hóa&lt;/te&gt;&lt;/color&gt; ngoài ra còn áp &lt;color=Highlight&gt;&lt;te href=851108&gt;Trạng Thái - Ác Nghiệt Sóng Dữ&lt;/te&gt;&lt;/color&gt; khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -29427,7 +29425,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Một phương tiện di chuyển đa địa hình nhẹ, đồng phát triển bởi Khoa Kỹ thuật Exostrider và Khoa Vật Chất Hư Không của Startorch Academy. Là công cụ không thể thiếu cho các chuyến thám hiểm thực địa, Học viện đã xây dựng các khóa học lái xe chuyên biệt và nhiều đường đua huấn luyện quanh khuôn viên để đáp ứng tinh thần phiêu lưu của sinh viên và giảng viên.</t>
+          <t>Một phương tiện địa hình nhẹ được đồng phát triển bởi Khoa Kỹ thuật Exostrider và Khoa Vật chất Hư không của Học viện Startorch. Không thể thiếu cho các chuyến thám hiểm thực địa, Học viện đã xây dựng các khóa học lái xe chuyên biệt và nhiều đường đua huấn luyện quanh khuôn viên để đáp ứng tinh thần phiêu lưu của giảng viên và sinh viên.</t>
         </is>
       </c>
     </row>
@@ -29622,7 +29620,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -29687,7 +29685,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -29752,7 +29750,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -29817,7 +29815,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -29882,7 +29880,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -29947,7 +29945,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30012,7 +30010,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30077,7 +30075,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30142,7 +30140,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30207,7 +30205,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30272,7 +30270,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30337,7 +30335,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30402,7 +30400,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30467,7 +30465,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30532,7 +30530,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30597,7 +30595,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30662,7 +30660,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30727,7 +30725,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30792,7 +30790,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30857,7 +30855,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30922,7 +30920,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -30987,7 +30985,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31052,7 +31050,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31117,7 +31115,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31182,7 +31180,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31247,7 +31245,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31312,7 +31310,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31377,7 +31375,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31442,7 +31440,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31507,7 +31505,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31572,7 +31570,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31637,7 +31635,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31702,7 +31700,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31767,7 +31765,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31832,7 +31830,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31897,7 +31895,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -31962,7 +31960,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32025,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32092,7 +32090,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32157,7 +32155,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32222,7 +32220,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32287,7 +32285,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32352,7 +32350,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32417,7 +32415,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32482,7 +32480,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32545,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32612,7 +32610,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32677,7 +32675,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32742,7 +32740,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32807,7 +32805,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32872,7 +32870,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -32937,7 +32935,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33002,7 +33000,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33067,7 +33065,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33132,7 +33130,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33197,7 +33195,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33262,7 +33260,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33327,7 +33325,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33392,7 +33390,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33457,7 +33455,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33522,7 +33520,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33587,7 +33585,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33652,7 +33650,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33717,7 +33715,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33782,7 +33780,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33847,7 +33845,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33912,7 +33910,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -33977,7 +33975,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34042,7 +34040,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34107,7 +34105,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34172,7 +34170,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34237,7 +34235,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34302,7 +34300,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34367,7 +34365,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34432,7 +34430,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34497,7 +34495,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34562,7 +34560,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34627,7 +34625,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
@@ -34692,7 +34690,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echoes thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
+          <t>Để đảm bảo an toàn và dễ tiếp cận, Giải Đấu Peaks of Prestige sử dụng Simulated Echoes—những thực thể nhân tạo được tạo ra bằng công nghệ chuyên dụng và chiếu qua Thiết bị đầu cuối. Khác với Echo thật, chúng chỉ tồn tại trong trận đấu và không gây hại thực sự.</t>
         </is>
       </c>
     </row>
